--- a/Data/numberalphabet.xlsx
+++ b/Data/numberalphabet.xlsx
@@ -472,121 +472,121 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Find missing letter: A, C, F, J, ?</t>
+          <t>What comes next: 1, 2, 6, 24, 120, ?</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>720</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>600</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>P</t>
+          <t>7200</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Q</t>
+          <t>700</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>720</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>Increments +2, +3, +4, +5</t>
+          <t>Factorials 1!, 2!, 3!, 4!, 5!, 6!</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>25</v>
+        <v>4</v>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>What comes next? 10, 21, 43, 87, 175, ?</t>
+          <t>Find the missing letter: A, C, F, J, O, ?</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>351</t>
+          <t>U</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>350</t>
+          <t>T</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>360</t>
+          <t>S</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>355</t>
+          <t>V</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>351</t>
+          <t>U</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>Each term roughly doubles plus 1</t>
+          <t>Alphabet position increments +2,+3,+4,+5,+6.</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>22</v>
+        <v>2</v>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>What comes next: 2, 6, 10, 14, 18, ?</t>
+          <t>What comes next: 3, 8, 15, 24, 35, ?</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>22</t>
+          <t>48</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>24</t>
+          <t>49</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>50</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>23</t>
+          <t>55</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>22</t>
+          <t>48</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>Increments of 4</t>
+          <t>Each term = n² + n, n=1,2,3,...</t>
         </is>
       </c>
     </row>
@@ -632,2851 +632,2851 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>24</v>
+        <v>3</v>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Next in series: ABC, DEF, GHI, JKL, ?</t>
+          <t>What comes next: 4, 9, 19, 39, 79, ?</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>MNO</t>
+          <t>159</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>PQR</t>
+          <t>149</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>STU</t>
+          <t>169</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>VWX</t>
+          <t>179</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>MNO</t>
+          <t>159</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>Triplets progress alphabetically.</t>
+          <t>Each term nearly doubles minus 1</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>5</v>
+        <v>12</v>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Find the next number: 1, 8, 27, 64, ?</t>
+          <t>Find missing letter: G, J, N, S, ?</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>125</t>
+          <t>Y</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>130</t>
+          <t>Z</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>120</t>
+          <t>X</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>135</t>
+          <t>W</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>125</t>
+          <t>Y</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>Cubes of 1,2,3,4,5.</t>
+          <t>Difference: +3,+4,+5,+6</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Find the next number: 3, 5, 9, 17, 33, ?</t>
+          <t>Next number in series: 2, 6, 18, 54, ?</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>65</t>
+          <t>162</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>63</t>
+          <t>150</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>60</t>
+          <t>180</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>70</t>
+          <t>170</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>65</t>
+          <t>162</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>Each term roughly double minus 1</t>
+          <t>Each term ×3</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>12</v>
+        <v>7</v>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Find missing number: 6, 11, 21, 36, 56, ?</t>
+          <t>Find the missing term: 2, 3, 5, 9, 17, ?</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>81</t>
+          <t>33</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>80</t>
+          <t>31</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>85</t>
+          <t>34</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>75</t>
+          <t>30</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>81</t>
+          <t>33</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>Add increasing numbers +5,+10,+15,...</t>
+          <t>Each term after 2 is previous term ×2 -1.</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>4</v>
+        <v>25</v>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Next in series: 1, 2, 6, 24, 120, ?</t>
+          <t>What comes next: 6, 24, 60, 120, 210, ?</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>720</t>
+          <t>336</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>600</t>
+          <t>350</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>7200</t>
+          <t>340</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>360</t>
+          <t>320</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>720</t>
+          <t>336</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>Factorials: 1!,2!,3!,4!,5!,6!</t>
+          <t>Pattern n(n+1)(n+2)/6 for n=2,3,4,5,6,7</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>17</v>
+        <v>8</v>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Next letter: F, K, P, U, ?</t>
+          <t>What comes next: 5, 15, 45, 135, ?</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Z</t>
+          <t>405</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>Y</t>
+          <t>400</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>410</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>W</t>
+          <t>420</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Z</t>
+          <t>405</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>Increasing by 5 letters each time.</t>
+          <t>Multiplied by 3</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>6</v>
+        <v>19</v>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Find missing number: 2, 5, 10, 17, 26, ?</t>
+          <t>Find the next letter: D, H, M, S, ?</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>37</t>
+          <t>Z</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>40</t>
+          <t>Y</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>42</t>
+          <t>X</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>35</t>
+          <t>W</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>37</t>
+          <t>Z</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>Add consecutive odd numbers +3,+5,+7,...</t>
+          <t>Increments +4, +5, +6, +7</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>13</v>
+        <v>8</v>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Next number: 1, 4, 9, 16, 25, ?</t>
+          <t>Find missing term: FG, IJ, MN, QR, ?</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>36</t>
+          <t>UV</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>49</t>
+          <t>ST</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>30</t>
+          <t>WX</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>42</t>
+          <t>YZ</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>36</t>
+          <t>UV</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>Squares of natural numbers</t>
+          <t>Pairs jump +4 letters each time.</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>6</v>
+        <v>24</v>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Find next number: 5, 10, 20, 40, 80, ?</t>
+          <t>Find the missing number: 4, 12, 36, 108, ?</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>160</t>
+          <t>324</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>180</t>
+          <t>300</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>150</t>
+          <t>350</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>200</t>
+          <t>320</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>160</t>
+          <t>324</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>Each term ×2</t>
+          <t>Each term ×3</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>4</v>
+        <v>22</v>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Find the missing letter: A, C, F, J, O, ?</t>
+          <t>Find missing number: 9, 19, 39, 79, 159, ?</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>U</t>
+          <t>319</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>T</t>
+          <t>310</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>S</t>
+          <t>320</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>V</t>
+          <t>300</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>U</t>
+          <t>319</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>Alphabet position increments +2,+3,+4,+5,+6.</t>
+          <t>Each term doubles minus 1</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>18</v>
+        <v>12</v>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Find missing term: 8, 27, 64, 125, 216, ?</t>
+          <t>Find missing letter: G, K, P, V, ?</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>343</t>
+          <t>C</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>350</t>
+          <t>B</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>330</t>
+          <t>A</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>300</t>
+          <t>Z</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>343</t>
+          <t>A</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>Cubes</t>
+          <t>Increments +4, +5, +6, +7</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>6</v>
+        <v>17</v>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Find missing number: 11, 21, 43, 87, 175, ?</t>
+          <t>Find next term: 1, 3, 6, 10, 15, ?</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>351</t>
+          <t>21</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>350</t>
+          <t>22</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>352</t>
+          <t>20</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>355</t>
+          <t>23</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>351</t>
+          <t>21</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>Each term doubles minus 1</t>
+          <t>Triangular numbers</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>2</v>
+        <v>18</v>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Find the missing number: 3, 9, 27, 81, ?</t>
+          <t>Find missing term: 8, 27, 64, 125, 216, ?</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>243</t>
+          <t>343</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>256</t>
+          <t>350</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>225</t>
+          <t>330</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>270</t>
+          <t>300</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>243</t>
+          <t>343</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>Each term multiplied by 3.</t>
+          <t>Cubes</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>11</v>
+        <v>16</v>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Find next number: 7, 14, 28, 56, ?</t>
+          <t>Find missing term: 7, 14, 28, 56, 112, ?</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>112</t>
+          <t>224</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>110</t>
+          <t>226</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>114</t>
+          <t>230</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>120</t>
+          <t>220</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>112</t>
+          <t>224</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>Each term ×2</t>
+          <t>Each term ×2.</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>4</v>
+        <v>19</v>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Find the next term: 1, 3, 7, 15, 31, ?</t>
+          <t>What comes next: 8, 27, 64, 125, ?</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>63</t>
+          <t>216</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>65</t>
+          <t>225</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>61</t>
+          <t>200</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>67</t>
+          <t>230</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>63</t>
+          <t>216</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>Each term = previous × 2 + 1</t>
+          <t>Cubes of 2,3,4,5,6.</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Next in series: ZX, VT, RP, NL, ?</t>
+          <t>Find next term: 1, 3, 6, 10, 15, ?</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>JH</t>
+          <t>21</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>KF</t>
+          <t>22</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>JG</t>
+          <t>20</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>KH</t>
+          <t>23</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>JH</t>
+          <t>21</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>Pairs move backward skipping one letter.</t>
+          <t>Triangular numbers.</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>2</v>
+        <v>10</v>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Find the missing number: 3, 9, 27, ?, 243</t>
+          <t>Find the next number: 21, 34, 55, 89, 144, ?</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>54</t>
+          <t>233</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>81</t>
+          <t>220</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>72</t>
+          <t>240</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>90</t>
+          <t>200</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>81</t>
+          <t>233</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>Each term multiplied by 3; 27×3=81</t>
+          <t>Fibonacci sequence</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>25</v>
+        <v>17</v>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>Find missing term: UV, YZ, DE, HI, ?</t>
+          <t>Find missing number: 3, 9, 27, 81, ?</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>LM</t>
+          <t>243</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>OP</t>
+          <t>250</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>QR</t>
+          <t>240</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>ST</t>
+          <t>245</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>LM</t>
+          <t>243</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>Pairs jump +4 letters cyclically.</t>
+          <t>Multiplied by 3</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>20</v>
+        <v>1</v>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>Find next letter: Z, V, Q, K, ?</t>
+          <t>Find the next number: 2, 12, 36, 80, 150, ?</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>252</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>F</t>
+          <t>200</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>E</t>
+          <t>240</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>300</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>F</t>
+          <t>252</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>Difference in positions: -4, -5, -6, -7</t>
+          <t>Pattern: n³ - n, for n=2,3,4,5,6 → 6³-6=216-6=210 (adjusted here as 252)</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>3</v>
+        <v>15</v>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>What comes next: 4, 9, 19, 39, 79, ?</t>
+          <t>Find next term: BC, DE, GH, KL, ?</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>159</t>
+          <t>OP</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>149</t>
+          <t>MN</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>169</t>
+          <t>QR</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>179</t>
+          <t>ST</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>159</t>
+          <t>OP</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>Each term nearly doubles minus 1</t>
+          <t>Pairs jump increasing letters.</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>What comes next: 3, 8, 15, 24, 35, ?</t>
+          <t>Next letter: A, D, H, M, S, ?</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>48</t>
+          <t>Z</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>49</t>
+          <t>Y</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>50</t>
+          <t>X</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>55</t>
+          <t>W</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>48</t>
+          <t>Z</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>Each term = n² + n, n=1,2,3,...</t>
+          <t>Increments +3, +4, +5, +6, +7</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>15</v>
+        <v>9</v>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>Find next number: 4, 9, 19, 39, 79, ?</t>
+          <t>Find missing number: 2, 4, 8, 14, 22, ?</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>159</t>
+          <t>32</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>149</t>
+          <t>30</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>169</t>
+          <t>34</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>179</t>
+          <t>36</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>159</t>
+          <t>32</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>Each term roughly doubles minus 1</t>
+          <t>Incrementing differences: +2, +4, +6, +8, next +10=32</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>22</v>
+        <v>16</v>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>What comes next: MNO, PQR, STU, VWX, ?</t>
+          <t>Find next letter: C, F, J, O, ?</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>YZA</t>
+          <t>U</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>BCD</t>
+          <t>V</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>CDE</t>
+          <t>W</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>DEF</t>
+          <t>X</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>YZA</t>
+          <t>U</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>Triplets shift +4 letters cyclically.</t>
+          <t>Increments +3, +4, +5, +6</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>What comes next: 8, 27, 64, 125, ?</t>
+          <t>Find missing letter: F, K, P, U, ?</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>216</t>
+          <t>Z</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>225</t>
+          <t>Y</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>220</t>
+          <t>X</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>230</t>
+          <t>W</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>216</t>
+          <t>Z</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>Cubes of 2,3,4,5,6</t>
+          <t>Increments +5 each time</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>22</v>
+        <v>5</v>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>Find missing number: 9, 19, 39, 79, 159, ?</t>
+          <t>Find missing term: CDE, FGH, KLM, PQR, ?</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>319</t>
+          <t>VWX</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>310</t>
+          <t>STU</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>320</t>
+          <t>XYZ</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>300</t>
+          <t>UVW</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>319</t>
+          <t>VWX</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>Each term doubles minus 1</t>
+          <t>Triplets jump by +3 letters each time.</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>Find the next number: 7, 14, 28, 56, ?</t>
+          <t>Find next number: 5, 10, 20, 40, 80, ?</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>110</t>
+          <t>160</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>112</t>
+          <t>180</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>120</t>
+          <t>150</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>114</t>
+          <t>200</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>112</t>
+          <t>160</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>Each term is multiplied by 2.</t>
+          <t>Each term ×2</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>2</v>
+        <v>21</v>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>Find the missing term: XYZ, UVW, RST, OPQ, ?</t>
+          <t>Next number: 3, 9, 27, 81, ?</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>LMN</t>
+          <t>243</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>NOP</t>
+          <t>256</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>KLM</t>
+          <t>225</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>JKL</t>
+          <t>270</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>LMN</t>
+          <t>243</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>Each triple moves backward by 3 letters.</t>
+          <t>Multiplying by 3.</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>11</v>
+        <v>25</v>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>What comes next: 3, 6, 12, 24, 48, ?</t>
+          <t>Next letter: A, C, F, J, O, ?</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>96</t>
+          <t>U</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>100</t>
+          <t>T</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>90</t>
+          <t>S</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>98</t>
+          <t>V</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>96</t>
+          <t>U</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>Each term multiplied by 2</t>
+          <t>Incrementing by increasing letters.</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>21</v>
+        <v>2</v>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>Next number: 3, 9, 27, 81, ?</t>
+          <t>Find the missing letter: Z, X, U, Q, L, ?</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>243</t>
+          <t>F</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>256</t>
+          <t>G</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>225</t>
+          <t>E</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>270</t>
+          <t>H</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>243</t>
+          <t>F</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>Multiplying by 3.</t>
+          <t>Positions decrease by 2,3,4,5,6</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>5</v>
+        <v>13</v>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>What comes next? 121, 144, 169, 196, ?</t>
+          <t>Next number: 1, 4, 9, 16, 25, ?</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>225</t>
+          <t>36</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>240</t>
+          <t>49</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>256</t>
+          <t>30</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>289</t>
+          <t>42</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>225</t>
+          <t>36</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>Squares of 11,12,13,14,15</t>
+          <t>Squares of natural numbers</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>12</v>
+        <v>1</v>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>Next in series: UVW, RST, OPQ, LMN, ?</t>
+          <t>Find the next number: 2, 5, 10, 17, 26, ?</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>IJK</t>
+          <t>35</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>HIJ</t>
+          <t>37</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>FGH</t>
+          <t>38</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>GHI</t>
+          <t>40</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>IJK</t>
+          <t>37</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>Triplets move backward by 3 letters.</t>
+          <t>Each term increases by consecutive odd numbers: +3, +5, +7, +9, next +11=37</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>19</v>
+        <v>14</v>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>Next number in series: 2, 6, 18, 54, ?</t>
+          <t>Find next letter: D, G, K, P, ?</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>162</t>
+          <t>V</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>150</t>
+          <t>W</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>180</t>
+          <t>U</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>170</t>
+          <t>T</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>162</t>
+          <t>V</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>Each term ×3</t>
+          <t>Increments +3, +4, +5, +6</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>21</v>
+        <v>6</v>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>What comes next: 10, 21, 43, 87, 175, ?</t>
+          <t>What comes next: Z, X, U, Q, L, ?</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>351</t>
+          <t>F</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>350</t>
+          <t>G</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>360</t>
+          <t>H</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>355</t>
+          <t>I</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>351</t>
+          <t>F</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>Each term doubles minus 1</t>
+          <t>Alphabet positions decrease by 2,3,4,5,6.</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>19</v>
+        <v>8</v>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>Find the next term: DE, GH, KL, OP, ?</t>
+          <t>Find missing number: 1, 3, 7, 15, 31, ?</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>ST</t>
+          <t>63</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>UV</t>
+          <t>64</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>WX</t>
+          <t>65</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>YZ</t>
+          <t>62</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>ST</t>
+          <t>63</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>Pairs jump +4 letters.</t>
+          <t>Each term = previous ×2 +1</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>14</v>
+        <v>6</v>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>Find the missing number: 7, 21, 63, 189, ?</t>
+          <t>Find the next term: PQ, RS, TU, WX, ?</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>567</t>
+          <t>YZ</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>560</t>
+          <t>ZA</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>570</t>
+          <t>AB</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>600</t>
+          <t>BC</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>567</t>
+          <t>YZ</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>Each term ×3</t>
+          <t>Pairs move sequentially in alphabets; after WX is YZ.</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>What is the next term? 3, 6, 12, 24, 48, ?</t>
+          <t>What comes next: ZYX, WVU, TSR, QPO, ?</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>96</t>
+          <t>NML</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>90</t>
+          <t>KJI</t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>100</t>
+          <t>HGF</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>108</t>
+          <t>EDC</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>96</t>
+          <t>NML</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>Each term ×2</t>
+          <t>Triplets decrease by 3 letters.</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>13</v>
+        <v>21</v>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>Next number: 7, 14, 28, 56, 112, ?</t>
+          <t>What comes next: 10, 21, 43, 87, 175, ?</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>224</t>
+          <t>351</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>225</t>
+          <t>350</t>
         </is>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>223</t>
+          <t>360</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>220</t>
+          <t>355</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>224</t>
+          <t>351</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>Each term multiplied by 2</t>
+          <t>Each term doubles minus 1</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>14</v>
+        <v>19</v>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>Find the missing letter: Z, W, S, N, ?</t>
+          <t>Find the next term: DE, GH, KL, OP, ?</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>I</t>
+          <t>ST</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>H</t>
+          <t>UV</t>
         </is>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>J</t>
+          <t>WX</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>K</t>
+          <t>YZ</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>I</t>
+          <t>ST</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>Decreasing by 3,4,5,6 letters</t>
+          <t>Pairs jump +4 letters.</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>3</v>
+        <v>24</v>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>What is the next term? A, D, I, P, ?</t>
+          <t>Next in series: ABC, DEF, GHI, JKL, ?</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Y</t>
+          <t>MNO</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>Z</t>
+          <t>PQR</t>
         </is>
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>W</t>
+          <t>STU</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>VWX</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Y</t>
+          <t>MNO</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>Positions are squares: 1,4,9,16,25 → A,E,I,P,Y</t>
+          <t>Triplets progress alphabetically.</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>7</v>
+        <v>14</v>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>Find the missing term: 2, 3, 5, 9, 17, ?</t>
+          <t>Find the missing number: 7, 21, 63, 189, ?</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>33</t>
+          <t>567</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>31</t>
+          <t>560</t>
         </is>
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>34</t>
+          <t>570</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>30</t>
+          <t>600</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>33</t>
+          <t>567</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>Each term after 2 is previous term ×2 -1.</t>
+          <t>Each term ×3</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>Next in series: 11, 13, 17, 19, 23, ?</t>
+          <t>Find the missing letter: C, F, J, O, ?</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>29</t>
+          <t>U</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>31</t>
+          <t>V</t>
         </is>
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>28</t>
+          <t>W</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>27</t>
+          <t>X</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>29</t>
+          <t>U</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>Prime numbers in order</t>
+          <t>Incrementing by +3,+4,+5,+6.</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>What comes next: Z, X, U, Q, L, ?</t>
+          <t>What comes next? KL, NO, ST, WX, ?</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>F</t>
+          <t>BD</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>G</t>
+          <t>YZ</t>
         </is>
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>H</t>
+          <t>AB</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>I</t>
+          <t>CD</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>F</t>
+          <t>AB</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>Alphabet positions decrease by 2,3,4,5,6.</t>
+          <t>Letters move in pairs skipping one letter; after WX comes AB.</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>Next letter: A, D, H, M, S, ?</t>
+          <t>Find missing number: 4, 9, 19, 39, 79, ?</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Z</t>
+          <t>159</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>Y</t>
+          <t>169</t>
         </is>
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>149</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>W</t>
+          <t>179</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Z</t>
+          <t>159</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>Increments +3, +4, +5, +6, +7</t>
+          <t>Each term approximately doubles minus 1.</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>4</v>
+        <v>18</v>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>Find the missing letter: B, D, G, K, P, ?</t>
+          <t>Find missing letter: A, C, F, J, ?</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>V</t>
+          <t>O</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>U</t>
+          <t>N</t>
         </is>
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>T</t>
+          <t>P</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>S</t>
+          <t>Q</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>V</t>
+          <t>O</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>Difference in positions: +2,+3,+4,+5,+6</t>
+          <t>Increments +2, +3, +4, +5</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>24</v>
+        <v>20</v>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>Find the missing number: 4, 12, 36, 108, ?</t>
+          <t>Find the next number: 3, 5, 9, 17, 33, ?</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>324</t>
+          <t>65</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>300</t>
+          <t>63</t>
         </is>
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>350</t>
+          <t>60</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>320</t>
+          <t>70</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>324</t>
+          <t>65</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>Each term ×3</t>
+          <t>Each term roughly double minus 1</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>12</v>
+        <v>1</v>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>Find the missing letter: C, F, J, O, ?</t>
+          <t>What comes next in the series? AB, DE, IJ, OP, ?</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>U</t>
+          <t>UV</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>V</t>
+          <t>ST</t>
         </is>
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>W</t>
+          <t>WX</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>YZ</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>U</t>
+          <t>UV</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>Incrementing by +3,+4,+5,+6.</t>
+          <t>Each pair skips increasing letters: +3,+4,+5,+6 between first letters.</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>23</v>
+        <v>14</v>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>What comes next: 5, 11, 23, 47, 95, ?</t>
+          <t>Find the missing letter: P, M, J, G, ?</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>191</t>
+          <t>D</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>189</t>
+          <t>C</t>
         </is>
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>193</t>
+          <t>E</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>185</t>
+          <t>F</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>191</t>
+          <t>D</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>Doubling minus 1.</t>
+          <t>Decreasing by 3 letters.</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>19</v>
+        <v>24</v>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>Find the next letter: D, H, M, S, ?</t>
+          <t>Find next letter: Y, V, R, M, ?</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Z</t>
+          <t>H</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>Y</t>
+          <t>I</t>
         </is>
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>J</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>W</t>
+          <t>G</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Z</t>
+          <t>H</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>Increments +4, +5, +6, +7</t>
+          <t>Decreases by 3,4,5,6 letters</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>Find next number: 6, 12, 24, 48, 96, ?</t>
+          <t>What comes next: 11, 13, 17, 19, 23, ?</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>192</t>
+          <t>29</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>190</t>
+          <t>27</t>
         </is>
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>195</t>
+          <t>31</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>185</t>
+          <t>25</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>192</t>
+          <t>29</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>Each term multiplied by 2</t>
+          <t>Prime numbers in order.</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>1</v>
+        <v>9</v>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>Find the next number: 2, 12, 36, 80, 150, ?</t>
+          <t>Find the next term: 2, 3, 5, 8, 12, 17, ?</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>252</t>
+          <t>23</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>200</t>
+          <t>25</t>
         </is>
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>240</t>
+          <t>24</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>300</t>
+          <t>26</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>252</t>
+          <t>23</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>Pattern: n³ - n, for n=2,3,4,5,6 → 6³-6=216-6=210 (adjusted here as 252)</t>
+          <t>Difference increases by 1: +1,+2,+3,+4,+5</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>18</v>
+        <v>7</v>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>What comes next: UVW, XYZ, ABC, DEF, ?</t>
+          <t>Find next letter: B, E, I, N, ?</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>GHI</t>
+          <t>T</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>JKL</t>
+          <t>U</t>
         </is>
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>MNO</t>
+          <t>S</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>PQR</t>
+          <t>R</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>GHI</t>
+          <t>T</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>Triplets shift +3 letters cyclically.</t>
+          <t>Increments +3, +4, +5, +6</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>25</v>
+        <v>14</v>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>What comes next: 6, 24, 60, 120, 210, ?</t>
+          <t>Find the missing letter: Z, W, S, N, ?</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>336</t>
+          <t>I</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>350</t>
+          <t>H</t>
         </is>
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>340</t>
+          <t>J</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>320</t>
+          <t>K</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>336</t>
+          <t>I</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>Pattern n(n+1)(n+2)/6 for n=2,3,4,5,6,7</t>
+          <t>Decreasing by 3,4,5,6 letters</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>16</v>
+        <v>9</v>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>Find next letter: C, F, J, O, ?</t>
+          <t>Next in series: 11, 13, 17, 19, 23, ?</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>U</t>
+          <t>29</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>V</t>
+          <t>31</t>
         </is>
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>W</t>
+          <t>28</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>27</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>U</t>
+          <t>29</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>Increments +3, +4, +5, +6</t>
+          <t>Prime numbers in order</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>1</v>
+        <v>11</v>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>Find the next number: 2, 5, 10, 17, 26, ?</t>
+          <t>What comes next: 3, 6, 12, 24, 48, ?</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>35</t>
+          <t>96</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>37</t>
+          <t>90</t>
         </is>
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>38</t>
+          <t>100</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>40</t>
+          <t>110</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>37</t>
+          <t>96</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>Each term increases by consecutive odd numbers: +3, +5, +7, +9, next +11=37</t>
+          <t>Each term doubles</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>What comes next in the series? 2, 6, 12, 20, 30, ?</t>
+          <t>Find the missing letter: B, D, G, K, P, ?</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>40</t>
+          <t>V</t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>42</t>
+          <t>U</t>
         </is>
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>44</t>
+          <t>T</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>36</t>
+          <t>S</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>42</t>
+          <t>V</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>Each term is n(n+1); next: 6×7=42</t>
+          <t>Difference in positions: +2,+3,+4,+5,+6</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>What comes next: 1, 2, 6, 24, 120, ?</t>
+          <t>Find next letter: P, M, J, G, ?</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>720</t>
+          <t>D</t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>600</t>
+          <t>C</t>
         </is>
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>7200</t>
+          <t>B</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>700</t>
+          <t>E</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>720</t>
+          <t>D</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>Factorials 1!, 2!, 3!, 4!, 5!, 6!</t>
+          <t>Decreasing by 3 letters</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>24</v>
+        <v>10</v>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>Find next term: 1, 4, 9, 16, 25, ?</t>
+          <t>What comes next: ABC, BCD, CDE, DEF, ?</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>36</t>
+          <t>EFG</t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>49</t>
+          <t>FGH</t>
         </is>
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>30</t>
+          <t>GHI</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>42</t>
+          <t>HIJ</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>36</t>
+          <t>EFG</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>Squares.</t>
+          <t>Each triplet shifts by one letter forward.</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>16</v>
+        <v>23</v>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>What letter comes next? P, M, J, G, ?</t>
+          <t>What comes next: 5, 11, 23, 47, 95, ?</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>191</t>
         </is>
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>189</t>
         </is>
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>E</t>
+          <t>193</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>F</t>
+          <t>185</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>191</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>Decreasing by 3 positions each time</t>
+          <t>Doubling minus 1.</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>3</v>
+        <v>17</v>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>Next in series: AZ, CY, EX, GV, ?</t>
+          <t>What comes next: 1, 8, 27, 64, 125, ?</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>IT</t>
+          <t>216</t>
         </is>
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>HS</t>
+          <t>225</t>
         </is>
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>JU</t>
+          <t>210</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>KT</t>
+          <t>230</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>IT</t>
+          <t>216</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>First letters move +2, second letters -2; IT follows pattern.</t>
+          <t>Cubes of natural numbers</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>Find next letter: P, M, J, G, ?</t>
+          <t>Find the next term: 7, 14, 28, 56, 112, ?</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>224</t>
         </is>
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>230</t>
         </is>
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>220</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>E</t>
+          <t>210</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>224</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>Decreasing by 3 letters</t>
+          <t>Each term ×2</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>7</v>
+        <v>22</v>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>Find the missing letter: Z, X, U, Q, L, ?</t>
+          <t>What comes next: 2, 6, 10, 14, 18, ?</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>F</t>
+          <t>22</t>
         </is>
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>G</t>
+          <t>24</t>
         </is>
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>H</t>
+          <t>20</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>I</t>
+          <t>23</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>F</t>
+          <t>22</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>Positions decrease by 2,3,4,5,6</t>
+          <t>Increments of 4</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>17</v>
+        <v>9</v>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>Find next term: 1, 3, 6, 10, 15, ?</t>
+          <t>Next in series: ZX, VT, RP, NL, ?</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>21</t>
+          <t>JH</t>
         </is>
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>22</t>
+          <t>KF</t>
         </is>
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>JG</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>23</t>
+          <t>KH</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>21</t>
+          <t>JH</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>Triangular numbers</t>
+          <t>Pairs move backward skipping one letter.</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>8</v>
+        <v>3</v>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>What comes next: 5, 15, 45, 135, ?</t>
+          <t>What is the next term? A, D, I, P, ?</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>405</t>
+          <t>Y</t>
         </is>
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>400</t>
+          <t>Z</t>
         </is>
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>410</t>
+          <t>W</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>420</t>
+          <t>X</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>405</t>
+          <t>Y</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>Multiplied by 3</t>
+          <t>Positions are squares: 1,4,9,16,25 → A,E,I,P,Y</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>14</v>
+        <v>18</v>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>Find the missing letter: P, M, J, G, ?</t>
+          <t>What comes next: UVW, XYZ, ABC, DEF, ?</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>GHI</t>
         </is>
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>JKL</t>
         </is>
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>E</t>
+          <t>MNO</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>F</t>
+          <t>PQR</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>GHI</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>Decreasing by 3 letters.</t>
+          <t>Triplets shift +3 letters cyclically.</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>Find next number: 5, 15, 45, 135, ?</t>
+          <t>Find the missing number: 2, 6, 12, 20, 30, ?</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>405</t>
+          <t>40</t>
         </is>
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>420</t>
+          <t>42</t>
         </is>
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>400</t>
+          <t>44</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>410</t>
+          <t>36</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>405</t>
+          <t>42</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>Multiply by 3</t>
+          <t>Using formula n(n+1).</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>7</v>
+        <v>20</v>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>Find next letter: B, E, I, N, ?</t>
+          <t>Find next letter: Z, V, Q, K, ?</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>T</t>
+          <t>B</t>
         </is>
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>U</t>
+          <t>F</t>
         </is>
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>S</t>
+          <t>E</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>R</t>
+          <t>C</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>T</t>
+          <t>F</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>Increments +3, +4, +5, +6</t>
+          <t>Difference in positions: -4, -5, -6, -7</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>18</v>
+        <v>13</v>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>What comes next: 13, 21, 34, 55, 89, ?</t>
+          <t>Next number: 5, 10, 20, 40, 80, ?</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>144</t>
+          <t>160</t>
         </is>
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>135</t>
+          <t>180</t>
         </is>
       </c>
       <c r="E72" t="inlineStr">
         <is>
+          <t>150</t>
+        </is>
+      </c>
+      <c r="F72" t="inlineStr">
+        <is>
           <t>140</t>
         </is>
       </c>
-      <c r="F72" t="inlineStr">
-        <is>
-          <t>150</t>
-        </is>
-      </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>144</t>
+          <t>160</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>Fibonacci sequence</t>
+          <t>Each term ×2.</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>23</v>
+        <v>12</v>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>Next number in series: 1, 2, 6, 24, 120, ?</t>
+          <t>Next in series: UVW, RST, OPQ, LMN, ?</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>720</t>
+          <t>IJK</t>
         </is>
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>600</t>
+          <t>HIJ</t>
         </is>
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>7200</t>
+          <t>FGH</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>72000</t>
+          <t>GHI</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>720</t>
+          <t>IJK</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>Factorials: 1!, 2!, 3!, 4!, 5!, 6!</t>
+          <t>Triplets move backward by 3 letters.</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>What comes next in the series? AB, DE, IJ, OP, ?</t>
+          <t>Find the next term: 1, 3, 7, 15, 31, ?</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>UV</t>
+          <t>63</t>
         </is>
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>ST</t>
+          <t>65</t>
         </is>
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>WX</t>
+          <t>61</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>YZ</t>
+          <t>67</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>UV</t>
+          <t>63</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>Each pair skips increasing letters: +3,+4,+5,+6 between first letters.</t>
+          <t>Each term = previous × 2 + 1</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>9</v>
+        <v>17</v>
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>What comes next: 13, 21, 34, 55, 89, ?</t>
+          <t>Find missing term: JK, NO, RS, VW, ?</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>144</t>
+          <t>BC</t>
         </is>
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>135</t>
+          <t>YZ</t>
         </is>
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>150</t>
+          <t>XY</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>140</t>
+          <t>ZA</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>144</t>
+          <t>BC</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>Fibonacci series.</t>
+          <t>Pairs jump +4 letters.</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>21</v>
+        <v>8</v>
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>Find the missing term: 5, 11, 23, 47, 95, ?</t>
+          <t>Next letter: B, D, G, K, P, ?</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>191</t>
+          <t>V</t>
         </is>
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>189</t>
+          <t>W</t>
         </is>
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>193</t>
+          <t>U</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>185</t>
+          <t>T</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>191</t>
+          <t>V</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>Each term roughly doubles minus 1</t>
+          <t>Incrementing letter positions +2,+3,+4,+5,+6.</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>Find missing number: 4, 9, 19, 39, 79, ?</t>
+          <t>Find next number: 4, 9, 19, 39, 79, ?</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
@@ -3486,14 +3486,14 @@
       </c>
       <c r="D77" t="inlineStr">
         <is>
+          <t>149</t>
+        </is>
+      </c>
+      <c r="E77" t="inlineStr">
+        <is>
           <t>169</t>
         </is>
       </c>
-      <c r="E77" t="inlineStr">
-        <is>
-          <t>149</t>
-        </is>
-      </c>
       <c r="F77" t="inlineStr">
         <is>
           <t>179</t>
@@ -3506,1887 +3506,1887 @@
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>Each term approximately doubles minus 1.</t>
+          <t>Each term roughly doubles minus 1</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>Next number: 5, 10, 20, 40, 80, ?</t>
+          <t>What comes next: 2, 6, 18, 54, 162, ?</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>160</t>
+          <t>486</t>
         </is>
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>180</t>
+          <t>500</t>
         </is>
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>150</t>
+          <t>490</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>140</t>
+          <t>480</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>160</t>
+          <t>486</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>Each term ×2.</t>
+          <t>Each term ×3</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>9</v>
+        <v>21</v>
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>Find missing number: 2, 4, 8, 14, 22, ?</t>
+          <t>Find missing term: EF, IJ, MN, ST, ?</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>32</t>
+          <t>YZ</t>
         </is>
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>30</t>
+          <t>WX</t>
         </is>
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>34</t>
+          <t>UV</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>36</t>
+          <t>QR</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>32</t>
+          <t>YZ</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>Incrementing differences: +2, +4, +6, +8, next +10=32</t>
+          <t>Pairs jump +4 letters.</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>Find the next term: 2, 3, 5, 8, 12, 17, ?</t>
+          <t>What comes next: ABC, DEF, GHI, JKL, ?</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>23</t>
+          <t>MNO</t>
         </is>
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>25</t>
+          <t>PQR</t>
         </is>
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>24</t>
+          <t>STU</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>26</t>
+          <t>VWX</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>23</t>
+          <t>MNO</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>Difference increases by 1: +1,+2,+3,+4,+5</t>
+          <t>Triplets progress in alphabetical order.</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="n">
-        <v>12</v>
+        <v>1</v>
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>Find missing letter: G, K, P, V, ?</t>
+          <t>What comes next in the series? 2, 6, 12, 20, 30, ?</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>40</t>
         </is>
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>42</t>
         </is>
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>44</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Z</t>
+          <t>36</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>42</t>
         </is>
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>Increments +4, +5, +6, +7</t>
+          <t>Each term is n(n+1); next: 6×7=42</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="n">
-        <v>19</v>
+        <v>8</v>
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>What comes next: 8, 27, 64, 125, ?</t>
+          <t>What is next? 1, 4, 9, 16, 25, ?</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>216</t>
+          <t>36</t>
         </is>
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>225</t>
+          <t>49</t>
         </is>
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>200</t>
+          <t>30</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>230</t>
+          <t>42</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>216</t>
+          <t>36</t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>Cubes of 2,3,4,5,6.</t>
+          <t>Perfect squares</t>
         </is>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="n">
-        <v>13</v>
+        <v>24</v>
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>Find missing term: CD, GH, LM, ST, ?</t>
+          <t>Find next term: 1, 4, 9, 16, 25, ?</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>YZ</t>
+          <t>36</t>
         </is>
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>WX</t>
+          <t>49</t>
         </is>
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>UV</t>
+          <t>30</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>QR</t>
+          <t>42</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>YZ</t>
+          <t>36</t>
         </is>
       </c>
       <c r="H83" t="inlineStr">
         <is>
-          <t>Pairs jump +4 letters each time.</t>
+          <t>Squares.</t>
         </is>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>Find missing number: 3, 9, 27, 81, ?</t>
+          <t>Find next number: 5, 15, 45, 135, ?</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>243</t>
+          <t>405</t>
         </is>
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>250</t>
+          <t>420</t>
         </is>
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>240</t>
+          <t>400</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>245</t>
+          <t>410</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>243</t>
+          <t>405</t>
         </is>
       </c>
       <c r="H84" t="inlineStr">
         <is>
-          <t>Multiplied by 3</t>
+          <t>Multiply by 3</t>
         </is>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="n">
-        <v>15</v>
+        <v>23</v>
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>What comes next: 11, 13, 17, 19, 23, ?</t>
+          <t>Next number in series: 1, 2, 6, 24, 120, ?</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>29</t>
+          <t>720</t>
         </is>
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t>27</t>
+          <t>600</t>
         </is>
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>31</t>
+          <t>7200</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>25</t>
+          <t>72000</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>29</t>
+          <t>720</t>
         </is>
       </c>
       <c r="H85" t="inlineStr">
         <is>
-          <t>Prime numbers in order.</t>
+          <t>Factorials: 1!, 2!, 3!, 4!, 5!, 6!</t>
         </is>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="n">
-        <v>11</v>
+        <v>20</v>
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>Find next term: 1, 3, 6, 10, 15, ?</t>
+          <t>Find next number: 6, 12, 24, 48, 96, ?</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>21</t>
+          <t>192</t>
         </is>
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t>22</t>
+          <t>190</t>
         </is>
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>195</t>
         </is>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>23</t>
+          <t>185</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>21</t>
+          <t>192</t>
         </is>
       </c>
       <c r="H86" t="inlineStr">
         <is>
-          <t>Triangular numbers.</t>
+          <t>Each term multiplied by 2</t>
         </is>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="n">
-        <v>22</v>
+        <v>2</v>
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>Find the missing letter: Z, W, S, N, ?</t>
+          <t>Find the missing number: 3, 9, 27, ?, 243</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>I</t>
+          <t>54</t>
         </is>
       </c>
       <c r="D87" t="inlineStr">
         <is>
-          <t>J</t>
+          <t>81</t>
         </is>
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>H</t>
+          <t>72</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>K</t>
+          <t>90</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>I</t>
+          <t>81</t>
         </is>
       </c>
       <c r="H87" t="inlineStr">
         <is>
-          <t>Decreasing by 3,4,5,6 letters.</t>
+          <t>Each term multiplied by 3; 27×3=81</t>
         </is>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>What comes next: ABC, BCD, CDE, DEF, ?</t>
+          <t>Find the missing letter: Z, X, U, Q, L, ?</t>
         </is>
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>EFG</t>
+          <t>F</t>
         </is>
       </c>
       <c r="D88" t="inlineStr">
         <is>
-          <t>FGH</t>
+          <t>G</t>
         </is>
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>GHI</t>
+          <t>H</t>
         </is>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>HIJ</t>
+          <t>I</t>
         </is>
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>EFG</t>
+          <t>F</t>
         </is>
       </c>
       <c r="H88" t="inlineStr">
         <is>
-          <t>Each triplet shifts by one letter forward.</t>
+          <t>Positions decrease by 2,3,4,5,6</t>
         </is>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>Find missing letter: F, K, P, U, ?</t>
+          <t>What comes next: MNO, PQR, STU, VWX, ?</t>
         </is>
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>Z</t>
+          <t>YZA</t>
         </is>
       </c>
       <c r="D89" t="inlineStr">
         <is>
-          <t>Y</t>
+          <t>BCD</t>
         </is>
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>CDE</t>
         </is>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>W</t>
+          <t>DEF</t>
         </is>
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>Z</t>
+          <t>YZA</t>
         </is>
       </c>
       <c r="H89" t="inlineStr">
         <is>
-          <t>Increments +5 each time</t>
+          <t>Triplets shift +4 letters cyclically.</t>
         </is>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="n">
-        <v>16</v>
+        <v>23</v>
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>Find missing term: 7, 14, 28, 56, 112, ?</t>
+          <t>Find next term: GH, KL, PQ, TU, ?</t>
         </is>
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>224</t>
+          <t>YZ</t>
         </is>
       </c>
       <c r="D90" t="inlineStr">
         <is>
-          <t>226</t>
+          <t>WX</t>
         </is>
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>230</t>
+          <t>UV</t>
         </is>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>220</t>
+          <t>QR</t>
         </is>
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>224</t>
+          <t>YZ</t>
         </is>
       </c>
       <c r="H90" t="inlineStr">
         <is>
-          <t>Each term ×2.</t>
+          <t>Pairs jump +4 letters.</t>
         </is>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="n">
-        <v>12</v>
+        <v>25</v>
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>Find missing letter: G, J, N, S, ?</t>
+          <t>What comes next? 10, 21, 43, 87, 175, ?</t>
         </is>
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>Y</t>
+          <t>351</t>
         </is>
       </c>
       <c r="D91" t="inlineStr">
         <is>
-          <t>Z</t>
+          <t>350</t>
         </is>
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>360</t>
         </is>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>W</t>
+          <t>355</t>
         </is>
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>Y</t>
+          <t>351</t>
         </is>
       </c>
       <c r="H91" t="inlineStr">
         <is>
-          <t>Difference: +3,+4,+5,+6</t>
+          <t>Each term roughly doubles plus 1</t>
         </is>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>What letter comes next? C, F, J, O, ?</t>
+          <t>What comes next? 121, 144, 169, 196, ?</t>
         </is>
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>U</t>
+          <t>225</t>
         </is>
       </c>
       <c r="D92" t="inlineStr">
         <is>
-          <t>T</t>
+          <t>240</t>
         </is>
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>S</t>
+          <t>256</t>
         </is>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>R</t>
+          <t>289</t>
         </is>
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>U</t>
+          <t>225</t>
         </is>
       </c>
       <c r="H92" t="inlineStr">
         <is>
-          <t>Difference in positions: +3,+4,+5,+6</t>
+          <t>Squares of 11,12,13,14,15</t>
         </is>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="n">
-        <v>24</v>
+        <v>3</v>
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>Find next letter: B, E, I, N, ?</t>
+          <t>Find missing number: 5, 10, 20, 40, 80, ?</t>
         </is>
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>T</t>
+          <t>160</t>
         </is>
       </c>
       <c r="D93" t="inlineStr">
         <is>
-          <t>U</t>
+          <t>150</t>
         </is>
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>S</t>
+          <t>140</t>
         </is>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>R</t>
+          <t>170</t>
         </is>
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>T</t>
+          <t>160</t>
         </is>
       </c>
       <c r="H93" t="inlineStr">
         <is>
-          <t>Differences +3,+4,+5,+6</t>
+          <t>Each term doubles</t>
         </is>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="n">
-        <v>7</v>
+        <v>11</v>
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>What comes next: ABC, DEF, GHI, JKL, ?</t>
+          <t>Find next number: 7, 14, 28, 56, ?</t>
         </is>
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>MNO</t>
+          <t>112</t>
         </is>
       </c>
       <c r="D94" t="inlineStr">
         <is>
-          <t>PQR</t>
+          <t>110</t>
         </is>
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>STU</t>
+          <t>114</t>
         </is>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>VWX</t>
+          <t>120</t>
         </is>
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>MNO</t>
+          <t>112</t>
         </is>
       </c>
       <c r="H94" t="inlineStr">
         <is>
-          <t>Triplets progress in alphabetical order.</t>
+          <t>Each term ×2</t>
         </is>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="n">
-        <v>14</v>
+        <v>20</v>
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>What comes next: ZYX, WVU, TSR, QPO, ?</t>
+          <t>Next in series: RST, UVW, XYZ, ABC, ?</t>
         </is>
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>NML</t>
+          <t>DEF</t>
         </is>
       </c>
       <c r="D95" t="inlineStr">
         <is>
-          <t>KJI</t>
+          <t>GHI</t>
         </is>
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>HGF</t>
+          <t>JKL</t>
         </is>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>EDC</t>
+          <t>MNO</t>
         </is>
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>NML</t>
+          <t>DEF</t>
         </is>
       </c>
       <c r="H95" t="inlineStr">
         <is>
-          <t>Triplets decrease by 3 letters.</t>
+          <t>Triplets shift +3 letters cyclically.</t>
         </is>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="n">
-        <v>18</v>
+        <v>21</v>
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>Find the missing number: 2, 6, 12, 20, 30, ?</t>
+          <t>Find the missing term: 5, 11, 23, 47, 95, ?</t>
         </is>
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>40</t>
+          <t>191</t>
         </is>
       </c>
       <c r="D96" t="inlineStr">
         <is>
-          <t>42</t>
+          <t>189</t>
         </is>
       </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t>44</t>
+          <t>193</t>
         </is>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>36</t>
+          <t>185</t>
         </is>
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>42</t>
+          <t>191</t>
         </is>
       </c>
       <c r="H96" t="inlineStr">
         <is>
-          <t>Using formula n(n+1).</t>
+          <t>Each term roughly doubles minus 1</t>
         </is>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="n">
-        <v>4</v>
+        <v>22</v>
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>What comes next? KL, NO, ST, WX, ?</t>
+          <t>What comes next? E, G, J, N, ?</t>
         </is>
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>BD</t>
+          <t>S</t>
         </is>
       </c>
       <c r="D97" t="inlineStr">
         <is>
-          <t>YZ</t>
+          <t>T</t>
         </is>
       </c>
       <c r="E97" t="inlineStr">
         <is>
-          <t>AB</t>
+          <t>R</t>
         </is>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>CD</t>
+          <t>Q</t>
         </is>
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>AB</t>
+          <t>S</t>
         </is>
       </c>
       <c r="H97" t="inlineStr">
         <is>
-          <t>Letters move in pairs skipping one letter; after WX comes AB.</t>
+          <t>Increments +2,+3,+4,+5</t>
         </is>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="n">
-        <v>23</v>
+        <v>16</v>
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>Find the next number: 17, 19, 23, 29, 31, ?</t>
+          <t>What letter comes next? P, M, J, G, ?</t>
         </is>
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>37</t>
+          <t>D</t>
         </is>
       </c>
       <c r="D98" t="inlineStr">
         <is>
-          <t>35</t>
+          <t>C</t>
         </is>
       </c>
       <c r="E98" t="inlineStr">
         <is>
-          <t>36</t>
+          <t>E</t>
         </is>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>38</t>
+          <t>F</t>
         </is>
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>37</t>
+          <t>D</t>
         </is>
       </c>
       <c r="H98" t="inlineStr">
         <is>
-          <t>Prime numbers</t>
+          <t>Decreasing by 3 positions each time</t>
         </is>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="n">
-        <v>8</v>
+        <v>2</v>
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>Next letter: B, D, G, K, P, ?</t>
+          <t>Find the missing number: 3, 9, 27, 81, ?</t>
         </is>
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>V</t>
+          <t>243</t>
         </is>
       </c>
       <c r="D99" t="inlineStr">
         <is>
-          <t>W</t>
+          <t>256</t>
         </is>
       </c>
       <c r="E99" t="inlineStr">
         <is>
-          <t>U</t>
+          <t>225</t>
         </is>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>T</t>
+          <t>270</t>
         </is>
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>V</t>
+          <t>243</t>
         </is>
       </c>
       <c r="H99" t="inlineStr">
         <is>
-          <t>Incrementing letter positions +2,+3,+4,+5,+6.</t>
+          <t>Each term multiplied by 3.</t>
         </is>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="n">
-        <v>23</v>
+        <v>6</v>
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>Find next term: GH, KL, PQ, TU, ?</t>
+          <t>Find missing number: 11, 21, 43, 87, 175, ?</t>
         </is>
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>YZ</t>
+          <t>351</t>
         </is>
       </c>
       <c r="D100" t="inlineStr">
         <is>
-          <t>WX</t>
+          <t>350</t>
         </is>
       </c>
       <c r="E100" t="inlineStr">
         <is>
-          <t>UV</t>
+          <t>352</t>
         </is>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>QR</t>
+          <t>355</t>
         </is>
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>YZ</t>
+          <t>351</t>
         </is>
       </c>
       <c r="H100" t="inlineStr">
         <is>
-          <t>Pairs jump +4 letters.</t>
+          <t>Each term doubles minus 1</t>
         </is>
       </c>
     </row>
     <row r="101">
       <c r="A101" t="n">
-        <v>3</v>
+        <v>13</v>
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>What comes next: 2, 6, 12, 20, 30, ?</t>
+          <t>What is the next term? 3, 6, 12, 24, 48, ?</t>
         </is>
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>42</t>
+          <t>96</t>
         </is>
       </c>
       <c r="D101" t="inlineStr">
         <is>
-          <t>40</t>
+          <t>90</t>
         </is>
       </c>
       <c r="E101" t="inlineStr">
         <is>
-          <t>44</t>
+          <t>100</t>
         </is>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>48</t>
+          <t>108</t>
         </is>
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t>42</t>
+          <t>96</t>
         </is>
       </c>
       <c r="H101" t="inlineStr">
         <is>
-          <t>Pattern n(n+1), next term 6×7=42.</t>
+          <t>Each term ×2</t>
         </is>
       </c>
     </row>
     <row r="102">
       <c r="A102" t="n">
-        <v>3</v>
+        <v>11</v>
       </c>
       <c r="B102" t="inlineStr">
         <is>
-          <t>Find missing number: 5, 10, 20, 40, 80, ?</t>
+          <t>What comes next: 3, 6, 12, 24, 48, ?</t>
         </is>
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>160</t>
+          <t>96</t>
         </is>
       </c>
       <c r="D102" t="inlineStr">
         <is>
-          <t>150</t>
+          <t>100</t>
         </is>
       </c>
       <c r="E102" t="inlineStr">
         <is>
-          <t>140</t>
+          <t>90</t>
         </is>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>170</t>
+          <t>98</t>
         </is>
       </c>
       <c r="G102" t="inlineStr">
         <is>
-          <t>160</t>
+          <t>96</t>
         </is>
       </c>
       <c r="H102" t="inlineStr">
         <is>
-          <t>Each term doubles</t>
+          <t>Each term multiplied by 2</t>
         </is>
       </c>
     </row>
     <row r="103">
       <c r="A103" t="n">
-        <v>21</v>
+        <v>13</v>
       </c>
       <c r="B103" t="inlineStr">
         <is>
-          <t>Find missing term: EF, IJ, MN, ST, ?</t>
+          <t>Next number: 7, 14, 28, 56, 112, ?</t>
         </is>
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>YZ</t>
+          <t>224</t>
         </is>
       </c>
       <c r="D103" t="inlineStr">
         <is>
-          <t>WX</t>
+          <t>225</t>
         </is>
       </c>
       <c r="E103" t="inlineStr">
         <is>
-          <t>UV</t>
+          <t>223</t>
         </is>
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>QR</t>
+          <t>220</t>
         </is>
       </c>
       <c r="G103" t="inlineStr">
         <is>
-          <t>YZ</t>
+          <t>224</t>
         </is>
       </c>
       <c r="H103" t="inlineStr">
         <is>
-          <t>Pairs jump +4 letters.</t>
+          <t>Each term multiplied by 2</t>
         </is>
       </c>
     </row>
     <row r="104">
       <c r="A104" t="n">
-        <v>20</v>
+        <v>6</v>
       </c>
       <c r="B104" t="inlineStr">
         <is>
-          <t>Find missing letter: D, G, K, P, ?</t>
+          <t>Find missing number: 2, 5, 10, 17, 26, ?</t>
         </is>
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>V</t>
+          <t>37</t>
         </is>
       </c>
       <c r="D104" t="inlineStr">
         <is>
-          <t>U</t>
+          <t>40</t>
         </is>
       </c>
       <c r="E104" t="inlineStr">
         <is>
-          <t>T</t>
+          <t>42</t>
         </is>
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>S</t>
+          <t>35</t>
         </is>
       </c>
       <c r="G104" t="inlineStr">
         <is>
-          <t>V</t>
+          <t>37</t>
         </is>
       </c>
       <c r="H104" t="inlineStr">
         <is>
-          <t>Increasing by 3,4,5,6 letters.</t>
+          <t>Add consecutive odd numbers +3,+5,+7,...</t>
         </is>
       </c>
     </row>
     <row r="105">
       <c r="A105" t="n">
-        <v>8</v>
+        <v>22</v>
       </c>
       <c r="B105" t="inlineStr">
         <is>
-          <t>What is next? 1, 4, 9, 16, 25, ?</t>
+          <t>Find the missing letter: Z, W, S, N, ?</t>
         </is>
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>36</t>
+          <t>I</t>
         </is>
       </c>
       <c r="D105" t="inlineStr">
         <is>
-          <t>49</t>
+          <t>J</t>
         </is>
       </c>
       <c r="E105" t="inlineStr">
         <is>
-          <t>30</t>
+          <t>H</t>
         </is>
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>42</t>
+          <t>K</t>
         </is>
       </c>
       <c r="G105" t="inlineStr">
         <is>
-          <t>36</t>
+          <t>I</t>
         </is>
       </c>
       <c r="H105" t="inlineStr">
         <is>
-          <t>Perfect squares</t>
+          <t>Decreasing by 3,4,5,6 letters.</t>
         </is>
       </c>
     </row>
     <row r="106">
       <c r="A106" t="n">
-        <v>8</v>
+        <v>25</v>
       </c>
       <c r="B106" t="inlineStr">
         <is>
-          <t>Find missing number: 1, 3, 7, 15, 31, ?</t>
+          <t>Find missing term: UV, YZ, DE, HI, ?</t>
         </is>
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>63</t>
+          <t>LM</t>
         </is>
       </c>
       <c r="D106" t="inlineStr">
         <is>
-          <t>64</t>
+          <t>OP</t>
         </is>
       </c>
       <c r="E106" t="inlineStr">
         <is>
-          <t>65</t>
+          <t>QR</t>
         </is>
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>62</t>
+          <t>ST</t>
         </is>
       </c>
       <c r="G106" t="inlineStr">
         <is>
-          <t>63</t>
+          <t>LM</t>
         </is>
       </c>
       <c r="H106" t="inlineStr">
         <is>
-          <t>Each term = previous ×2 +1</t>
+          <t>Pairs jump +4 letters cyclically.</t>
         </is>
       </c>
     </row>
     <row r="107">
       <c r="A107" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="B107" t="inlineStr">
         <is>
-          <t>Find next term: LM, OP, ST, WX, ?</t>
+          <t>What letter comes next? C, F, J, O, ?</t>
         </is>
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>AB</t>
+          <t>U</t>
         </is>
       </c>
       <c r="D107" t="inlineStr">
         <is>
-          <t>YZ</t>
+          <t>T</t>
         </is>
       </c>
       <c r="E107" t="inlineStr">
         <is>
-          <t>UV</t>
+          <t>S</t>
         </is>
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>YZ</t>
+          <t>R</t>
         </is>
       </c>
       <c r="G107" t="inlineStr">
         <is>
-          <t>AB</t>
+          <t>U</t>
         </is>
       </c>
       <c r="H107" t="inlineStr">
         <is>
-          <t>Pairs move +3 letters; after WX comes AB.</t>
+          <t>Difference in positions: +3,+4,+5,+6</t>
         </is>
       </c>
     </row>
     <row r="108">
       <c r="A108" t="n">
-        <v>5</v>
+        <v>11</v>
       </c>
       <c r="B108" t="inlineStr">
         <is>
-          <t>Find missing term: CDE, FGH, KLM, PQR, ?</t>
+          <t>Find next term: LM, OP, ST, WX, ?</t>
         </is>
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>VWX</t>
+          <t>AB</t>
         </is>
       </c>
       <c r="D108" t="inlineStr">
         <is>
-          <t>STU</t>
+          <t>YZ</t>
         </is>
       </c>
       <c r="E108" t="inlineStr">
         <is>
-          <t>XYZ</t>
+          <t>UV</t>
         </is>
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t>UVW</t>
+          <t>YZ</t>
         </is>
       </c>
       <c r="G108" t="inlineStr">
         <is>
-          <t>VWX</t>
+          <t>AB</t>
         </is>
       </c>
       <c r="H108" t="inlineStr">
         <is>
-          <t>Triplets jump by +3 letters each time.</t>
+          <t>Pairs move +3 letters; after WX comes AB.</t>
         </is>
       </c>
     </row>
     <row r="109">
       <c r="A109" t="n">
-        <v>25</v>
+        <v>20</v>
       </c>
       <c r="B109" t="inlineStr">
         <is>
-          <t>Next letter: A, C, F, J, O, ?</t>
+          <t>Find missing letter: D, G, K, P, ?</t>
         </is>
       </c>
       <c r="C109" t="inlineStr">
         <is>
+          <t>V</t>
+        </is>
+      </c>
+      <c r="D109" t="inlineStr">
+        <is>
           <t>U</t>
         </is>
       </c>
-      <c r="D109" t="inlineStr">
+      <c r="E109" t="inlineStr">
         <is>
           <t>T</t>
         </is>
       </c>
-      <c r="E109" t="inlineStr">
+      <c r="F109" t="inlineStr">
         <is>
           <t>S</t>
         </is>
       </c>
-      <c r="F109" t="inlineStr">
+      <c r="G109" t="inlineStr">
         <is>
           <t>V</t>
         </is>
       </c>
-      <c r="G109" t="inlineStr">
-        <is>
-          <t>U</t>
-        </is>
-      </c>
       <c r="H109" t="inlineStr">
         <is>
-          <t>Incrementing by increasing letters.</t>
+          <t>Increasing by 3,4,5,6 letters.</t>
         </is>
       </c>
     </row>
     <row r="110">
       <c r="A110" t="n">
-        <v>2</v>
+        <v>12</v>
       </c>
       <c r="B110" t="inlineStr">
         <is>
-          <t>Find the missing letter: Z, X, U, Q, L, ?</t>
+          <t>Find missing number: 6, 11, 21, 36, 56, ?</t>
         </is>
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t>F</t>
+          <t>81</t>
         </is>
       </c>
       <c r="D110" t="inlineStr">
         <is>
-          <t>G</t>
+          <t>80</t>
         </is>
       </c>
       <c r="E110" t="inlineStr">
         <is>
-          <t>E</t>
+          <t>85</t>
         </is>
       </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t>H</t>
+          <t>75</t>
         </is>
       </c>
       <c r="G110" t="inlineStr">
         <is>
-          <t>F</t>
+          <t>81</t>
         </is>
       </c>
       <c r="H110" t="inlineStr">
         <is>
-          <t>Positions decrease by 2,3,4,5,6</t>
+          <t>Add increasing numbers +5,+10,+15,...</t>
         </is>
       </c>
     </row>
     <row r="111">
       <c r="A111" t="n">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="B111" t="inlineStr">
         <is>
-          <t>Next in series: ABC, EFG, IJK, MNO, ?</t>
+          <t>Find missing term: CD, GH, LM, ST, ?</t>
         </is>
       </c>
       <c r="C111" t="inlineStr">
         <is>
-          <t>QRS</t>
+          <t>YZ</t>
         </is>
       </c>
       <c r="D111" t="inlineStr">
         <is>
-          <t>TUV</t>
+          <t>WX</t>
         </is>
       </c>
       <c r="E111" t="inlineStr">
         <is>
-          <t>WXY</t>
+          <t>UV</t>
         </is>
       </c>
       <c r="F111" t="inlineStr">
         <is>
-          <t>ZAB</t>
+          <t>QR</t>
         </is>
       </c>
       <c r="G111" t="inlineStr">
         <is>
-          <t>QRS</t>
+          <t>YZ</t>
         </is>
       </c>
       <c r="H111" t="inlineStr">
         <is>
-          <t>Triplets jump +4 letters each time.</t>
+          <t>Pairs jump +4 letters each time.</t>
         </is>
       </c>
     </row>
     <row r="112">
       <c r="A112" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="B112" t="inlineStr">
         <is>
-          <t>Find the next term: PQ, RS, TU, WX, ?</t>
+          <t>Next in series: AZ, CY, EX, GV, ?</t>
         </is>
       </c>
       <c r="C112" t="inlineStr">
         <is>
-          <t>YZ</t>
+          <t>IT</t>
         </is>
       </c>
       <c r="D112" t="inlineStr">
         <is>
-          <t>ZA</t>
+          <t>HS</t>
         </is>
       </c>
       <c r="E112" t="inlineStr">
         <is>
-          <t>AB</t>
+          <t>JU</t>
         </is>
       </c>
       <c r="F112" t="inlineStr">
         <is>
-          <t>BC</t>
+          <t>KT</t>
         </is>
       </c>
       <c r="G112" t="inlineStr">
         <is>
-          <t>YZ</t>
+          <t>IT</t>
         </is>
       </c>
       <c r="H112" t="inlineStr">
         <is>
-          <t>Pairs move sequentially in alphabets; after WX is YZ.</t>
+          <t>First letters move +2, second letters -2; IT follows pattern.</t>
         </is>
       </c>
     </row>
     <row r="113">
       <c r="A113" t="n">
-        <v>17</v>
+        <v>23</v>
       </c>
       <c r="B113" t="inlineStr">
         <is>
-          <t>Find missing term: JK, NO, RS, VW, ?</t>
+          <t>Find the next number: 17, 19, 23, 29, 31, ?</t>
         </is>
       </c>
       <c r="C113" t="inlineStr">
         <is>
-          <t>BC</t>
+          <t>37</t>
         </is>
       </c>
       <c r="D113" t="inlineStr">
         <is>
-          <t>YZ</t>
+          <t>35</t>
         </is>
       </c>
       <c r="E113" t="inlineStr">
         <is>
-          <t>XY</t>
+          <t>36</t>
         </is>
       </c>
       <c r="F113" t="inlineStr">
         <is>
-          <t>ZA</t>
+          <t>38</t>
         </is>
       </c>
       <c r="G113" t="inlineStr">
         <is>
-          <t>BC</t>
+          <t>37</t>
         </is>
       </c>
       <c r="H113" t="inlineStr">
         <is>
-          <t>Pairs jump +4 letters.</t>
+          <t>Prime numbers</t>
         </is>
       </c>
     </row>
     <row r="114">
       <c r="A114" t="n">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="B114" t="inlineStr">
         <is>
-          <t>Next in series: RST, UVW, XYZ, ABC, ?</t>
+          <t>What comes next: 13, 21, 34, 55, 89, ?</t>
         </is>
       </c>
       <c r="C114" t="inlineStr">
         <is>
-          <t>DEF</t>
+          <t>144</t>
         </is>
       </c>
       <c r="D114" t="inlineStr">
         <is>
-          <t>GHI</t>
+          <t>135</t>
         </is>
       </c>
       <c r="E114" t="inlineStr">
         <is>
-          <t>JKL</t>
+          <t>140</t>
         </is>
       </c>
       <c r="F114" t="inlineStr">
         <is>
-          <t>MNO</t>
+          <t>150</t>
         </is>
       </c>
       <c r="G114" t="inlineStr">
         <is>
-          <t>DEF</t>
+          <t>144</t>
         </is>
       </c>
       <c r="H114" t="inlineStr">
         <is>
-          <t>Triplets shift +3 letters cyclically.</t>
+          <t>Fibonacci sequence</t>
         </is>
       </c>
     </row>
     <row r="115">
       <c r="A115" t="n">
-        <v>8</v>
+        <v>16</v>
       </c>
       <c r="B115" t="inlineStr">
         <is>
-          <t>Find missing term: FG, IJ, MN, QR, ?</t>
+          <t>Next in series: ABC, EFG, IJK, MNO, ?</t>
         </is>
       </c>
       <c r="C115" t="inlineStr">
         <is>
-          <t>UV</t>
+          <t>QRS</t>
         </is>
       </c>
       <c r="D115" t="inlineStr">
         <is>
-          <t>ST</t>
+          <t>TUV</t>
         </is>
       </c>
       <c r="E115" t="inlineStr">
         <is>
-          <t>WX</t>
+          <t>WXY</t>
         </is>
       </c>
       <c r="F115" t="inlineStr">
         <is>
-          <t>YZ</t>
+          <t>ZAB</t>
         </is>
       </c>
       <c r="G115" t="inlineStr">
         <is>
-          <t>UV</t>
+          <t>QRS</t>
         </is>
       </c>
       <c r="H115" t="inlineStr">
         <is>
-          <t>Pairs jump +4 letters each time.</t>
+          <t>Triplets jump +4 letters each time.</t>
         </is>
       </c>
     </row>
     <row r="116">
       <c r="A116" t="n">
-        <v>11</v>
+        <v>17</v>
       </c>
       <c r="B116" t="inlineStr">
         <is>
-          <t>What comes next: 3, 6, 12, 24, 48, ?</t>
+          <t>Next letter: F, K, P, U, ?</t>
         </is>
       </c>
       <c r="C116" t="inlineStr">
         <is>
-          <t>96</t>
+          <t>Z</t>
         </is>
       </c>
       <c r="D116" t="inlineStr">
         <is>
-          <t>90</t>
+          <t>Y</t>
         </is>
       </c>
       <c r="E116" t="inlineStr">
         <is>
-          <t>100</t>
+          <t>X</t>
         </is>
       </c>
       <c r="F116" t="inlineStr">
         <is>
-          <t>110</t>
+          <t>W</t>
         </is>
       </c>
       <c r="G116" t="inlineStr">
         <is>
-          <t>96</t>
+          <t>Z</t>
         </is>
       </c>
       <c r="H116" t="inlineStr">
         <is>
-          <t>Each term doubles</t>
+          <t>Increasing by 5 letters each time.</t>
         </is>
       </c>
     </row>
     <row r="117">
       <c r="A117" t="n">
-        <v>15</v>
+        <v>5</v>
       </c>
       <c r="B117" t="inlineStr">
         <is>
-          <t>What comes next: 2, 6, 18, 54, 162, ?</t>
+          <t>Find the next number: 1, 8, 27, 64, ?</t>
         </is>
       </c>
       <c r="C117" t="inlineStr">
         <is>
-          <t>486</t>
+          <t>125</t>
         </is>
       </c>
       <c r="D117" t="inlineStr">
         <is>
-          <t>500</t>
+          <t>130</t>
         </is>
       </c>
       <c r="E117" t="inlineStr">
         <is>
-          <t>490</t>
+          <t>120</t>
         </is>
       </c>
       <c r="F117" t="inlineStr">
         <is>
-          <t>480</t>
+          <t>135</t>
         </is>
       </c>
       <c r="G117" t="inlineStr">
         <is>
-          <t>486</t>
+          <t>125</t>
         </is>
       </c>
       <c r="H117" t="inlineStr">
         <is>
-          <t>Each term ×3</t>
+          <t>Cubes of 1,2,3,4,5.</t>
         </is>
       </c>
     </row>
     <row r="118">
       <c r="A118" t="n">
-        <v>17</v>
+        <v>24</v>
       </c>
       <c r="B118" t="inlineStr">
         <is>
-          <t>What comes next: 1, 8, 27, 64, 125, ?</t>
+          <t>Find next letter: B, E, I, N, ?</t>
         </is>
       </c>
       <c r="C118" t="inlineStr">
         <is>
-          <t>216</t>
+          <t>T</t>
         </is>
       </c>
       <c r="D118" t="inlineStr">
         <is>
-          <t>225</t>
+          <t>U</t>
         </is>
       </c>
       <c r="E118" t="inlineStr">
         <is>
-          <t>210</t>
+          <t>S</t>
         </is>
       </c>
       <c r="F118" t="inlineStr">
         <is>
-          <t>230</t>
+          <t>R</t>
         </is>
       </c>
       <c r="G118" t="inlineStr">
         <is>
-          <t>216</t>
+          <t>T</t>
         </is>
       </c>
       <c r="H118" t="inlineStr">
         <is>
-          <t>Cubes of natural numbers</t>
+          <t>Differences +3,+4,+5,+6</t>
         </is>
       </c>
     </row>
     <row r="119">
       <c r="A119" t="n">
-        <v>14</v>
+        <v>9</v>
       </c>
       <c r="B119" t="inlineStr">
         <is>
-          <t>Find next letter: D, G, K, P, ?</t>
+          <t>What comes next: 13, 21, 34, 55, 89, ?</t>
         </is>
       </c>
       <c r="C119" t="inlineStr">
         <is>
-          <t>V</t>
+          <t>144</t>
         </is>
       </c>
       <c r="D119" t="inlineStr">
         <is>
-          <t>W</t>
+          <t>135</t>
         </is>
       </c>
       <c r="E119" t="inlineStr">
         <is>
-          <t>U</t>
+          <t>150</t>
         </is>
       </c>
       <c r="F119" t="inlineStr">
         <is>
-          <t>T</t>
+          <t>140</t>
         </is>
       </c>
       <c r="G119" t="inlineStr">
         <is>
-          <t>V</t>
+          <t>144</t>
         </is>
       </c>
       <c r="H119" t="inlineStr">
         <is>
-          <t>Increments +3, +4, +5, +6</t>
+          <t>Fibonacci series.</t>
         </is>
       </c>
     </row>
     <row r="120">
       <c r="A120" t="n">
-        <v>22</v>
+        <v>3</v>
       </c>
       <c r="B120" t="inlineStr">
         <is>
-          <t>What comes next? E, G, J, N, ?</t>
+          <t>What comes next: 2, 6, 12, 20, 30, ?</t>
         </is>
       </c>
       <c r="C120" t="inlineStr">
         <is>
-          <t>S</t>
+          <t>42</t>
         </is>
       </c>
       <c r="D120" t="inlineStr">
         <is>
-          <t>T</t>
+          <t>40</t>
         </is>
       </c>
       <c r="E120" t="inlineStr">
         <is>
-          <t>R</t>
+          <t>44</t>
         </is>
       </c>
       <c r="F120" t="inlineStr">
         <is>
-          <t>Q</t>
+          <t>48</t>
         </is>
       </c>
       <c r="G120" t="inlineStr">
         <is>
-          <t>S</t>
+          <t>42</t>
         </is>
       </c>
       <c r="H120" t="inlineStr">
         <is>
-          <t>Increments +2,+3,+4,+5</t>
+          <t>Pattern n(n+1), next term 6×7=42.</t>
         </is>
       </c>
     </row>
     <row r="121">
       <c r="A121" t="n">
-        <v>24</v>
+        <v>2</v>
       </c>
       <c r="B121" t="inlineStr">
         <is>
-          <t>Find next letter: Y, V, R, M, ?</t>
+          <t>Find the missing term: XYZ, UVW, RST, OPQ, ?</t>
         </is>
       </c>
       <c r="C121" t="inlineStr">
         <is>
-          <t>H</t>
+          <t>LMN</t>
         </is>
       </c>
       <c r="D121" t="inlineStr">
         <is>
-          <t>I</t>
+          <t>NOP</t>
         </is>
       </c>
       <c r="E121" t="inlineStr">
         <is>
-          <t>J</t>
+          <t>KLM</t>
         </is>
       </c>
       <c r="F121" t="inlineStr">
         <is>
-          <t>G</t>
+          <t>JKL</t>
         </is>
       </c>
       <c r="G121" t="inlineStr">
         <is>
-          <t>H</t>
+          <t>LMN</t>
         </is>
       </c>
       <c r="H121" t="inlineStr">
         <is>
-          <t>Decreases by 3,4,5,6 letters</t>
+          <t>Each triple moves backward by 3 letters.</t>
         </is>
       </c>
     </row>
     <row r="122">
       <c r="A122" t="n">
-        <v>5</v>
+        <v>25</v>
       </c>
       <c r="B122" t="inlineStr">
         <is>
-          <t>Find the next term: 7, 14, 28, 56, 112, ?</t>
+          <t>What comes next: 8, 27, 64, 125, ?</t>
         </is>
       </c>
       <c r="C122" t="inlineStr">
         <is>
-          <t>224</t>
+          <t>216</t>
         </is>
       </c>
       <c r="D122" t="inlineStr">
         <is>
+          <t>225</t>
+        </is>
+      </c>
+      <c r="E122" t="inlineStr">
+        <is>
+          <t>220</t>
+        </is>
+      </c>
+      <c r="F122" t="inlineStr">
+        <is>
           <t>230</t>
         </is>
       </c>
-      <c r="E122" t="inlineStr">
-        <is>
-          <t>220</t>
-        </is>
-      </c>
-      <c r="F122" t="inlineStr">
-        <is>
-          <t>210</t>
-        </is>
-      </c>
       <c r="G122" t="inlineStr">
         <is>
-          <t>224</t>
+          <t>216</t>
         </is>
       </c>
       <c r="H122" t="inlineStr">
         <is>
-          <t>Each term ×2</t>
+          <t>Cubes of 2,3,4,5,6</t>
         </is>
       </c>
     </row>
     <row r="123">
       <c r="A123" t="n">
-        <v>15</v>
+        <v>1</v>
       </c>
       <c r="B123" t="inlineStr">
         <is>
-          <t>Find next term: BC, DE, GH, KL, ?</t>
+          <t>Find the next number: 7, 14, 28, 56, ?</t>
         </is>
       </c>
       <c r="C123" t="inlineStr">
         <is>
-          <t>OP</t>
+          <t>110</t>
         </is>
       </c>
       <c r="D123" t="inlineStr">
         <is>
-          <t>MN</t>
+          <t>112</t>
         </is>
       </c>
       <c r="E123" t="inlineStr">
         <is>
-          <t>QR</t>
+          <t>120</t>
         </is>
       </c>
       <c r="F123" t="inlineStr">
         <is>
-          <t>ST</t>
+          <t>114</t>
         </is>
       </c>
       <c r="G123" t="inlineStr">
         <is>
-          <t>OP</t>
+          <t>112</t>
         </is>
       </c>
       <c r="H123" t="inlineStr">
         <is>
-          <t>Pairs jump increasing letters.</t>
+          <t>Each term is multiplied by 2.</t>
         </is>
       </c>
     </row>
     <row r="124">
       <c r="A124" t="n">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="B124" t="inlineStr">
         <is>
-          <t>Find the next number: 21, 34, 55, 89, 144, ?</t>
+          <t>Next in series: 1, 2, 6, 24, 120, ?</t>
         </is>
       </c>
       <c r="C124" t="inlineStr">
         <is>
-          <t>233</t>
+          <t>720</t>
         </is>
       </c>
       <c r="D124" t="inlineStr">
         <is>
-          <t>220</t>
+          <t>600</t>
         </is>
       </c>
       <c r="E124" t="inlineStr">
         <is>
-          <t>240</t>
+          <t>7200</t>
         </is>
       </c>
       <c r="F124" t="inlineStr">
         <is>
-          <t>200</t>
+          <t>360</t>
         </is>
       </c>
       <c r="G124" t="inlineStr">
         <is>
-          <t>233</t>
+          <t>720</t>
         </is>
       </c>
       <c r="H124" t="inlineStr">
         <is>
-          <t>Fibonacci sequence</t>
+          <t>Factorials: 1!,2!,3!,4!,5!,6!</t>
         </is>
       </c>
     </row>

--- a/Data/numberalphabet.xlsx
+++ b/Data/numberalphabet.xlsx
@@ -472,801 +472,801 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>15</v>
+        <v>25</v>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>What comes next: 1, 2, 6, 24, 120, ?</t>
+          <t>What comes next? 10, 21, 43, 87, 175, ?</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>720</t>
+          <t>351</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>600</t>
+          <t>350</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>7200</t>
+          <t>360</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>700</t>
+          <t>355</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>720</t>
+          <t>351</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>Factorials 1!, 2!, 3!, 4!, 5!, 6!</t>
+          <t>Each term roughly doubles plus 1</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Find the missing letter: A, C, F, J, O, ?</t>
+          <t>Next in series: ZX, VT, RP, NL, ?</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>U</t>
+          <t>JH</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>T</t>
+          <t>KF</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>S</t>
+          <t>JG</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>V</t>
+          <t>KH</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>U</t>
+          <t>JH</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>Alphabet position increments +2,+3,+4,+5,+6.</t>
+          <t>Pairs move backward skipping one letter.</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>2</v>
+        <v>21</v>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>What comes next: 3, 8, 15, 24, 35, ?</t>
+          <t>Find the missing term: 5, 11, 23, 47, 95, ?</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>48</t>
+          <t>191</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>49</t>
+          <t>189</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>50</t>
+          <t>193</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>55</t>
+          <t>185</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>48</t>
+          <t>191</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>Each term = n² + n, n=1,2,3,...</t>
+          <t>Each term roughly doubles minus 1</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>7</v>
+        <v>24</v>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>What comes next: 4, 9, 16, 25, 36, ?</t>
+          <t>Find next letter: Y, V, R, M, ?</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>49</t>
+          <t>H</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>48</t>
+          <t>I</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>50</t>
+          <t>J</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>51</t>
+          <t>G</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>49</t>
+          <t>H</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>Perfect squares</t>
+          <t>Decreases by 3,4,5,6 letters</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>3</v>
+        <v>21</v>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>What comes next: 4, 9, 19, 39, 79, ?</t>
+          <t>Find missing term: EF, IJ, MN, ST, ?</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>159</t>
+          <t>YZ</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>149</t>
+          <t>WX</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>169</t>
+          <t>UV</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>179</t>
+          <t>QR</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>159</t>
+          <t>YZ</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>Each term nearly doubles minus 1</t>
+          <t>Pairs jump +4 letters.</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Find missing letter: G, J, N, S, ?</t>
+          <t>What comes next: 3, 6, 12, 24, 48, ?</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Y</t>
+          <t>96</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>Z</t>
+          <t>100</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>90</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>W</t>
+          <t>98</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Y</t>
+          <t>96</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>Difference: +3,+4,+5,+6</t>
+          <t>Each term multiplied by 2</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Next number in series: 2, 6, 18, 54, ?</t>
+          <t>What comes next: UVW, XYZ, ABC, DEF, ?</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>162</t>
+          <t>GHI</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>150</t>
+          <t>JKL</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>180</t>
+          <t>MNO</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>170</t>
+          <t>PQR</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>162</t>
+          <t>GHI</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>Each term ×3</t>
+          <t>Triplets shift +3 letters cyclically.</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>7</v>
+        <v>11</v>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Find the missing term: 2, 3, 5, 9, 17, ?</t>
+          <t>Find next term: LM, OP, ST, WX, ?</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>33</t>
+          <t>AB</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>31</t>
+          <t>YZ</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>34</t>
+          <t>UV</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>30</t>
+          <t>YZ</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>33</t>
+          <t>AB</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>Each term after 2 is previous term ×2 -1.</t>
+          <t>Pairs move +3 letters; after WX comes AB.</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>25</v>
+        <v>7</v>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>What comes next: 6, 24, 60, 120, 210, ?</t>
+          <t>What comes next: ABC, DEF, GHI, JKL, ?</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>336</t>
+          <t>MNO</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>350</t>
+          <t>PQR</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>340</t>
+          <t>STU</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>320</t>
+          <t>VWX</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>336</t>
+          <t>MNO</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>Pattern n(n+1)(n+2)/6 for n=2,3,4,5,6,7</t>
+          <t>Triplets progress in alphabetical order.</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>8</v>
+        <v>25</v>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>What comes next: 5, 15, 45, 135, ?</t>
+          <t>Find missing term: UV, YZ, DE, HI, ?</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>405</t>
+          <t>LM</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>400</t>
+          <t>OP</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>410</t>
+          <t>QR</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>420</t>
+          <t>ST</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>405</t>
+          <t>LM</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>Multiplied by 3</t>
+          <t>Pairs jump +4 letters cyclically.</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Find the next letter: D, H, M, S, ?</t>
+          <t>Find missing letter: D, G, K, P, ?</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Z</t>
+          <t>V</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>Y</t>
+          <t>U</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>T</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>W</t>
+          <t>S</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Z</t>
+          <t>V</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>Increments +4, +5, +6, +7</t>
+          <t>Increasing by 3,4,5,6 letters.</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>8</v>
+        <v>14</v>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Find missing term: FG, IJ, MN, QR, ?</t>
+          <t>Find the missing letter: Z, W, S, N, ?</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>UV</t>
+          <t>I</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>ST</t>
+          <t>H</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>WX</t>
+          <t>J</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>YZ</t>
+          <t>K</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>UV</t>
+          <t>I</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>Pairs jump +4 letters each time.</t>
+          <t>Decreasing by 3,4,5,6 letters</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>24</v>
+        <v>16</v>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Find the missing number: 4, 12, 36, 108, ?</t>
+          <t>Find next letter: C, F, J, O, ?</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>324</t>
+          <t>U</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>300</t>
+          <t>V</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>350</t>
+          <t>W</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>320</t>
+          <t>X</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>324</t>
+          <t>U</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>Each term ×3</t>
+          <t>Increments +3, +4, +5, +6</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>22</v>
+        <v>2</v>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Find missing number: 9, 19, 39, 79, 159, ?</t>
+          <t>Find the missing number: 3, 9, 27, 81, ?</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>319</t>
+          <t>243</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>310</t>
+          <t>256</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>320</t>
+          <t>225</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>300</t>
+          <t>270</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>319</t>
+          <t>243</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>Each term doubles minus 1</t>
+          <t>Each term multiplied by 3.</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Find missing letter: G, K, P, V, ?</t>
+          <t>Find next number: 4, 9, 19, 39, 79, ?</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>159</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>149</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>169</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Z</t>
+          <t>179</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>159</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>Increments +4, +5, +6, +7</t>
+          <t>Each term roughly doubles minus 1</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>17</v>
+        <v>10</v>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Find next term: 1, 3, 6, 10, 15, ?</t>
+          <t>Find missing number: 4, 9, 19, 39, 79, ?</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>21</t>
+          <t>159</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>22</t>
+          <t>169</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>149</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>23</t>
+          <t>179</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>21</t>
+          <t>159</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>Triangular numbers</t>
+          <t>Each term approximately doubles minus 1.</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>18</v>
+        <v>10</v>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Find missing term: 8, 27, 64, 125, 216, ?</t>
+          <t>What letter comes next? C, F, J, O, ?</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>343</t>
+          <t>U</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>350</t>
+          <t>T</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>330</t>
+          <t>S</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>300</t>
+          <t>R</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>343</t>
+          <t>U</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>Cubes</t>
+          <t>Difference in positions: +3,+4,+5,+6</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>16</v>
+        <v>3</v>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Find missing term: 7, 14, 28, 56, 112, ?</t>
+          <t>What comes next: 2, 6, 12, 20, 30, ?</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>224</t>
+          <t>42</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>226</t>
+          <t>40</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>230</t>
+          <t>44</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>220</t>
+          <t>48</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>224</t>
+          <t>42</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>Each term ×2.</t>
+          <t>Pattern n(n+1), next term 6×7=42.</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>19</v>
+        <v>13</v>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>What comes next: 8, 27, 64, 125, ?</t>
+          <t>Find missing term: CD, GH, LM, ST, ?</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>216</t>
+          <t>YZ</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>225</t>
+          <t>WX</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>200</t>
+          <t>UV</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>230</t>
+          <t>QR</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>216</t>
+          <t>YZ</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>Cubes of 2,3,4,5,6.</t>
+          <t>Pairs jump +4 letters each time.</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>11</v>
+        <v>24</v>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Find next term: 1, 3, 6, 10, 15, ?</t>
+          <t>Next in series: ABC, DEF, GHI, JKL, ?</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>21</t>
+          <t>MNO</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>22</t>
+          <t>PQR</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>STU</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>23</t>
+          <t>VWX</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>21</t>
+          <t>MNO</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>Triangular numbers.</t>
+          <t>Triplets progress alphabetically.</t>
         </is>
       </c>
     </row>
@@ -1276,607 +1276,607 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Find the next number: 21, 34, 55, 89, 144, ?</t>
+          <t>What comes next: ABC, BCD, CDE, DEF, ?</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>233</t>
+          <t>EFG</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>220</t>
+          <t>FGH</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>240</t>
+          <t>GHI</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>200</t>
+          <t>HIJ</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>233</t>
+          <t>EFG</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>Fibonacci sequence</t>
+          <t>Each triplet shifts by one letter forward.</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>17</v>
+        <v>9</v>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>Find missing number: 3, 9, 27, 81, ?</t>
+          <t>Next in series: 11, 13, 17, 19, 23, ?</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>243</t>
+          <t>29</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>250</t>
+          <t>31</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>240</t>
+          <t>28</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>245</t>
+          <t>27</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>243</t>
+          <t>29</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>Multiplied by 3</t>
+          <t>Prime numbers in order</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>1</v>
+        <v>15</v>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>Find the next number: 2, 12, 36, 80, 150, ?</t>
+          <t>What comes next: 2, 6, 18, 54, 162, ?</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>252</t>
+          <t>486</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>200</t>
+          <t>500</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>240</t>
+          <t>490</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>300</t>
+          <t>480</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>252</t>
+          <t>486</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>Pattern: n³ - n, for n=2,3,4,5,6 → 6³-6=216-6=210 (adjusted here as 252)</t>
+          <t>Each term ×3</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>Find next term: BC, DE, GH, KL, ?</t>
+          <t>Find missing number: 6, 11, 21, 36, 56, ?</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>OP</t>
+          <t>81</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>MN</t>
+          <t>80</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>QR</t>
+          <t>85</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>ST</t>
+          <t>75</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>OP</t>
+          <t>81</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>Pairs jump increasing letters.</t>
+          <t>Add increasing numbers +5,+10,+15,...</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>5</v>
+        <v>22</v>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>Next letter: A, D, H, M, S, ?</t>
+          <t>What comes next? E, G, J, N, ?</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Z</t>
+          <t>S</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>Y</t>
+          <t>T</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>R</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>W</t>
+          <t>Q</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Z</t>
+          <t>S</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>Increments +3, +4, +5, +6, +7</t>
+          <t>Increments +2,+3,+4,+5</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>9</v>
+        <v>17</v>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>Find missing number: 2, 4, 8, 14, 22, ?</t>
+          <t>Next letter: F, K, P, U, ?</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>32</t>
+          <t>Z</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>30</t>
+          <t>Y</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>34</t>
+          <t>X</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>36</t>
+          <t>W</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>32</t>
+          <t>Z</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>Incrementing differences: +2, +4, +6, +8, next +10=32</t>
+          <t>Increasing by 5 letters each time.</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>Find next letter: C, F, J, O, ?</t>
+          <t>Next number: 5, 10, 20, 40, 80, ?</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>U</t>
+          <t>160</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>V</t>
+          <t>180</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>W</t>
+          <t>150</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>140</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>U</t>
+          <t>160</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>Increments +3, +4, +5, +6</t>
+          <t>Each term ×2.</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>21</v>
+        <v>2</v>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>Find missing letter: F, K, P, U, ?</t>
+          <t>What comes next: 3, 8, 15, 24, 35, ?</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Z</t>
+          <t>48</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>Y</t>
+          <t>49</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>50</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>W</t>
+          <t>55</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Z</t>
+          <t>48</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>Increments +5 each time</t>
+          <t>Each term = n² + n, n=1,2,3,...</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>Find missing term: CDE, FGH, KLM, PQR, ?</t>
+          <t>Find missing number: 1, 3, 7, 15, 31, ?</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>VWX</t>
+          <t>63</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>STU</t>
+          <t>64</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>XYZ</t>
+          <t>65</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>UVW</t>
+          <t>62</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>VWX</t>
+          <t>63</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>Triplets jump by +3 letters each time.</t>
+          <t>Each term = previous ×2 +1</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>6</v>
+        <v>15</v>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>Find next number: 5, 10, 20, 40, 80, ?</t>
+          <t>What comes next: 1, 2, 6, 24, 120, ?</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>160</t>
+          <t>720</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>180</t>
+          <t>600</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>150</t>
+          <t>7200</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>200</t>
+          <t>700</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>160</t>
+          <t>720</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>Each term ×2</t>
+          <t>Factorials 1!, 2!, 3!, 4!, 5!, 6!</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>21</v>
+        <v>6</v>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>Next number: 3, 9, 27, 81, ?</t>
+          <t>Find the next term: PQ, RS, TU, WX, ?</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>243</t>
+          <t>YZ</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>256</t>
+          <t>ZA</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>225</t>
+          <t>AB</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>270</t>
+          <t>BC</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>243</t>
+          <t>YZ</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>Multiplying by 3.</t>
+          <t>Pairs move sequentially in alphabets; after WX is YZ.</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>25</v>
+        <v>11</v>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>Next letter: A, C, F, J, O, ?</t>
+          <t>Find next number: 7, 14, 28, 56, ?</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>U</t>
+          <t>112</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>T</t>
+          <t>110</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>S</t>
+          <t>114</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>V</t>
+          <t>120</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>U</t>
+          <t>112</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>Incrementing by increasing letters.</t>
+          <t>Each term ×2</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>Find the missing letter: Z, X, U, Q, L, ?</t>
+          <t>Next letter: A, D, H, M, S, ?</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>F</t>
+          <t>Z</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>G</t>
+          <t>Y</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>E</t>
+          <t>X</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>H</t>
+          <t>W</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>F</t>
+          <t>Z</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>Positions decrease by 2,3,4,5,6</t>
+          <t>Increments +3, +4, +5, +6, +7</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>Next number: 1, 4, 9, 16, 25, ?</t>
+          <t>Find the next term: 2, 3, 5, 8, 12, 17, ?</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>36</t>
+          <t>23</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>49</t>
+          <t>25</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>30</t>
+          <t>24</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>42</t>
+          <t>26</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>36</t>
+          <t>23</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>Squares of natural numbers</t>
+          <t>Difference increases by 1: +1,+2,+3,+4,+5</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>Find the next number: 2, 5, 10, 17, 26, ?</t>
+          <t>What comes next: 4, 9, 19, 39, 79, ?</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>35</t>
+          <t>159</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>37</t>
+          <t>149</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>38</t>
+          <t>169</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>40</t>
+          <t>179</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>37</t>
+          <t>159</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>Each term increases by consecutive odd numbers: +3, +5, +7, +9, next +11=37</t>
+          <t>Each term nearly doubles minus 1</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>14</v>
+        <v>8</v>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>Find next letter: D, G, K, P, ?</t>
+          <t>Next letter: B, D, G, K, P, ?</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
@@ -1906,1007 +1906,1007 @@
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>Increments +3, +4, +5, +6</t>
+          <t>Incrementing letter positions +2,+3,+4,+5,+6.</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>6</v>
+        <v>14</v>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>What comes next: Z, X, U, Q, L, ?</t>
+          <t>What comes next: ZYX, WVU, TSR, QPO, ?</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>F</t>
+          <t>NML</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>G</t>
+          <t>KJI</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>H</t>
+          <t>HGF</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>I</t>
+          <t>EDC</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>F</t>
+          <t>NML</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>Alphabet positions decrease by 2,3,4,5,6.</t>
+          <t>Triplets decrease by 3 letters.</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>8</v>
+        <v>25</v>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>Find missing number: 1, 3, 7, 15, 31, ?</t>
+          <t>What comes next: 8, 27, 64, 125, ?</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>63</t>
+          <t>216</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>64</t>
+          <t>225</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>65</t>
+          <t>220</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>62</t>
+          <t>230</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>63</t>
+          <t>216</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>Each term = previous ×2 +1</t>
+          <t>Cubes of 2,3,4,5,6</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>6</v>
+        <v>19</v>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>Find the next term: PQ, RS, TU, WX, ?</t>
+          <t>Find the next term: DE, GH, KL, OP, ?</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
+          <t>ST</t>
+        </is>
+      </c>
+      <c r="D40" t="inlineStr">
+        <is>
+          <t>UV</t>
+        </is>
+      </c>
+      <c r="E40" t="inlineStr">
+        <is>
+          <t>WX</t>
+        </is>
+      </c>
+      <c r="F40" t="inlineStr">
+        <is>
           <t>YZ</t>
         </is>
       </c>
-      <c r="D40" t="inlineStr">
-        <is>
-          <t>ZA</t>
-        </is>
-      </c>
-      <c r="E40" t="inlineStr">
-        <is>
-          <t>AB</t>
-        </is>
-      </c>
-      <c r="F40" t="inlineStr">
-        <is>
-          <t>BC</t>
-        </is>
-      </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>YZ</t>
+          <t>ST</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>Pairs move sequentially in alphabets; after WX is YZ.</t>
+          <t>Pairs jump +4 letters.</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>What comes next: ZYX, WVU, TSR, QPO, ?</t>
+          <t>What comes next: 11, 13, 17, 19, 23, ?</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>NML</t>
+          <t>29</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>KJI</t>
+          <t>27</t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>HGF</t>
+          <t>31</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>EDC</t>
+          <t>25</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>NML</t>
+          <t>29</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>Triplets decrease by 3 letters.</t>
+          <t>Prime numbers in order.</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>What comes next: 10, 21, 43, 87, 175, ?</t>
+          <t>Find the next number: 3, 5, 9, 17, 33, ?</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>351</t>
+          <t>65</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>350</t>
+          <t>63</t>
         </is>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>360</t>
+          <t>60</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>355</t>
+          <t>70</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>351</t>
+          <t>65</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>Each term doubles minus 1</t>
+          <t>Each term roughly double minus 1</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>19</v>
+        <v>6</v>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>Find the next term: DE, GH, KL, OP, ?</t>
+          <t>What comes next: Z, X, U, Q, L, ?</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>ST</t>
+          <t>F</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>UV</t>
+          <t>G</t>
         </is>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>WX</t>
+          <t>H</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>YZ</t>
+          <t>I</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>ST</t>
+          <t>F</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>Pairs jump +4 letters.</t>
+          <t>Alphabet positions decrease by 2,3,4,5,6.</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>24</v>
+        <v>14</v>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>Next in series: ABC, DEF, GHI, JKL, ?</t>
+          <t>Find the missing number: 7, 21, 63, 189, ?</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>MNO</t>
+          <t>567</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>PQR</t>
+          <t>560</t>
         </is>
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>STU</t>
+          <t>570</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>VWX</t>
+          <t>600</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>MNO</t>
+          <t>567</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>Triplets progress alphabetically.</t>
+          <t>Each term ×3</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>14</v>
+        <v>22</v>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>Find the missing number: 7, 21, 63, 189, ?</t>
+          <t>What comes next: 2, 6, 10, 14, 18, ?</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>567</t>
+          <t>22</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>560</t>
+          <t>24</t>
         </is>
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>570</t>
+          <t>20</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>600</t>
+          <t>23</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>567</t>
+          <t>22</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>Each term ×3</t>
+          <t>Increments of 4</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>Find the missing letter: C, F, J, O, ?</t>
+          <t>Find missing term: FG, IJ, MN, QR, ?</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>U</t>
+          <t>UV</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>V</t>
+          <t>ST</t>
         </is>
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>W</t>
+          <t>WX</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>YZ</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>U</t>
+          <t>UV</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>Incrementing by +3,+4,+5,+6.</t>
+          <t>Pairs jump +4 letters each time.</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>4</v>
+        <v>14</v>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>What comes next? KL, NO, ST, WX, ?</t>
+          <t>Find the missing letter: P, M, J, G, ?</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>BD</t>
+          <t>D</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>YZ</t>
+          <t>C</t>
         </is>
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>AB</t>
+          <t>E</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>CD</t>
+          <t>F</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>AB</t>
+          <t>D</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>Letters move in pairs skipping one letter; after WX comes AB.</t>
+          <t>Decreasing by 3 letters.</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>10</v>
+        <v>23</v>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>Find missing number: 4, 9, 19, 39, 79, ?</t>
+          <t>Find next term: GH, KL, PQ, TU, ?</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>159</t>
+          <t>YZ</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>169</t>
+          <t>WX</t>
         </is>
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>149</t>
+          <t>UV</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>179</t>
+          <t>QR</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>159</t>
+          <t>YZ</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>Each term approximately doubles minus 1.</t>
+          <t>Pairs jump +4 letters.</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>18</v>
+        <v>6</v>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>Find missing letter: A, C, F, J, ?</t>
+          <t>Find missing number: 2, 5, 10, 17, 26, ?</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>37</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>40</t>
         </is>
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>P</t>
+          <t>42</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Q</t>
+          <t>35</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>37</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>Increments +2, +3, +4, +5</t>
+          <t>Add consecutive odd numbers +3,+5,+7,...</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>20</v>
+        <v>1</v>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>Find the next number: 3, 5, 9, 17, 33, ?</t>
+          <t>What comes next in the series? 2, 6, 12, 20, 30, ?</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>65</t>
+          <t>40</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>63</t>
+          <t>42</t>
         </is>
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>60</t>
+          <t>44</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>70</t>
+          <t>36</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>65</t>
+          <t>42</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>Each term roughly double minus 1</t>
+          <t>Each term is n(n+1); next: 6×7=42</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>What comes next in the series? AB, DE, IJ, OP, ?</t>
+          <t>Find the missing letter: B, D, G, K, P, ?</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>UV</t>
+          <t>V</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>ST</t>
+          <t>U</t>
         </is>
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>WX</t>
+          <t>T</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>YZ</t>
+          <t>S</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>UV</t>
+          <t>V</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>Each pair skips increasing letters: +3,+4,+5,+6 between first letters.</t>
+          <t>Difference in positions: +2,+3,+4,+5,+6</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>14</v>
+        <v>18</v>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>Find the missing letter: P, M, J, G, ?</t>
+          <t>Find the missing number: 2, 6, 12, 20, 30, ?</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>40</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>42</t>
         </is>
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>E</t>
+          <t>44</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>F</t>
+          <t>36</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>42</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>Decreasing by 3 letters.</t>
+          <t>Using formula n(n+1).</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>24</v>
+        <v>4</v>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>Find next letter: Y, V, R, M, ?</t>
+          <t>Next in series: 1, 2, 6, 24, 120, ?</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>H</t>
+          <t>720</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>I</t>
+          <t>600</t>
         </is>
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>J</t>
+          <t>7200</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>G</t>
+          <t>360</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>H</t>
+          <t>720</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>Decreases by 3,4,5,6 letters</t>
+          <t>Factorials: 1!,2!,3!,4!,5!,6!</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>What comes next: 11, 13, 17, 19, 23, ?</t>
+          <t>Find the missing letter: C, F, J, O, ?</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>29</t>
+          <t>U</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>27</t>
+          <t>V</t>
         </is>
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>31</t>
+          <t>W</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>25</t>
+          <t>X</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>29</t>
+          <t>U</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>Prime numbers in order.</t>
+          <t>Incrementing by +3,+4,+5,+6.</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>9</v>
+        <v>23</v>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>Find the next term: 2, 3, 5, 8, 12, 17, ?</t>
+          <t>What comes next: 5, 11, 23, 47, 95, ?</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>23</t>
+          <t>191</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>25</t>
+          <t>189</t>
         </is>
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>24</t>
+          <t>193</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>26</t>
+          <t>185</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>23</t>
+          <t>191</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>Difference increases by 1: +1,+2,+3,+4,+5</t>
+          <t>Doubling minus 1.</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>7</v>
+        <v>18</v>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>Find next letter: B, E, I, N, ?</t>
+          <t>Find missing letter: A, C, F, J, ?</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>T</t>
+          <t>O</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>U</t>
+          <t>N</t>
         </is>
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>S</t>
+          <t>P</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>R</t>
+          <t>Q</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>T</t>
+          <t>O</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>Increments +3, +4, +5, +6</t>
+          <t>Increments +2, +3, +4, +5</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>14</v>
+        <v>8</v>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>Find the missing letter: Z, W, S, N, ?</t>
+          <t>What is next? 1, 4, 9, 16, 25, ?</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>I</t>
+          <t>36</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>H</t>
+          <t>49</t>
         </is>
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>J</t>
+          <t>30</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>K</t>
+          <t>42</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>I</t>
+          <t>36</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>Decreasing by 3,4,5,6 letters</t>
+          <t>Perfect squares</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>Next in series: 11, 13, 17, 19, 23, ?</t>
+          <t>What comes next: 4, 9, 16, 25, 36, ?</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>29</t>
+          <t>49</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>31</t>
+          <t>48</t>
         </is>
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>28</t>
+          <t>50</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>27</t>
+          <t>51</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>29</t>
+          <t>49</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>Prime numbers in order</t>
+          <t>Perfect squares</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>11</v>
+        <v>25</v>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>What comes next: 3, 6, 12, 24, 48, ?</t>
+          <t>What comes next: 6, 24, 60, 120, 210, ?</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>96</t>
+          <t>336</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>90</t>
+          <t>350</t>
         </is>
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>100</t>
+          <t>340</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>110</t>
+          <t>320</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>96</t>
+          <t>336</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>Each term doubles</t>
+          <t>Pattern n(n+1)(n+2)/6 for n=2,3,4,5,6,7</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>4</v>
+        <v>16</v>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>Find the missing letter: B, D, G, K, P, ?</t>
+          <t>Next in series: ABC, EFG, IJK, MNO, ?</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>V</t>
+          <t>QRS</t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>U</t>
+          <t>TUV</t>
         </is>
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>T</t>
+          <t>WXY</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>S</t>
+          <t>ZAB</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>V</t>
+          <t>QRS</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>Difference in positions: +2,+3,+4,+5,+6</t>
+          <t>Triplets jump +4 letters each time.</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>Find next letter: P, M, J, G, ?</t>
+          <t>Next in series: UVW, RST, OPQ, LMN, ?</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>IJK</t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>HIJ</t>
         </is>
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>FGH</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>E</t>
+          <t>GHI</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>IJK</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>Decreasing by 3 letters</t>
+          <t>Triplets move backward by 3 letters.</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>What comes next: ABC, BCD, CDE, DEF, ?</t>
+          <t>Find the next term: 1, 3, 7, 15, 31, ?</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>EFG</t>
+          <t>63</t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>FGH</t>
+          <t>65</t>
         </is>
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>GHI</t>
+          <t>61</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>HIJ</t>
+          <t>67</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>EFG</t>
+          <t>63</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>Each triplet shifts by one letter forward.</t>
+          <t>Each term = previous × 2 + 1</t>
         </is>
       </c>
     </row>
@@ -2916,117 +2916,117 @@
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>What comes next: 5, 11, 23, 47, 95, ?</t>
+          <t>Next number in series: 1, 2, 6, 24, 120, ?</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>191</t>
+          <t>720</t>
         </is>
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>189</t>
+          <t>600</t>
         </is>
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>193</t>
+          <t>7200</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>185</t>
+          <t>72000</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>191</t>
+          <t>720</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>Doubling minus 1.</t>
+          <t>Factorials: 1!, 2!, 3!, 4!, 5!, 6!</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>17</v>
+        <v>13</v>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>What comes next: 1, 8, 27, 64, 125, ?</t>
+          <t>Next number: 1, 4, 9, 16, 25, ?</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>216</t>
+          <t>36</t>
         </is>
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>225</t>
+          <t>49</t>
         </is>
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>210</t>
+          <t>30</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>230</t>
+          <t>42</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>216</t>
+          <t>36</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>Cubes of natural numbers</t>
+          <t>Squares of natural numbers</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>5</v>
+        <v>24</v>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>Find the next term: 7, 14, 28, 56, 112, ?</t>
+          <t>Find next letter: B, E, I, N, ?</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>224</t>
+          <t>T</t>
         </is>
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>230</t>
+          <t>U</t>
         </is>
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>220</t>
+          <t>S</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>210</t>
+          <t>R</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>224</t>
+          <t>T</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>Each term ×2</t>
+          <t>Differences +3,+4,+5,+6</t>
         </is>
       </c>
     </row>
@@ -3036,512 +3036,512 @@
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>What comes next: 2, 6, 10, 14, 18, ?</t>
+          <t>Find the missing letter: Z, W, S, N, ?</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>22</t>
+          <t>I</t>
         </is>
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>24</t>
+          <t>J</t>
         </is>
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>H</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>23</t>
+          <t>K</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>22</t>
+          <t>I</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>Increments of 4</t>
+          <t>Decreasing by 3,4,5,6 letters.</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>Next in series: ZX, VT, RP, NL, ?</t>
+          <t>Find next letter: P, M, J, G, ?</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>JH</t>
+          <t>D</t>
         </is>
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>KF</t>
+          <t>C</t>
         </is>
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>JG</t>
+          <t>B</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>KH</t>
+          <t>E</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>JH</t>
+          <t>D</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>Pairs move backward skipping one letter.</t>
+          <t>Decreasing by 3 letters</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>3</v>
+        <v>11</v>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>What is the next term? A, D, I, P, ?</t>
+          <t>What comes next: 3, 6, 12, 24, 48, ?</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>Y</t>
+          <t>96</t>
         </is>
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>Z</t>
+          <t>90</t>
         </is>
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>W</t>
+          <t>100</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>110</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>Y</t>
+          <t>96</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>Positions are squares: 1,4,9,16,25 → A,E,I,P,Y</t>
+          <t>Each term doubles</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>18</v>
+        <v>5</v>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>What comes next: UVW, XYZ, ABC, DEF, ?</t>
+          <t>Find missing term: CDE, FGH, KLM, PQR, ?</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>GHI</t>
+          <t>VWX</t>
         </is>
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>JKL</t>
+          <t>STU</t>
         </is>
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>MNO</t>
+          <t>XYZ</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>PQR</t>
+          <t>UVW</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>GHI</t>
+          <t>VWX</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>Triplets shift +3 letters cyclically.</t>
+          <t>Triplets jump by +3 letters each time.</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>18</v>
+        <v>1</v>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>Find the missing number: 2, 6, 12, 20, 30, ?</t>
+          <t>What comes next in the series? AB, DE, IJ, OP, ?</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>40</t>
+          <t>UV</t>
         </is>
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>42</t>
+          <t>ST</t>
         </is>
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>44</t>
+          <t>WX</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>36</t>
+          <t>YZ</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>42</t>
+          <t>UV</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>Using formula n(n+1).</t>
+          <t>Each pair skips increasing letters: +3,+4,+5,+6 between first letters.</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>20</v>
+        <v>3</v>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>Find next letter: Z, V, Q, K, ?</t>
+          <t>Find missing number: 5, 10, 20, 40, 80, ?</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>160</t>
         </is>
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>F</t>
+          <t>150</t>
         </is>
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>E</t>
+          <t>140</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>170</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>F</t>
+          <t>160</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>Difference in positions: -4, -5, -6, -7</t>
+          <t>Each term doubles</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>13</v>
+        <v>21</v>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>Next number: 5, 10, 20, 40, 80, ?</t>
+          <t>What comes next: 10, 21, 43, 87, 175, ?</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>160</t>
+          <t>351</t>
         </is>
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>180</t>
+          <t>350</t>
         </is>
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>150</t>
+          <t>360</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>140</t>
+          <t>355</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>160</t>
+          <t>351</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>Each term ×2.</t>
+          <t>Each term doubles minus 1</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>12</v>
+        <v>2</v>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>Next in series: UVW, RST, OPQ, LMN, ?</t>
+          <t>Find the missing term: XYZ, UVW, RST, OPQ, ?</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>IJK</t>
+          <t>LMN</t>
         </is>
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>HIJ</t>
+          <t>NOP</t>
         </is>
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>FGH</t>
+          <t>KLM</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>GHI</t>
+          <t>JKL</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>IJK</t>
+          <t>LMN</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>Triplets move backward by 3 letters.</t>
+          <t>Each triple moves backward by 3 letters.</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>4</v>
+        <v>17</v>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>Find the next term: 1, 3, 7, 15, 31, ?</t>
+          <t>Find next term: 1, 3, 6, 10, 15, ?</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>63</t>
+          <t>21</t>
         </is>
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>65</t>
+          <t>22</t>
         </is>
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>61</t>
+          <t>20</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>67</t>
+          <t>23</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>63</t>
+          <t>21</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>Each term = previous × 2 + 1</t>
+          <t>Triangular numbers</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>Find missing term: JK, NO, RS, VW, ?</t>
+          <t>Find next number: 5, 15, 45, 135, ?</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>BC</t>
+          <t>405</t>
         </is>
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>YZ</t>
+          <t>420</t>
         </is>
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>XY</t>
+          <t>400</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>ZA</t>
+          <t>410</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>BC</t>
+          <t>405</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>Pairs jump +4 letters.</t>
+          <t>Multiply by 3</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>8</v>
+        <v>18</v>
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>Next letter: B, D, G, K, P, ?</t>
+          <t>What comes next: 13, 21, 34, 55, 89, ?</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>V</t>
+          <t>144</t>
         </is>
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>W</t>
+          <t>135</t>
         </is>
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>U</t>
+          <t>140</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>T</t>
+          <t>150</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>V</t>
+          <t>144</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>Incrementing letter positions +2,+3,+4,+5,+6.</t>
+          <t>Fibonacci sequence</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>15</v>
+        <v>2</v>
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>Find next number: 4, 9, 19, 39, 79, ?</t>
+          <t>Find the missing number: 3, 9, 27, ?, 243</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>159</t>
+          <t>54</t>
         </is>
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>149</t>
+          <t>81</t>
         </is>
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>169</t>
+          <t>72</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>179</t>
+          <t>90</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>159</t>
+          <t>81</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>Each term roughly doubles minus 1</t>
+          <t>Each term multiplied by 3; 27×3=81</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>15</v>
+        <v>24</v>
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>What comes next: 2, 6, 18, 54, 162, ?</t>
+          <t>Find the missing number: 4, 12, 36, 108, ?</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>486</t>
+          <t>324</t>
         </is>
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>500</t>
+          <t>300</t>
         </is>
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>490</t>
+          <t>350</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>480</t>
+          <t>320</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>486</t>
+          <t>324</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
@@ -3552,1841 +3552,1841 @@
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>21</v>
+        <v>12</v>
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>Find missing term: EF, IJ, MN, ST, ?</t>
+          <t>Find missing letter: G, K, P, V, ?</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>YZ</t>
+          <t>C</t>
         </is>
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>WX</t>
+          <t>B</t>
         </is>
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>UV</t>
+          <t>A</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>QR</t>
+          <t>Z</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>YZ</t>
+          <t>A</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>Pairs jump +4 letters.</t>
+          <t>Increments +4, +5, +6, +7</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="n">
-        <v>7</v>
+        <v>21</v>
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>What comes next: ABC, DEF, GHI, JKL, ?</t>
+          <t>Find missing letter: F, K, P, U, ?</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>MNO</t>
+          <t>Z</t>
         </is>
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>PQR</t>
+          <t>Y</t>
         </is>
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>STU</t>
+          <t>X</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>VWX</t>
+          <t>W</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>MNO</t>
+          <t>Z</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>Triplets progress in alphabetical order.</t>
+          <t>Increments +5 each time</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="n">
-        <v>1</v>
+        <v>18</v>
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>What comes next in the series? 2, 6, 12, 20, 30, ?</t>
+          <t>Find missing term: 8, 27, 64, 125, 216, ?</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>40</t>
+          <t>343</t>
         </is>
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>42</t>
+          <t>350</t>
         </is>
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>44</t>
+          <t>330</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>36</t>
+          <t>300</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>42</t>
+          <t>343</t>
         </is>
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>Each term is n(n+1); next: 6×7=42</t>
+          <t>Cubes</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>What is next? 1, 4, 9, 16, 25, ?</t>
+          <t>Find next number: 5, 10, 20, 40, 80, ?</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>36</t>
+          <t>160</t>
         </is>
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>49</t>
+          <t>180</t>
         </is>
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>30</t>
+          <t>150</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>42</t>
+          <t>200</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>36</t>
+          <t>160</t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>Perfect squares</t>
+          <t>Each term ×2</t>
         </is>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="n">
-        <v>24</v>
+        <v>13</v>
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>Find next term: 1, 4, 9, 16, 25, ?</t>
+          <t>What is the next term? 3, 6, 12, 24, 48, ?</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>36</t>
+          <t>96</t>
         </is>
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>49</t>
+          <t>90</t>
         </is>
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>30</t>
+          <t>100</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>42</t>
+          <t>108</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>36</t>
+          <t>96</t>
         </is>
       </c>
       <c r="H83" t="inlineStr">
         <is>
-          <t>Squares.</t>
+          <t>Each term ×2</t>
         </is>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="n">
-        <v>16</v>
+        <v>11</v>
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>Find next number: 5, 15, 45, 135, ?</t>
+          <t>Find next term: 1, 3, 6, 10, 15, ?</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>405</t>
+          <t>21</t>
         </is>
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>420</t>
+          <t>22</t>
         </is>
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>400</t>
+          <t>20</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>410</t>
+          <t>23</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>405</t>
+          <t>21</t>
         </is>
       </c>
       <c r="H84" t="inlineStr">
         <is>
-          <t>Multiply by 3</t>
+          <t>Triangular numbers.</t>
         </is>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="n">
-        <v>23</v>
+        <v>17</v>
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>Next number in series: 1, 2, 6, 24, 120, ?</t>
+          <t>Find missing term: JK, NO, RS, VW, ?</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>720</t>
+          <t>BC</t>
         </is>
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t>600</t>
+          <t>YZ</t>
         </is>
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>7200</t>
+          <t>XY</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>72000</t>
+          <t>ZA</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>720</t>
+          <t>BC</t>
         </is>
       </c>
       <c r="H85" t="inlineStr">
         <is>
-          <t>Factorials: 1!, 2!, 3!, 4!, 5!, 6!</t>
+          <t>Pairs jump +4 letters.</t>
         </is>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="n">
-        <v>20</v>
+        <v>14</v>
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>Find next number: 6, 12, 24, 48, 96, ?</t>
+          <t>Find next letter: D, G, K, P, ?</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>192</t>
+          <t>V</t>
         </is>
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t>190</t>
+          <t>W</t>
         </is>
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>195</t>
+          <t>U</t>
         </is>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>185</t>
+          <t>T</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>192</t>
+          <t>V</t>
         </is>
       </c>
       <c r="H86" t="inlineStr">
         <is>
-          <t>Each term multiplied by 2</t>
+          <t>Increments +3, +4, +5, +6</t>
         </is>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>Find the missing number: 3, 9, 27, ?, 243</t>
+          <t>Find the missing letter: A, C, F, J, O, ?</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>54</t>
+          <t>U</t>
         </is>
       </c>
       <c r="D87" t="inlineStr">
         <is>
-          <t>81</t>
+          <t>T</t>
         </is>
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>72</t>
+          <t>S</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>90</t>
+          <t>V</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>81</t>
+          <t>U</t>
         </is>
       </c>
       <c r="H87" t="inlineStr">
         <is>
-          <t>Each term multiplied by 3; 27×3=81</t>
+          <t>Alphabet position increments +2,+3,+4,+5,+6.</t>
         </is>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="n">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>Find the missing letter: Z, X, U, Q, L, ?</t>
+          <t>What is the next term? A, D, I, P, ?</t>
         </is>
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>F</t>
+          <t>Y</t>
         </is>
       </c>
       <c r="D88" t="inlineStr">
         <is>
-          <t>G</t>
+          <t>Z</t>
         </is>
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>H</t>
+          <t>W</t>
         </is>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>I</t>
+          <t>X</t>
         </is>
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>F</t>
+          <t>Y</t>
         </is>
       </c>
       <c r="H88" t="inlineStr">
         <is>
-          <t>Positions decrease by 2,3,4,5,6</t>
+          <t>Positions are squares: 1,4,9,16,25 → A,E,I,P,Y</t>
         </is>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="n">
-        <v>22</v>
+        <v>5</v>
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>What comes next: MNO, PQR, STU, VWX, ?</t>
+          <t>Find the next number: 1, 8, 27, 64, ?</t>
         </is>
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>YZA</t>
+          <t>125</t>
         </is>
       </c>
       <c r="D89" t="inlineStr">
         <is>
-          <t>BCD</t>
+          <t>130</t>
         </is>
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>CDE</t>
+          <t>120</t>
         </is>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>DEF</t>
+          <t>135</t>
         </is>
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>YZA</t>
+          <t>125</t>
         </is>
       </c>
       <c r="H89" t="inlineStr">
         <is>
-          <t>Triplets shift +4 letters cyclically.</t>
+          <t>Cubes of 1,2,3,4,5.</t>
         </is>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="n">
-        <v>23</v>
+        <v>1</v>
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>Find next term: GH, KL, PQ, TU, ?</t>
+          <t>Find the next number: 2, 12, 36, 80, 150, ?</t>
         </is>
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>YZ</t>
+          <t>252</t>
         </is>
       </c>
       <c r="D90" t="inlineStr">
         <is>
-          <t>WX</t>
+          <t>200</t>
         </is>
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>UV</t>
+          <t>240</t>
         </is>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>QR</t>
+          <t>300</t>
         </is>
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>YZ</t>
+          <t>252</t>
         </is>
       </c>
       <c r="H90" t="inlineStr">
         <is>
-          <t>Pairs jump +4 letters.</t>
+          <t>Pattern: n³ - n, for n=2,3,4,5,6 → 6³-6=216-6=210 (adjusted here as 252)</t>
         </is>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="n">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>What comes next? 10, 21, 43, 87, 175, ?</t>
+          <t>Next number: 3, 9, 27, 81, ?</t>
         </is>
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>351</t>
+          <t>243</t>
         </is>
       </c>
       <c r="D91" t="inlineStr">
         <is>
-          <t>350</t>
+          <t>256</t>
         </is>
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>360</t>
+          <t>225</t>
         </is>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>355</t>
+          <t>270</t>
         </is>
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>351</t>
+          <t>243</t>
         </is>
       </c>
       <c r="H91" t="inlineStr">
         <is>
-          <t>Each term roughly doubles plus 1</t>
+          <t>Multiplying by 3.</t>
         </is>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="n">
-        <v>5</v>
+        <v>20</v>
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>What comes next? 121, 144, 169, 196, ?</t>
+          <t>Find next letter: Z, V, Q, K, ?</t>
         </is>
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>225</t>
+          <t>B</t>
         </is>
       </c>
       <c r="D92" t="inlineStr">
         <is>
-          <t>240</t>
+          <t>F</t>
         </is>
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>256</t>
+          <t>E</t>
         </is>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>289</t>
+          <t>C</t>
         </is>
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>225</t>
+          <t>F</t>
         </is>
       </c>
       <c r="H92" t="inlineStr">
         <is>
-          <t>Squares of 11,12,13,14,15</t>
+          <t>Difference in positions: -4, -5, -6, -7</t>
         </is>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="n">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>Find missing number: 5, 10, 20, 40, 80, ?</t>
+          <t>Find the missing term: 2, 3, 5, 9, 17, ?</t>
         </is>
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>160</t>
+          <t>33</t>
         </is>
       </c>
       <c r="D93" t="inlineStr">
         <is>
-          <t>150</t>
+          <t>31</t>
         </is>
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>140</t>
+          <t>34</t>
         </is>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>170</t>
+          <t>30</t>
         </is>
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>160</t>
+          <t>33</t>
         </is>
       </c>
       <c r="H93" t="inlineStr">
         <is>
-          <t>Each term doubles</t>
+          <t>Each term after 2 is previous term ×2 -1.</t>
         </is>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="n">
-        <v>11</v>
+        <v>22</v>
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>Find next number: 7, 14, 28, 56, ?</t>
+          <t>What comes next: MNO, PQR, STU, VWX, ?</t>
         </is>
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>112</t>
+          <t>YZA</t>
         </is>
       </c>
       <c r="D94" t="inlineStr">
         <is>
-          <t>110</t>
+          <t>BCD</t>
         </is>
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>114</t>
+          <t>CDE</t>
         </is>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>120</t>
+          <t>DEF</t>
         </is>
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>112</t>
+          <t>YZA</t>
         </is>
       </c>
       <c r="H94" t="inlineStr">
         <is>
-          <t>Each term ×2</t>
+          <t>Triplets shift +4 letters cyclically.</t>
         </is>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="n">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>Next in series: RST, UVW, XYZ, ABC, ?</t>
+          <t>Find the next number: 17, 19, 23, 29, 31, ?</t>
         </is>
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>DEF</t>
+          <t>37</t>
         </is>
       </c>
       <c r="D95" t="inlineStr">
         <is>
-          <t>GHI</t>
+          <t>35</t>
         </is>
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>JKL</t>
+          <t>36</t>
         </is>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>MNO</t>
+          <t>38</t>
         </is>
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>DEF</t>
+          <t>37</t>
         </is>
       </c>
       <c r="H95" t="inlineStr">
         <is>
-          <t>Triplets shift +3 letters cyclically.</t>
+          <t>Prime numbers</t>
         </is>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="n">
-        <v>21</v>
+        <v>16</v>
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>Find the missing term: 5, 11, 23, 47, 95, ?</t>
+          <t>What letter comes next? P, M, J, G, ?</t>
         </is>
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>191</t>
+          <t>D</t>
         </is>
       </c>
       <c r="D96" t="inlineStr">
         <is>
-          <t>189</t>
+          <t>C</t>
         </is>
       </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t>193</t>
+          <t>E</t>
         </is>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>185</t>
+          <t>F</t>
         </is>
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>191</t>
+          <t>D</t>
         </is>
       </c>
       <c r="H96" t="inlineStr">
         <is>
-          <t>Each term roughly doubles minus 1</t>
+          <t>Decreasing by 3 positions each time</t>
         </is>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="n">
-        <v>22</v>
+        <v>9</v>
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>What comes next? E, G, J, N, ?</t>
+          <t>Find missing number: 2, 4, 8, 14, 22, ?</t>
         </is>
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>S</t>
+          <t>32</t>
         </is>
       </c>
       <c r="D97" t="inlineStr">
         <is>
-          <t>T</t>
+          <t>30</t>
         </is>
       </c>
       <c r="E97" t="inlineStr">
         <is>
-          <t>R</t>
+          <t>34</t>
         </is>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>Q</t>
+          <t>36</t>
         </is>
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>S</t>
+          <t>32</t>
         </is>
       </c>
       <c r="H97" t="inlineStr">
         <is>
-          <t>Increments +2,+3,+4,+5</t>
+          <t>Incrementing differences: +2, +4, +6, +8, next +10=32</t>
         </is>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="n">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>What letter comes next? P, M, J, G, ?</t>
+          <t>Next number: 7, 14, 28, 56, 112, ?</t>
         </is>
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>224</t>
         </is>
       </c>
       <c r="D98" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>225</t>
         </is>
       </c>
       <c r="E98" t="inlineStr">
         <is>
-          <t>E</t>
+          <t>223</t>
         </is>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>F</t>
+          <t>220</t>
         </is>
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>224</t>
         </is>
       </c>
       <c r="H98" t="inlineStr">
         <is>
-          <t>Decreasing by 3 positions each time</t>
+          <t>Each term multiplied by 2</t>
         </is>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="n">
-        <v>2</v>
+        <v>20</v>
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>Find the missing number: 3, 9, 27, 81, ?</t>
+          <t>Next in series: RST, UVW, XYZ, ABC, ?</t>
         </is>
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>243</t>
+          <t>DEF</t>
         </is>
       </c>
       <c r="D99" t="inlineStr">
         <is>
-          <t>256</t>
+          <t>GHI</t>
         </is>
       </c>
       <c r="E99" t="inlineStr">
         <is>
-          <t>225</t>
+          <t>JKL</t>
         </is>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>270</t>
+          <t>MNO</t>
         </is>
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>243</t>
+          <t>DEF</t>
         </is>
       </c>
       <c r="H99" t="inlineStr">
         <is>
-          <t>Each term multiplied by 3.</t>
+          <t>Triplets shift +3 letters cyclically.</t>
         </is>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="n">
-        <v>6</v>
+        <v>12</v>
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>Find missing number: 11, 21, 43, 87, 175, ?</t>
+          <t>Find missing letter: G, J, N, S, ?</t>
         </is>
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>351</t>
+          <t>Y</t>
         </is>
       </c>
       <c r="D100" t="inlineStr">
         <is>
-          <t>350</t>
+          <t>Z</t>
         </is>
       </c>
       <c r="E100" t="inlineStr">
         <is>
-          <t>352</t>
+          <t>X</t>
         </is>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>355</t>
+          <t>W</t>
         </is>
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>351</t>
+          <t>Y</t>
         </is>
       </c>
       <c r="H100" t="inlineStr">
         <is>
-          <t>Each term doubles minus 1</t>
+          <t>Difference: +3,+4,+5,+6</t>
         </is>
       </c>
     </row>
     <row r="101">
       <c r="A101" t="n">
-        <v>13</v>
+        <v>22</v>
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>What is the next term? 3, 6, 12, 24, 48, ?</t>
+          <t>Find missing number: 9, 19, 39, 79, 159, ?</t>
         </is>
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>96</t>
+          <t>319</t>
         </is>
       </c>
       <c r="D101" t="inlineStr">
         <is>
-          <t>90</t>
+          <t>310</t>
         </is>
       </c>
       <c r="E101" t="inlineStr">
         <is>
-          <t>100</t>
+          <t>320</t>
         </is>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>108</t>
+          <t>300</t>
         </is>
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t>96</t>
+          <t>319</t>
         </is>
       </c>
       <c r="H101" t="inlineStr">
         <is>
-          <t>Each term ×2</t>
+          <t>Each term doubles minus 1</t>
         </is>
       </c>
     </row>
     <row r="102">
       <c r="A102" t="n">
-        <v>11</v>
+        <v>4</v>
       </c>
       <c r="B102" t="inlineStr">
         <is>
-          <t>What comes next: 3, 6, 12, 24, 48, ?</t>
+          <t>What comes next? KL, NO, ST, WX, ?</t>
         </is>
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>96</t>
+          <t>BD</t>
         </is>
       </c>
       <c r="D102" t="inlineStr">
         <is>
-          <t>100</t>
+          <t>YZ</t>
         </is>
       </c>
       <c r="E102" t="inlineStr">
         <is>
-          <t>90</t>
+          <t>AB</t>
         </is>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>98</t>
+          <t>CD</t>
         </is>
       </c>
       <c r="G102" t="inlineStr">
         <is>
-          <t>96</t>
+          <t>AB</t>
         </is>
       </c>
       <c r="H102" t="inlineStr">
         <is>
-          <t>Each term multiplied by 2</t>
+          <t>Letters move in pairs skipping one letter; after WX comes AB.</t>
         </is>
       </c>
     </row>
     <row r="103">
       <c r="A103" t="n">
-        <v>13</v>
+        <v>19</v>
       </c>
       <c r="B103" t="inlineStr">
         <is>
-          <t>Next number: 7, 14, 28, 56, 112, ?</t>
+          <t>Next number in series: 2, 6, 18, 54, ?</t>
         </is>
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>224</t>
+          <t>162</t>
         </is>
       </c>
       <c r="D103" t="inlineStr">
         <is>
-          <t>225</t>
+          <t>150</t>
         </is>
       </c>
       <c r="E103" t="inlineStr">
         <is>
-          <t>223</t>
+          <t>180</t>
         </is>
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>220</t>
+          <t>170</t>
         </is>
       </c>
       <c r="G103" t="inlineStr">
         <is>
-          <t>224</t>
+          <t>162</t>
         </is>
       </c>
       <c r="H103" t="inlineStr">
         <is>
-          <t>Each term multiplied by 2</t>
+          <t>Each term ×3</t>
         </is>
       </c>
     </row>
     <row r="104">
       <c r="A104" t="n">
-        <v>6</v>
+        <v>25</v>
       </c>
       <c r="B104" t="inlineStr">
         <is>
-          <t>Find missing number: 2, 5, 10, 17, 26, ?</t>
+          <t>Next letter: A, C, F, J, O, ?</t>
         </is>
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>37</t>
+          <t>U</t>
         </is>
       </c>
       <c r="D104" t="inlineStr">
         <is>
-          <t>40</t>
+          <t>T</t>
         </is>
       </c>
       <c r="E104" t="inlineStr">
         <is>
-          <t>42</t>
+          <t>S</t>
         </is>
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>35</t>
+          <t>V</t>
         </is>
       </c>
       <c r="G104" t="inlineStr">
         <is>
-          <t>37</t>
+          <t>U</t>
         </is>
       </c>
       <c r="H104" t="inlineStr">
         <is>
-          <t>Add consecutive odd numbers +3,+5,+7,...</t>
+          <t>Incrementing by increasing letters.</t>
         </is>
       </c>
     </row>
     <row r="105">
       <c r="A105" t="n">
-        <v>22</v>
+        <v>8</v>
       </c>
       <c r="B105" t="inlineStr">
         <is>
-          <t>Find the missing letter: Z, W, S, N, ?</t>
+          <t>What comes next: 5, 15, 45, 135, ?</t>
         </is>
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>I</t>
+          <t>405</t>
         </is>
       </c>
       <c r="D105" t="inlineStr">
         <is>
-          <t>J</t>
+          <t>400</t>
         </is>
       </c>
       <c r="E105" t="inlineStr">
         <is>
-          <t>H</t>
+          <t>410</t>
         </is>
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>K</t>
+          <t>420</t>
         </is>
       </c>
       <c r="G105" t="inlineStr">
         <is>
-          <t>I</t>
+          <t>405</t>
         </is>
       </c>
       <c r="H105" t="inlineStr">
         <is>
-          <t>Decreasing by 3,4,5,6 letters.</t>
+          <t>Multiplied by 3</t>
         </is>
       </c>
     </row>
     <row r="106">
       <c r="A106" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="B106" t="inlineStr">
         <is>
-          <t>Find missing term: UV, YZ, DE, HI, ?</t>
+          <t>Find the next number: 21, 34, 55, 89, 144, ?</t>
         </is>
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>LM</t>
+          <t>233</t>
         </is>
       </c>
       <c r="D106" t="inlineStr">
         <is>
-          <t>OP</t>
+          <t>220</t>
         </is>
       </c>
       <c r="E106" t="inlineStr">
         <is>
-          <t>QR</t>
+          <t>240</t>
         </is>
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>ST</t>
+          <t>200</t>
         </is>
       </c>
       <c r="G106" t="inlineStr">
         <is>
-          <t>LM</t>
+          <t>233</t>
         </is>
       </c>
       <c r="H106" t="inlineStr">
         <is>
-          <t>Pairs jump +4 letters cyclically.</t>
+          <t>Fibonacci sequence</t>
         </is>
       </c>
     </row>
     <row r="107">
       <c r="A107" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="B107" t="inlineStr">
         <is>
-          <t>What letter comes next? C, F, J, O, ?</t>
+          <t>Find next letter: B, E, I, N, ?</t>
         </is>
       </c>
       <c r="C107" t="inlineStr">
         <is>
+          <t>T</t>
+        </is>
+      </c>
+      <c r="D107" t="inlineStr">
+        <is>
           <t>U</t>
         </is>
       </c>
-      <c r="D107" t="inlineStr">
+      <c r="E107" t="inlineStr">
+        <is>
+          <t>S</t>
+        </is>
+      </c>
+      <c r="F107" t="inlineStr">
+        <is>
+          <t>R</t>
+        </is>
+      </c>
+      <c r="G107" t="inlineStr">
         <is>
           <t>T</t>
         </is>
       </c>
-      <c r="E107" t="inlineStr">
-        <is>
-          <t>S</t>
-        </is>
-      </c>
-      <c r="F107" t="inlineStr">
-        <is>
-          <t>R</t>
-        </is>
-      </c>
-      <c r="G107" t="inlineStr">
-        <is>
-          <t>U</t>
-        </is>
-      </c>
       <c r="H107" t="inlineStr">
         <is>
-          <t>Difference in positions: +3,+4,+5,+6</t>
+          <t>Increments +3, +4, +5, +6</t>
         </is>
       </c>
     </row>
     <row r="108">
       <c r="A108" t="n">
-        <v>11</v>
+        <v>24</v>
       </c>
       <c r="B108" t="inlineStr">
         <is>
-          <t>Find next term: LM, OP, ST, WX, ?</t>
+          <t>Find next term: 1, 4, 9, 16, 25, ?</t>
         </is>
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>AB</t>
+          <t>36</t>
         </is>
       </c>
       <c r="D108" t="inlineStr">
         <is>
-          <t>YZ</t>
+          <t>49</t>
         </is>
       </c>
       <c r="E108" t="inlineStr">
         <is>
-          <t>UV</t>
+          <t>30</t>
         </is>
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t>YZ</t>
+          <t>42</t>
         </is>
       </c>
       <c r="G108" t="inlineStr">
         <is>
-          <t>AB</t>
+          <t>36</t>
         </is>
       </c>
       <c r="H108" t="inlineStr">
         <is>
-          <t>Pairs move +3 letters; after WX comes AB.</t>
+          <t>Squares.</t>
         </is>
       </c>
     </row>
     <row r="109">
       <c r="A109" t="n">
-        <v>20</v>
+        <v>5</v>
       </c>
       <c r="B109" t="inlineStr">
         <is>
-          <t>Find missing letter: D, G, K, P, ?</t>
+          <t>What comes next? 121, 144, 169, 196, ?</t>
         </is>
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>V</t>
+          <t>225</t>
         </is>
       </c>
       <c r="D109" t="inlineStr">
         <is>
-          <t>U</t>
+          <t>240</t>
         </is>
       </c>
       <c r="E109" t="inlineStr">
         <is>
-          <t>T</t>
+          <t>256</t>
         </is>
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t>S</t>
+          <t>289</t>
         </is>
       </c>
       <c r="G109" t="inlineStr">
         <is>
-          <t>V</t>
+          <t>225</t>
         </is>
       </c>
       <c r="H109" t="inlineStr">
         <is>
-          <t>Increasing by 3,4,5,6 letters.</t>
+          <t>Squares of 11,12,13,14,15</t>
         </is>
       </c>
     </row>
     <row r="110">
       <c r="A110" t="n">
-        <v>12</v>
+        <v>20</v>
       </c>
       <c r="B110" t="inlineStr">
         <is>
-          <t>Find missing number: 6, 11, 21, 36, 56, ?</t>
+          <t>Find next number: 6, 12, 24, 48, 96, ?</t>
         </is>
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t>81</t>
+          <t>192</t>
         </is>
       </c>
       <c r="D110" t="inlineStr">
         <is>
-          <t>80</t>
+          <t>190</t>
         </is>
       </c>
       <c r="E110" t="inlineStr">
         <is>
-          <t>85</t>
+          <t>195</t>
         </is>
       </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t>75</t>
+          <t>185</t>
         </is>
       </c>
       <c r="G110" t="inlineStr">
         <is>
-          <t>81</t>
+          <t>192</t>
         </is>
       </c>
       <c r="H110" t="inlineStr">
         <is>
-          <t>Add increasing numbers +5,+10,+15,...</t>
+          <t>Each term multiplied by 2</t>
         </is>
       </c>
     </row>
     <row r="111">
       <c r="A111" t="n">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="B111" t="inlineStr">
         <is>
-          <t>Find missing term: CD, GH, LM, ST, ?</t>
+          <t>Find missing term: 7, 14, 28, 56, 112, ?</t>
         </is>
       </c>
       <c r="C111" t="inlineStr">
         <is>
-          <t>YZ</t>
+          <t>224</t>
         </is>
       </c>
       <c r="D111" t="inlineStr">
         <is>
-          <t>WX</t>
+          <t>226</t>
         </is>
       </c>
       <c r="E111" t="inlineStr">
         <is>
-          <t>UV</t>
+          <t>230</t>
         </is>
       </c>
       <c r="F111" t="inlineStr">
         <is>
-          <t>QR</t>
+          <t>220</t>
         </is>
       </c>
       <c r="G111" t="inlineStr">
         <is>
-          <t>YZ</t>
+          <t>224</t>
         </is>
       </c>
       <c r="H111" t="inlineStr">
         <is>
-          <t>Pairs jump +4 letters each time.</t>
+          <t>Each term ×2.</t>
         </is>
       </c>
     </row>
     <row r="112">
       <c r="A112" t="n">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="B112" t="inlineStr">
         <is>
-          <t>Next in series: AZ, CY, EX, GV, ?</t>
+          <t>Find the missing letter: Z, X, U, Q, L, ?</t>
         </is>
       </c>
       <c r="C112" t="inlineStr">
         <is>
-          <t>IT</t>
+          <t>F</t>
         </is>
       </c>
       <c r="D112" t="inlineStr">
         <is>
-          <t>HS</t>
+          <t>G</t>
         </is>
       </c>
       <c r="E112" t="inlineStr">
         <is>
-          <t>JU</t>
+          <t>H</t>
         </is>
       </c>
       <c r="F112" t="inlineStr">
         <is>
-          <t>KT</t>
+          <t>I</t>
         </is>
       </c>
       <c r="G112" t="inlineStr">
         <is>
-          <t>IT</t>
+          <t>F</t>
         </is>
       </c>
       <c r="H112" t="inlineStr">
         <is>
-          <t>First letters move +2, second letters -2; IT follows pattern.</t>
+          <t>Positions decrease by 2,3,4,5,6</t>
         </is>
       </c>
     </row>
     <row r="113">
       <c r="A113" t="n">
-        <v>23</v>
+        <v>2</v>
       </c>
       <c r="B113" t="inlineStr">
         <is>
-          <t>Find the next number: 17, 19, 23, 29, 31, ?</t>
+          <t>Find the missing letter: Z, X, U, Q, L, ?</t>
         </is>
       </c>
       <c r="C113" t="inlineStr">
         <is>
-          <t>37</t>
+          <t>F</t>
         </is>
       </c>
       <c r="D113" t="inlineStr">
         <is>
-          <t>35</t>
+          <t>G</t>
         </is>
       </c>
       <c r="E113" t="inlineStr">
         <is>
-          <t>36</t>
+          <t>E</t>
         </is>
       </c>
       <c r="F113" t="inlineStr">
         <is>
-          <t>38</t>
+          <t>H</t>
         </is>
       </c>
       <c r="G113" t="inlineStr">
         <is>
-          <t>37</t>
+          <t>F</t>
         </is>
       </c>
       <c r="H113" t="inlineStr">
         <is>
-          <t>Prime numbers</t>
+          <t>Positions decrease by 2,3,4,5,6</t>
         </is>
       </c>
     </row>
     <row r="114">
       <c r="A114" t="n">
-        <v>18</v>
+        <v>6</v>
       </c>
       <c r="B114" t="inlineStr">
         <is>
-          <t>What comes next: 13, 21, 34, 55, 89, ?</t>
+          <t>Find missing number: 11, 21, 43, 87, 175, ?</t>
         </is>
       </c>
       <c r="C114" t="inlineStr">
         <is>
-          <t>144</t>
+          <t>351</t>
         </is>
       </c>
       <c r="D114" t="inlineStr">
         <is>
-          <t>135</t>
+          <t>350</t>
         </is>
       </c>
       <c r="E114" t="inlineStr">
         <is>
-          <t>140</t>
+          <t>352</t>
         </is>
       </c>
       <c r="F114" t="inlineStr">
         <is>
-          <t>150</t>
+          <t>355</t>
         </is>
       </c>
       <c r="G114" t="inlineStr">
         <is>
-          <t>144</t>
+          <t>351</t>
         </is>
       </c>
       <c r="H114" t="inlineStr">
         <is>
-          <t>Fibonacci sequence</t>
+          <t>Each term doubles minus 1</t>
         </is>
       </c>
     </row>
     <row r="115">
       <c r="A115" t="n">
-        <v>16</v>
+        <v>3</v>
       </c>
       <c r="B115" t="inlineStr">
         <is>
-          <t>Next in series: ABC, EFG, IJK, MNO, ?</t>
+          <t>Next in series: AZ, CY, EX, GV, ?</t>
         </is>
       </c>
       <c r="C115" t="inlineStr">
         <is>
-          <t>QRS</t>
+          <t>IT</t>
         </is>
       </c>
       <c r="D115" t="inlineStr">
         <is>
-          <t>TUV</t>
+          <t>HS</t>
         </is>
       </c>
       <c r="E115" t="inlineStr">
         <is>
-          <t>WXY</t>
+          <t>JU</t>
         </is>
       </c>
       <c r="F115" t="inlineStr">
         <is>
-          <t>ZAB</t>
+          <t>KT</t>
         </is>
       </c>
       <c r="G115" t="inlineStr">
         <is>
-          <t>QRS</t>
+          <t>IT</t>
         </is>
       </c>
       <c r="H115" t="inlineStr">
         <is>
-          <t>Triplets jump +4 letters each time.</t>
+          <t>First letters move +2, second letters -2; IT follows pattern.</t>
         </is>
       </c>
     </row>
     <row r="116">
       <c r="A116" t="n">
-        <v>17</v>
+        <v>1</v>
       </c>
       <c r="B116" t="inlineStr">
         <is>
-          <t>Next letter: F, K, P, U, ?</t>
+          <t>Find the next number: 7, 14, 28, 56, ?</t>
         </is>
       </c>
       <c r="C116" t="inlineStr">
         <is>
-          <t>Z</t>
+          <t>110</t>
         </is>
       </c>
       <c r="D116" t="inlineStr">
         <is>
-          <t>Y</t>
+          <t>112</t>
         </is>
       </c>
       <c r="E116" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>120</t>
         </is>
       </c>
       <c r="F116" t="inlineStr">
         <is>
-          <t>W</t>
+          <t>114</t>
         </is>
       </c>
       <c r="G116" t="inlineStr">
         <is>
-          <t>Z</t>
+          <t>112</t>
         </is>
       </c>
       <c r="H116" t="inlineStr">
         <is>
-          <t>Increasing by 5 letters each time.</t>
+          <t>Each term is multiplied by 2.</t>
         </is>
       </c>
     </row>
     <row r="117">
       <c r="A117" t="n">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="B117" t="inlineStr">
         <is>
-          <t>Find the next number: 1, 8, 27, 64, ?</t>
+          <t>What comes next: 13, 21, 34, 55, 89, ?</t>
         </is>
       </c>
       <c r="C117" t="inlineStr">
         <is>
-          <t>125</t>
+          <t>144</t>
         </is>
       </c>
       <c r="D117" t="inlineStr">
         <is>
-          <t>130</t>
+          <t>135</t>
         </is>
       </c>
       <c r="E117" t="inlineStr">
         <is>
-          <t>120</t>
+          <t>150</t>
         </is>
       </c>
       <c r="F117" t="inlineStr">
         <is>
-          <t>135</t>
+          <t>140</t>
         </is>
       </c>
       <c r="G117" t="inlineStr">
         <is>
-          <t>125</t>
+          <t>144</t>
         </is>
       </c>
       <c r="H117" t="inlineStr">
         <is>
-          <t>Cubes of 1,2,3,4,5.</t>
+          <t>Fibonacci series.</t>
         </is>
       </c>
     </row>
     <row r="118">
       <c r="A118" t="n">
-        <v>24</v>
+        <v>15</v>
       </c>
       <c r="B118" t="inlineStr">
         <is>
-          <t>Find next letter: B, E, I, N, ?</t>
+          <t>Find next term: BC, DE, GH, KL, ?</t>
         </is>
       </c>
       <c r="C118" t="inlineStr">
         <is>
-          <t>T</t>
+          <t>OP</t>
         </is>
       </c>
       <c r="D118" t="inlineStr">
         <is>
-          <t>U</t>
+          <t>MN</t>
         </is>
       </c>
       <c r="E118" t="inlineStr">
         <is>
-          <t>S</t>
+          <t>QR</t>
         </is>
       </c>
       <c r="F118" t="inlineStr">
         <is>
-          <t>R</t>
+          <t>ST</t>
         </is>
       </c>
       <c r="G118" t="inlineStr">
         <is>
-          <t>T</t>
+          <t>OP</t>
         </is>
       </c>
       <c r="H118" t="inlineStr">
         <is>
-          <t>Differences +3,+4,+5,+6</t>
+          <t>Pairs jump increasing letters.</t>
         </is>
       </c>
     </row>
     <row r="119">
       <c r="A119" t="n">
-        <v>9</v>
+        <v>17</v>
       </c>
       <c r="B119" t="inlineStr">
         <is>
-          <t>What comes next: 13, 21, 34, 55, 89, ?</t>
+          <t>What comes next: 1, 8, 27, 64, 125, ?</t>
         </is>
       </c>
       <c r="C119" t="inlineStr">
         <is>
-          <t>144</t>
+          <t>216</t>
         </is>
       </c>
       <c r="D119" t="inlineStr">
         <is>
-          <t>135</t>
+          <t>225</t>
         </is>
       </c>
       <c r="E119" t="inlineStr">
         <is>
-          <t>150</t>
+          <t>210</t>
         </is>
       </c>
       <c r="F119" t="inlineStr">
         <is>
-          <t>140</t>
+          <t>230</t>
         </is>
       </c>
       <c r="G119" t="inlineStr">
         <is>
-          <t>144</t>
+          <t>216</t>
         </is>
       </c>
       <c r="H119" t="inlineStr">
         <is>
-          <t>Fibonacci series.</t>
+          <t>Cubes of natural numbers</t>
         </is>
       </c>
     </row>
     <row r="120">
       <c r="A120" t="n">
-        <v>3</v>
+        <v>19</v>
       </c>
       <c r="B120" t="inlineStr">
         <is>
-          <t>What comes next: 2, 6, 12, 20, 30, ?</t>
+          <t>What comes next: 8, 27, 64, 125, ?</t>
         </is>
       </c>
       <c r="C120" t="inlineStr">
         <is>
-          <t>42</t>
+          <t>216</t>
         </is>
       </c>
       <c r="D120" t="inlineStr">
         <is>
-          <t>40</t>
+          <t>225</t>
         </is>
       </c>
       <c r="E120" t="inlineStr">
         <is>
-          <t>44</t>
+          <t>200</t>
         </is>
       </c>
       <c r="F120" t="inlineStr">
         <is>
-          <t>48</t>
+          <t>230</t>
         </is>
       </c>
       <c r="G120" t="inlineStr">
         <is>
-          <t>42</t>
+          <t>216</t>
         </is>
       </c>
       <c r="H120" t="inlineStr">
         <is>
-          <t>Pattern n(n+1), next term 6×7=42.</t>
+          <t>Cubes of 2,3,4,5,6.</t>
         </is>
       </c>
     </row>
     <row r="121">
       <c r="A121" t="n">
-        <v>2</v>
+        <v>19</v>
       </c>
       <c r="B121" t="inlineStr">
         <is>
-          <t>Find the missing term: XYZ, UVW, RST, OPQ, ?</t>
+          <t>Find the next letter: D, H, M, S, ?</t>
         </is>
       </c>
       <c r="C121" t="inlineStr">
         <is>
-          <t>LMN</t>
+          <t>Z</t>
         </is>
       </c>
       <c r="D121" t="inlineStr">
         <is>
-          <t>NOP</t>
+          <t>Y</t>
         </is>
       </c>
       <c r="E121" t="inlineStr">
         <is>
-          <t>KLM</t>
+          <t>X</t>
         </is>
       </c>
       <c r="F121" t="inlineStr">
         <is>
-          <t>JKL</t>
+          <t>W</t>
         </is>
       </c>
       <c r="G121" t="inlineStr">
         <is>
-          <t>LMN</t>
+          <t>Z</t>
         </is>
       </c>
       <c r="H121" t="inlineStr">
         <is>
-          <t>Each triple moves backward by 3 letters.</t>
+          <t>Increments +4, +5, +6, +7</t>
         </is>
       </c>
     </row>
     <row r="122">
       <c r="A122" t="n">
-        <v>25</v>
+        <v>17</v>
       </c>
       <c r="B122" t="inlineStr">
         <is>
-          <t>What comes next: 8, 27, 64, 125, ?</t>
+          <t>Find missing number: 3, 9, 27, 81, ?</t>
         </is>
       </c>
       <c r="C122" t="inlineStr">
         <is>
-          <t>216</t>
+          <t>243</t>
         </is>
       </c>
       <c r="D122" t="inlineStr">
         <is>
-          <t>225</t>
+          <t>250</t>
         </is>
       </c>
       <c r="E122" t="inlineStr">
         <is>
-          <t>220</t>
+          <t>240</t>
         </is>
       </c>
       <c r="F122" t="inlineStr">
         <is>
-          <t>230</t>
+          <t>245</t>
         </is>
       </c>
       <c r="G122" t="inlineStr">
         <is>
-          <t>216</t>
+          <t>243</t>
         </is>
       </c>
       <c r="H122" t="inlineStr">
         <is>
-          <t>Cubes of 2,3,4,5,6</t>
+          <t>Multiplied by 3</t>
         </is>
       </c>
     </row>
     <row r="123">
       <c r="A123" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="B123" t="inlineStr">
         <is>
-          <t>Find the next number: 7, 14, 28, 56, ?</t>
+          <t>Find the next term: 7, 14, 28, 56, 112, ?</t>
         </is>
       </c>
       <c r="C123" t="inlineStr">
         <is>
-          <t>110</t>
+          <t>224</t>
         </is>
       </c>
       <c r="D123" t="inlineStr">
         <is>
-          <t>112</t>
+          <t>230</t>
         </is>
       </c>
       <c r="E123" t="inlineStr">
         <is>
-          <t>120</t>
+          <t>220</t>
         </is>
       </c>
       <c r="F123" t="inlineStr">
         <is>
-          <t>114</t>
+          <t>210</t>
         </is>
       </c>
       <c r="G123" t="inlineStr">
         <is>
-          <t>112</t>
+          <t>224</t>
         </is>
       </c>
       <c r="H123" t="inlineStr">
         <is>
-          <t>Each term is multiplied by 2.</t>
+          <t>Each term ×2</t>
         </is>
       </c>
     </row>
     <row r="124">
       <c r="A124" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="B124" t="inlineStr">
         <is>
-          <t>Next in series: 1, 2, 6, 24, 120, ?</t>
+          <t>Find the next number: 2, 5, 10, 17, 26, ?</t>
         </is>
       </c>
       <c r="C124" t="inlineStr">
         <is>
-          <t>720</t>
+          <t>35</t>
         </is>
       </c>
       <c r="D124" t="inlineStr">
         <is>
-          <t>600</t>
+          <t>37</t>
         </is>
       </c>
       <c r="E124" t="inlineStr">
         <is>
-          <t>7200</t>
+          <t>38</t>
         </is>
       </c>
       <c r="F124" t="inlineStr">
         <is>
-          <t>360</t>
+          <t>40</t>
         </is>
       </c>
       <c r="G124" t="inlineStr">
         <is>
-          <t>720</t>
+          <t>37</t>
         </is>
       </c>
       <c r="H124" t="inlineStr">
         <is>
-          <t>Factorials: 1!,2!,3!,4!,5!,6!</t>
+          <t>Each term increases by consecutive odd numbers: +3, +5, +7, +9, next +11=37</t>
         </is>
       </c>
     </row>

--- a/Data/numberalphabet.xlsx
+++ b/Data/numberalphabet.xlsx
@@ -472,121 +472,121 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>What comes next? 10, 21, 43, 87, 175, ?</t>
+          <t>Find next term: GH, KL, PQ, TU, ?</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>351</t>
+          <t>YZ</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>350</t>
+          <t>WX</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>360</t>
+          <t>UV</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>355</t>
+          <t>QR</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>351</t>
+          <t>YZ</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>Each term roughly doubles plus 1</t>
+          <t>Pairs jump +4 letters.</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Next in series: ZX, VT, RP, NL, ?</t>
+          <t>Find missing letter: G, K, P, V, ?</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>JH</t>
+          <t>C</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>KF</t>
+          <t>B</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>JG</t>
+          <t>A</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>KH</t>
+          <t>Z</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>JH</t>
+          <t>A</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>Pairs move backward skipping one letter.</t>
+          <t>Increments +4, +5, +6, +7</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>21</v>
+        <v>14</v>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Find the missing term: 5, 11, 23, 47, 95, ?</t>
+          <t>Find the missing number: 7, 21, 63, 189, ?</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>191</t>
+          <t>567</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>189</t>
+          <t>560</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>193</t>
+          <t>570</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>185</t>
+          <t>600</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>191</t>
+          <t>567</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>Each term roughly doubles minus 1</t>
+          <t>Each term ×3</t>
         </is>
       </c>
     </row>
@@ -596,277 +596,277 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Find next letter: Y, V, R, M, ?</t>
+          <t>Find the missing number: 4, 12, 36, 108, ?</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>H</t>
+          <t>324</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>I</t>
+          <t>300</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>J</t>
+          <t>350</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>G</t>
+          <t>320</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>H</t>
+          <t>324</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>Decreases by 3,4,5,6 letters</t>
+          <t>Each term ×3</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>21</v>
+        <v>13</v>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Find missing term: EF, IJ, MN, ST, ?</t>
+          <t>Next number: 5, 10, 20, 40, 80, ?</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>YZ</t>
+          <t>160</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>WX</t>
+          <t>180</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>UV</t>
+          <t>150</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>QR</t>
+          <t>140</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>YZ</t>
+          <t>160</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>Pairs jump +4 letters.</t>
+          <t>Each term ×2.</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>11</v>
+        <v>20</v>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>What comes next: 3, 6, 12, 24, 48, ?</t>
+          <t>Find the next number: 3, 5, 9, 17, 33, ?</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>96</t>
+          <t>65</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>100</t>
+          <t>63</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>90</t>
+          <t>60</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>98</t>
+          <t>70</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>96</t>
+          <t>65</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>Each term multiplied by 2</t>
+          <t>Each term roughly double minus 1</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>18</v>
+        <v>14</v>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>What comes next: UVW, XYZ, ABC, DEF, ?</t>
+          <t>What comes next: ZYX, WVU, TSR, QPO, ?</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>GHI</t>
+          <t>NML</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>JKL</t>
+          <t>KJI</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>MNO</t>
+          <t>HGF</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>PQR</t>
+          <t>EDC</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>GHI</t>
+          <t>NML</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>Triplets shift +3 letters cyclically.</t>
+          <t>Triplets decrease by 3 letters.</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>11</v>
+        <v>4</v>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Find next term: LM, OP, ST, WX, ?</t>
+          <t>Find the next term: 1, 3, 7, 15, 31, ?</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>AB</t>
+          <t>63</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>YZ</t>
+          <t>65</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>UV</t>
+          <t>61</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>YZ</t>
+          <t>67</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>AB</t>
+          <t>63</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>Pairs move +3 letters; after WX comes AB.</t>
+          <t>Each term = previous × 2 + 1</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>What comes next: ABC, DEF, GHI, JKL, ?</t>
+          <t>Find the missing letter: B, D, G, K, P, ?</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>MNO</t>
+          <t>V</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>PQR</t>
+          <t>U</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>STU</t>
+          <t>T</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>VWX</t>
+          <t>S</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>MNO</t>
+          <t>V</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>Triplets progress in alphabetical order.</t>
+          <t>Difference in positions: +2,+3,+4,+5,+6</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>25</v>
+        <v>6</v>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Find missing term: UV, YZ, DE, HI, ?</t>
+          <t>Find the next term: PQ, RS, TU, WX, ?</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>LM</t>
+          <t>YZ</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>OP</t>
+          <t>ZA</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>QR</t>
+          <t>AB</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>ST</t>
+          <t>BC</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>LM</t>
+          <t>YZ</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>Pairs jump +4 letters cyclically.</t>
+          <t>Pairs move sequentially in alphabets; after WX is YZ.</t>
         </is>
       </c>
     </row>
@@ -876,317 +876,317 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Find missing letter: D, G, K, P, ?</t>
+          <t>Find next number: 6, 12, 24, 48, 96, ?</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>V</t>
+          <t>192</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>U</t>
+          <t>190</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>T</t>
+          <t>195</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>S</t>
+          <t>185</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>V</t>
+          <t>192</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>Increasing by 3,4,5,6 letters.</t>
+          <t>Each term multiplied by 2</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>14</v>
+        <v>2</v>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Find the missing letter: Z, W, S, N, ?</t>
+          <t>Find the missing term: XYZ, UVW, RST, OPQ, ?</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>I</t>
+          <t>LMN</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>H</t>
+          <t>NOP</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>J</t>
+          <t>KLM</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>K</t>
+          <t>JKL</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>I</t>
+          <t>LMN</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>Decreasing by 3,4,5,6 letters</t>
+          <t>Each triple moves backward by 3 letters.</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>16</v>
+        <v>8</v>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Find next letter: C, F, J, O, ?</t>
+          <t>What comes next: 5, 15, 45, 135, ?</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>U</t>
+          <t>405</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>V</t>
+          <t>400</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>W</t>
+          <t>410</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>420</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>U</t>
+          <t>405</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>Increments +3, +4, +5, +6</t>
+          <t>Multiplied by 3</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>2</v>
+        <v>11</v>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Find the missing number: 3, 9, 27, 81, ?</t>
+          <t>Find next term: 1, 3, 6, 10, 15, ?</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>243</t>
+          <t>21</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>256</t>
+          <t>22</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>225</t>
+          <t>20</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>270</t>
+          <t>23</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>243</t>
+          <t>21</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>Each term multiplied by 3.</t>
+          <t>Triangular numbers.</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>15</v>
+        <v>9</v>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Find next number: 4, 9, 19, 39, 79, ?</t>
+          <t>Next in series: 11, 13, 17, 19, 23, ?</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>159</t>
+          <t>29</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>149</t>
+          <t>31</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>169</t>
+          <t>28</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>179</t>
+          <t>27</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>159</t>
+          <t>29</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>Each term roughly doubles minus 1</t>
+          <t>Prime numbers in order</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>10</v>
+        <v>14</v>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Find missing number: 4, 9, 19, 39, 79, ?</t>
+          <t>Find the missing letter: Z, W, S, N, ?</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>159</t>
+          <t>I</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>169</t>
+          <t>H</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>149</t>
+          <t>J</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>179</t>
+          <t>K</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>159</t>
+          <t>I</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>Each term approximately doubles minus 1.</t>
+          <t>Decreasing by 3,4,5,6 letters</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>What letter comes next? C, F, J, O, ?</t>
+          <t>Find the next term: 2, 3, 5, 8, 12, 17, ?</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>U</t>
+          <t>23</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>T</t>
+          <t>25</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>S</t>
+          <t>24</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>R</t>
+          <t>26</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>U</t>
+          <t>23</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>Difference in positions: +3,+4,+5,+6</t>
+          <t>Difference increases by 1: +1,+2,+3,+4,+5</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>What comes next: 2, 6, 12, 20, 30, ?</t>
+          <t>Find the next number: 7, 14, 28, 56, ?</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>42</t>
+          <t>110</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>40</t>
+          <t>112</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>44</t>
+          <t>120</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>48</t>
+          <t>114</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>42</t>
+          <t>112</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>Pattern n(n+1), next term 6×7=42.</t>
+          <t>Each term is multiplied by 2.</t>
         </is>
       </c>
     </row>
@@ -1232,601 +1232,601 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Next in series: ABC, DEF, GHI, JKL, ?</t>
+          <t>Next letter: A, C, F, J, O, ?</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>MNO</t>
+          <t>U</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>PQR</t>
+          <t>T</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>STU</t>
+          <t>S</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>VWX</t>
+          <t>V</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>MNO</t>
+          <t>U</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>Triplets progress alphabetically.</t>
+          <t>Incrementing by increasing letters.</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>10</v>
+        <v>18</v>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>What comes next: ABC, BCD, CDE, DEF, ?</t>
+          <t>Find missing term: 8, 27, 64, 125, 216, ?</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>EFG</t>
+          <t>343</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>FGH</t>
+          <t>350</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>GHI</t>
+          <t>330</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>HIJ</t>
+          <t>300</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>EFG</t>
+          <t>343</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>Each triplet shifts by one letter forward.</t>
+          <t>Cubes</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>9</v>
+        <v>24</v>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>Next in series: 11, 13, 17, 19, 23, ?</t>
+          <t>Find next letter: B, E, I, N, ?</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>29</t>
+          <t>T</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>31</t>
+          <t>U</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>28</t>
+          <t>S</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>27</t>
+          <t>R</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>29</t>
+          <t>T</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>Prime numbers in order</t>
+          <t>Differences +3,+4,+5,+6</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>What comes next: 2, 6, 18, 54, 162, ?</t>
+          <t>Find next number: 5, 15, 45, 135, ?</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>486</t>
+          <t>405</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>500</t>
+          <t>420</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>490</t>
+          <t>400</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>480</t>
+          <t>410</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>486</t>
+          <t>405</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>Each term ×3</t>
+          <t>Multiply by 3</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>12</v>
+        <v>24</v>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>Find missing number: 6, 11, 21, 36, 56, ?</t>
+          <t>Next in series: ABC, DEF, GHI, JKL, ?</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>81</t>
+          <t>MNO</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>80</t>
+          <t>PQR</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>85</t>
+          <t>STU</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>75</t>
+          <t>VWX</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>81</t>
+          <t>MNO</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>Add increasing numbers +5,+10,+15,...</t>
+          <t>Triplets progress alphabetically.</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>22</v>
+        <v>8</v>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>What comes next? E, G, J, N, ?</t>
+          <t>What is next? 1, 4, 9, 16, 25, ?</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>S</t>
+          <t>36</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>T</t>
+          <t>49</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>R</t>
+          <t>30</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Q</t>
+          <t>42</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>S</t>
+          <t>36</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>Increments +2,+3,+4,+5</t>
+          <t>Perfect squares</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>17</v>
+        <v>1</v>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>Next letter: F, K, P, U, ?</t>
+          <t>Find the next number: 2, 12, 36, 80, 150, ?</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Z</t>
+          <t>252</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>Y</t>
+          <t>200</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>240</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>W</t>
+          <t>300</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Z</t>
+          <t>252</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>Increasing by 5 letters each time.</t>
+          <t>Pattern: n³ - n, for n=2,3,4,5,6 → 6³-6=216-6=210 (adjusted here as 252)</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>Next number: 5, 10, 20, 40, 80, ?</t>
+          <t>Next in series: ABC, EFG, IJK, MNO, ?</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>160</t>
+          <t>QRS</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>180</t>
+          <t>TUV</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>150</t>
+          <t>WXY</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>140</t>
+          <t>ZAB</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>160</t>
+          <t>QRS</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>Each term ×2.</t>
+          <t>Triplets jump +4 letters each time.</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>What comes next: 3, 8, 15, 24, 35, ?</t>
+          <t>Find the next number: 2, 5, 10, 17, 26, ?</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>48</t>
+          <t>35</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>49</t>
+          <t>37</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>50</t>
+          <t>38</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>55</t>
+          <t>40</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>48</t>
+          <t>37</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>Each term = n² + n, n=1,2,3,...</t>
+          <t>Each term increases by consecutive odd numbers: +3, +5, +7, +9, next +11=37</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>8</v>
+        <v>22</v>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>Find missing number: 1, 3, 7, 15, 31, ?</t>
+          <t>What comes next: 2, 6, 10, 14, 18, ?</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>63</t>
+          <t>22</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>64</t>
+          <t>24</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>65</t>
+          <t>20</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>62</t>
+          <t>23</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>63</t>
+          <t>22</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>Each term = previous ×2 +1</t>
+          <t>Increments of 4</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>What comes next: 1, 2, 6, 24, 120, ?</t>
+          <t>What is the next term? 3, 6, 12, 24, 48, ?</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>720</t>
+          <t>96</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>600</t>
+          <t>90</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>7200</t>
+          <t>100</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>700</t>
+          <t>108</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>720</t>
+          <t>96</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>Factorials 1!, 2!, 3!, 4!, 5!, 6!</t>
+          <t>Each term ×2</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>Find the next term: PQ, RS, TU, WX, ?</t>
+          <t>Find missing number: 5, 10, 20, 40, 80, ?</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>YZ</t>
+          <t>160</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>ZA</t>
+          <t>150</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>AB</t>
+          <t>140</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>BC</t>
+          <t>170</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>YZ</t>
+          <t>160</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>Pairs move sequentially in alphabets; after WX is YZ.</t>
+          <t>Each term doubles</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>11</v>
+        <v>4</v>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>Find next number: 7, 14, 28, 56, ?</t>
+          <t>What comes next? KL, NO, ST, WX, ?</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>112</t>
+          <t>BD</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>110</t>
+          <t>YZ</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>114</t>
+          <t>AB</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>120</t>
+          <t>CD</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>112</t>
+          <t>AB</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>Each term ×2</t>
+          <t>Letters move in pairs skipping one letter; after WX comes AB.</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>5</v>
+        <v>16</v>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>Next letter: A, D, H, M, S, ?</t>
+          <t>Find next letter: C, F, J, O, ?</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Z</t>
+          <t>U</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>Y</t>
+          <t>V</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
         <is>
+          <t>W</t>
+        </is>
+      </c>
+      <c r="F34" t="inlineStr">
+        <is>
           <t>X</t>
         </is>
       </c>
-      <c r="F34" t="inlineStr">
-        <is>
-          <t>W</t>
-        </is>
-      </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Z</t>
+          <t>U</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>Increments +3, +4, +5, +6, +7</t>
+          <t>Increments +3, +4, +5, +6</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>Find the next term: 2, 3, 5, 8, 12, 17, ?</t>
+          <t>What comes next: Z, X, U, Q, L, ?</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>23</t>
+          <t>F</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>25</t>
+          <t>G</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>24</t>
+          <t>H</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>26</t>
+          <t>I</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>23</t>
+          <t>F</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>Difference increases by 1: +1,+2,+3,+4,+5</t>
+          <t>Alphabet positions decrease by 2,3,4,5,6.</t>
         </is>
       </c>
     </row>
@@ -1836,117 +1836,117 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>What comes next: 4, 9, 19, 39, 79, ?</t>
+          <t>What comes next: 2, 6, 12, 20, 30, ?</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>159</t>
+          <t>42</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>149</t>
+          <t>40</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>169</t>
+          <t>44</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>179</t>
+          <t>48</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>159</t>
+          <t>42</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>Each term nearly doubles minus 1</t>
+          <t>Pattern n(n+1), next term 6×7=42.</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>Next letter: B, D, G, K, P, ?</t>
+          <t>Next in series: 1, 2, 6, 24, 120, ?</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>V</t>
+          <t>720</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>W</t>
+          <t>600</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>U</t>
+          <t>7200</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>T</t>
+          <t>360</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>V</t>
+          <t>720</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>Incrementing letter positions +2,+3,+4,+5,+6.</t>
+          <t>Factorials: 1!,2!,3!,4!,5!,6!</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>14</v>
+        <v>18</v>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>What comes next: ZYX, WVU, TSR, QPO, ?</t>
+          <t>Find missing letter: A, C, F, J, ?</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>NML</t>
+          <t>O</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>KJI</t>
+          <t>N</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>HGF</t>
+          <t>P</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>EDC</t>
+          <t>Q</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>NML</t>
+          <t>O</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>Triplets decrease by 3 letters.</t>
+          <t>Increments +2, +3, +4, +5</t>
         </is>
       </c>
     </row>
@@ -1992,451 +1992,451 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>19</v>
+        <v>6</v>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>Find the next term: DE, GH, KL, OP, ?</t>
+          <t>Find missing number: 2, 5, 10, 17, 26, ?</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>ST</t>
+          <t>37</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>UV</t>
+          <t>40</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>WX</t>
+          <t>42</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>YZ</t>
+          <t>35</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>ST</t>
+          <t>37</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>Pairs jump +4 letters.</t>
+          <t>Add consecutive odd numbers +3,+5,+7,...</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>15</v>
+        <v>5</v>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>What comes next: 11, 13, 17, 19, 23, ?</t>
+          <t>Find the next term: 7, 14, 28, 56, 112, ?</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>29</t>
+          <t>224</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>27</t>
+          <t>230</t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>31</t>
+          <t>220</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>25</t>
+          <t>210</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>29</t>
+          <t>224</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>Prime numbers in order.</t>
+          <t>Each term ×2</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>Find the next number: 3, 5, 9, 17, 33, ?</t>
+          <t>What comes next: 1, 2, 6, 24, 120, ?</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>65</t>
+          <t>720</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>63</t>
+          <t>600</t>
         </is>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>60</t>
+          <t>7200</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>70</t>
+          <t>700</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>65</t>
+          <t>720</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>Each term roughly double minus 1</t>
+          <t>Factorials 1!, 2!, 3!, 4!, 5!, 6!</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>6</v>
+        <v>21</v>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>What comes next: Z, X, U, Q, L, ?</t>
+          <t>What comes next: 10, 21, 43, 87, 175, ?</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>F</t>
+          <t>351</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>G</t>
+          <t>350</t>
         </is>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>H</t>
+          <t>360</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>I</t>
+          <t>355</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>F</t>
+          <t>351</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>Alphabet positions decrease by 2,3,4,5,6.</t>
+          <t>Each term doubles minus 1</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>Find the missing number: 7, 21, 63, 189, ?</t>
+          <t>Find next term: LM, OP, ST, WX, ?</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>567</t>
+          <t>AB</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>560</t>
+          <t>YZ</t>
         </is>
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>570</t>
+          <t>UV</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>600</t>
+          <t>YZ</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>567</t>
+          <t>AB</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>Each term ×3</t>
+          <t>Pairs move +3 letters; after WX comes AB.</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>What comes next: 2, 6, 10, 14, 18, ?</t>
+          <t>Next number in series: 1, 2, 6, 24, 120, ?</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>22</t>
+          <t>720</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>24</t>
+          <t>600</t>
         </is>
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>7200</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>23</t>
+          <t>72000</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>22</t>
+          <t>720</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>Increments of 4</t>
+          <t>Factorials: 1!, 2!, 3!, 4!, 5!, 6!</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>8</v>
+        <v>25</v>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>Find missing term: FG, IJ, MN, QR, ?</t>
+          <t>What comes next: 6, 24, 60, 120, 210, ?</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>UV</t>
+          <t>336</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>ST</t>
+          <t>350</t>
         </is>
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>WX</t>
+          <t>340</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>YZ</t>
+          <t>320</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>UV</t>
+          <t>336</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>Pairs jump +4 letters each time.</t>
+          <t>Pattern n(n+1)(n+2)/6 for n=2,3,4,5,6,7</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>Find the missing letter: P, M, J, G, ?</t>
+          <t>Find the missing letter: C, F, J, O, ?</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>U</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>V</t>
         </is>
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>E</t>
+          <t>W</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>F</t>
+          <t>X</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>U</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>Decreasing by 3 letters.</t>
+          <t>Incrementing by +3,+4,+5,+6.</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>23</v>
+        <v>7</v>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>Find next term: GH, KL, PQ, TU, ?</t>
+          <t>Find the missing letter: Z, X, U, Q, L, ?</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>YZ</t>
+          <t>F</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>WX</t>
+          <t>G</t>
         </is>
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>UV</t>
+          <t>H</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>QR</t>
+          <t>I</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>YZ</t>
+          <t>F</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>Pairs jump +4 letters.</t>
+          <t>Positions decrease by 2,3,4,5,6</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>6</v>
+        <v>19</v>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>Find missing number: 2, 5, 10, 17, 26, ?</t>
+          <t>What comes next: 8, 27, 64, 125, ?</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>37</t>
+          <t>216</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>40</t>
+          <t>225</t>
         </is>
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>42</t>
+          <t>200</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>35</t>
+          <t>230</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>37</t>
+          <t>216</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>Add consecutive odd numbers +3,+5,+7,...</t>
+          <t>Cubes of 2,3,4,5,6.</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>1</v>
+        <v>17</v>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>What comes next in the series? 2, 6, 12, 20, 30, ?</t>
+          <t>Find missing number: 3, 9, 27, 81, ?</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>40</t>
+          <t>243</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>42</t>
+          <t>250</t>
         </is>
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>44</t>
+          <t>240</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>36</t>
+          <t>245</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>42</t>
+          <t>243</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>Each term is n(n+1); next: 6×7=42</t>
+          <t>Multiplied by 3</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>Find the missing letter: B, D, G, K, P, ?</t>
+          <t>Next letter: B, D, G, K, P, ?</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
@@ -2446,19 +2446,19 @@
       </c>
       <c r="D51" t="inlineStr">
         <is>
+          <t>W</t>
+        </is>
+      </c>
+      <c r="E51" t="inlineStr">
+        <is>
           <t>U</t>
         </is>
       </c>
-      <c r="E51" t="inlineStr">
+      <c r="F51" t="inlineStr">
         <is>
           <t>T</t>
         </is>
       </c>
-      <c r="F51" t="inlineStr">
-        <is>
-          <t>S</t>
-        </is>
-      </c>
       <c r="G51" t="inlineStr">
         <is>
           <t>V</t>
@@ -2466,842 +2466,842 @@
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>Difference in positions: +2,+3,+4,+5,+6</t>
+          <t>Incrementing letter positions +2,+3,+4,+5,+6.</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>18</v>
+        <v>9</v>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>Find the missing number: 2, 6, 12, 20, 30, ?</t>
+          <t>Next in series: ZX, VT, RP, NL, ?</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>40</t>
+          <t>JH</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>42</t>
+          <t>KF</t>
         </is>
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>44</t>
+          <t>JG</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>36</t>
+          <t>KH</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>42</t>
+          <t>JH</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>Using formula n(n+1).</t>
+          <t>Pairs move backward skipping one letter.</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>4</v>
+        <v>15</v>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>Next in series: 1, 2, 6, 24, 120, ?</t>
+          <t>Find next term: BC, DE, GH, KL, ?</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>720</t>
+          <t>OP</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>600</t>
+          <t>MN</t>
         </is>
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>7200</t>
+          <t>QR</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>360</t>
+          <t>ST</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>720</t>
+          <t>OP</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>Factorials: 1!,2!,3!,4!,5!,6!</t>
+          <t>Pairs jump increasing letters.</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>12</v>
+        <v>7</v>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>Find the missing letter: C, F, J, O, ?</t>
+          <t>What comes next: ABC, DEF, GHI, JKL, ?</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>U</t>
+          <t>MNO</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>V</t>
+          <t>PQR</t>
         </is>
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>W</t>
+          <t>STU</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>VWX</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>U</t>
+          <t>MNO</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>Incrementing by +3,+4,+5,+6.</t>
+          <t>Triplets progress in alphabetical order.</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>23</v>
+        <v>3</v>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>What comes next: 5, 11, 23, 47, 95, ?</t>
+          <t>Next in series: AZ, CY, EX, GV, ?</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>191</t>
+          <t>IT</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>189</t>
+          <t>HS</t>
         </is>
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>193</t>
+          <t>JU</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>185</t>
+          <t>KT</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>191</t>
+          <t>IT</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>Doubling minus 1.</t>
+          <t>First letters move +2, second letters -2; IT follows pattern.</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>Find missing letter: A, C, F, J, ?</t>
+          <t>Next in series: RST, UVW, XYZ, ABC, ?</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>DEF</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>GHI</t>
         </is>
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>P</t>
+          <t>JKL</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Q</t>
+          <t>MNO</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>DEF</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>Increments +2, +3, +4, +5</t>
+          <t>Triplets shift +3 letters cyclically.</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>What is next? 1, 4, 9, 16, 25, ?</t>
+          <t>Next in series: UVW, RST, OPQ, LMN, ?</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>36</t>
+          <t>IJK</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>49</t>
+          <t>HIJ</t>
         </is>
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>30</t>
+          <t>FGH</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>42</t>
+          <t>GHI</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>36</t>
+          <t>IJK</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>Perfect squares</t>
+          <t>Triplets move backward by 3 letters.</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>7</v>
+        <v>25</v>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>What comes next: 4, 9, 16, 25, 36, ?</t>
+          <t>What comes next? 10, 21, 43, 87, 175, ?</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>49</t>
+          <t>351</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>48</t>
+          <t>350</t>
         </is>
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>50</t>
+          <t>360</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>51</t>
+          <t>355</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>49</t>
+          <t>351</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>Perfect squares</t>
+          <t>Each term roughly doubles plus 1</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>What comes next: 6, 24, 60, 120, 210, ?</t>
+          <t>Find missing letter: F, K, P, U, ?</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>336</t>
+          <t>Z</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>350</t>
+          <t>Y</t>
         </is>
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>340</t>
+          <t>X</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>320</t>
+          <t>W</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>336</t>
+          <t>Z</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>Pattern n(n+1)(n+2)/6 for n=2,3,4,5,6,7</t>
+          <t>Increments +5 each time</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>16</v>
+        <v>12</v>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>Next in series: ABC, EFG, IJK, MNO, ?</t>
+          <t>Find missing letter: G, J, N, S, ?</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>QRS</t>
+          <t>Y</t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>TUV</t>
+          <t>Z</t>
         </is>
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>WXY</t>
+          <t>X</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>ZAB</t>
+          <t>W</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>QRS</t>
+          <t>Y</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>Triplets jump +4 letters each time.</t>
+          <t>Difference: +3,+4,+5,+6</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>12</v>
+        <v>3</v>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>Next in series: UVW, RST, OPQ, LMN, ?</t>
+          <t>What is the next term? A, D, I, P, ?</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>IJK</t>
+          <t>Y</t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>HIJ</t>
+          <t>Z</t>
         </is>
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>FGH</t>
+          <t>W</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>GHI</t>
+          <t>X</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>IJK</t>
+          <t>Y</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>Triplets move backward by 3 letters.</t>
+          <t>Positions are squares: 1,4,9,16,25 → A,E,I,P,Y</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>Find the next term: 1, 3, 7, 15, 31, ?</t>
+          <t>Find the missing term: 2, 3, 5, 9, 17, ?</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>63</t>
+          <t>33</t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>65</t>
+          <t>31</t>
         </is>
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>61</t>
+          <t>34</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>67</t>
+          <t>30</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>63</t>
+          <t>33</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>Each term = previous × 2 + 1</t>
+          <t>Each term after 2 is previous term ×2 -1.</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>Next number in series: 1, 2, 6, 24, 120, ?</t>
+          <t>Find the missing term: 5, 11, 23, 47, 95, ?</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>720</t>
+          <t>191</t>
         </is>
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>600</t>
+          <t>189</t>
         </is>
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>7200</t>
+          <t>193</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>72000</t>
+          <t>185</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>720</t>
+          <t>191</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>Factorials: 1!, 2!, 3!, 4!, 5!, 6!</t>
+          <t>Each term roughly doubles minus 1</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>13</v>
+        <v>20</v>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>Next number: 1, 4, 9, 16, 25, ?</t>
+          <t>Find missing letter: D, G, K, P, ?</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>36</t>
+          <t>V</t>
         </is>
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>49</t>
+          <t>U</t>
         </is>
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>30</t>
+          <t>T</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>42</t>
+          <t>S</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>36</t>
+          <t>V</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>Squares of natural numbers</t>
+          <t>Increasing by 3,4,5,6 letters.</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>24</v>
+        <v>11</v>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>Find next letter: B, E, I, N, ?</t>
+          <t>What comes next: 3, 6, 12, 24, 48, ?</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>T</t>
+          <t>96</t>
         </is>
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>U</t>
+          <t>90</t>
         </is>
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>S</t>
+          <t>100</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>R</t>
+          <t>110</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>T</t>
+          <t>96</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>Differences +3,+4,+5,+6</t>
+          <t>Each term doubles</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>22</v>
+        <v>11</v>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>Find the missing letter: Z, W, S, N, ?</t>
+          <t>Find next number: 7, 14, 28, 56, ?</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>I</t>
+          <t>112</t>
         </is>
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>J</t>
+          <t>110</t>
         </is>
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>H</t>
+          <t>114</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>K</t>
+          <t>120</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>I</t>
+          <t>112</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>Decreasing by 3,4,5,6 letters.</t>
+          <t>Each term ×2</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>10</v>
+        <v>21</v>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>Find next letter: P, M, J, G, ?</t>
+          <t>Next number: 3, 9, 27, 81, ?</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>243</t>
         </is>
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>256</t>
         </is>
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>225</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>E</t>
+          <t>270</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>243</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>Decreasing by 3 letters</t>
+          <t>Multiplying by 3.</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>11</v>
+        <v>18</v>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>What comes next: 3, 6, 12, 24, 48, ?</t>
+          <t>What comes next: UVW, XYZ, ABC, DEF, ?</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>96</t>
+          <t>GHI</t>
         </is>
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>90</t>
+          <t>JKL</t>
         </is>
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>100</t>
+          <t>MNO</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>110</t>
+          <t>PQR</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>96</t>
+          <t>GHI</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>Each term doubles</t>
+          <t>Triplets shift +3 letters cyclically.</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>5</v>
+        <v>14</v>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>Find missing term: CDE, FGH, KLM, PQR, ?</t>
+          <t>Find next letter: D, G, K, P, ?</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>VWX</t>
+          <t>V</t>
         </is>
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>STU</t>
+          <t>W</t>
         </is>
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>XYZ</t>
+          <t>U</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>UVW</t>
+          <t>T</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>VWX</t>
+          <t>V</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>Triplets jump by +3 letters each time.</t>
+          <t>Increments +3, +4, +5, +6</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>1</v>
+        <v>15</v>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>What comes next in the series? AB, DE, IJ, OP, ?</t>
+          <t>What comes next: 11, 13, 17, 19, 23, ?</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>UV</t>
+          <t>29</t>
         </is>
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>ST</t>
+          <t>27</t>
         </is>
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>WX</t>
+          <t>31</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>YZ</t>
+          <t>25</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>UV</t>
+          <t>29</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>Each pair skips increasing letters: +3,+4,+5,+6 between first letters.</t>
+          <t>Prime numbers in order.</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>3</v>
+        <v>20</v>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>Find missing number: 5, 10, 20, 40, 80, ?</t>
+          <t>Find next letter: Z, V, Q, K, ?</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>160</t>
+          <t>B</t>
         </is>
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>150</t>
+          <t>F</t>
         </is>
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>140</t>
+          <t>E</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>170</t>
+          <t>C</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>160</t>
+          <t>F</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>Each term doubles</t>
+          <t>Difference in positions: -4, -5, -6, -7</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>What comes next: 10, 21, 43, 87, 175, ?</t>
+          <t>Find missing number: 9, 19, 39, 79, 159, ?</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>351</t>
+          <t>319</t>
         </is>
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>350</t>
+          <t>310</t>
         </is>
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>360</t>
+          <t>320</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>355</t>
+          <t>300</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>351</t>
+          <t>319</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
@@ -3312,241 +3312,241 @@
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>2</v>
+        <v>24</v>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>Find the missing term: XYZ, UVW, RST, OPQ, ?</t>
+          <t>Find next letter: Y, V, R, M, ?</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>LMN</t>
+          <t>H</t>
         </is>
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>NOP</t>
+          <t>I</t>
         </is>
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>KLM</t>
+          <t>J</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>JKL</t>
+          <t>G</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>LMN</t>
+          <t>H</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>Each triple moves backward by 3 letters.</t>
+          <t>Decreases by 3,4,5,6 letters</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>17</v>
+        <v>22</v>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>Find next term: 1, 3, 6, 10, 15, ?</t>
+          <t>Find the missing letter: Z, W, S, N, ?</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>21</t>
+          <t>I</t>
         </is>
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>22</t>
+          <t>J</t>
         </is>
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>H</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>23</t>
+          <t>K</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>21</t>
+          <t>I</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>Triangular numbers</t>
+          <t>Decreasing by 3,4,5,6 letters.</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>16</v>
+        <v>23</v>
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>Find next number: 5, 15, 45, 135, ?</t>
+          <t>Find the next number: 17, 19, 23, 29, 31, ?</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>405</t>
+          <t>37</t>
         </is>
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>420</t>
+          <t>35</t>
         </is>
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>400</t>
+          <t>36</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>410</t>
+          <t>38</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>405</t>
+          <t>37</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>Multiply by 3</t>
+          <t>Prime numbers</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>18</v>
+        <v>9</v>
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>What comes next: 13, 21, 34, 55, 89, ?</t>
+          <t>Find missing number: 2, 4, 8, 14, 22, ?</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>144</t>
+          <t>32</t>
         </is>
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>135</t>
+          <t>30</t>
         </is>
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>140</t>
+          <t>34</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>150</t>
+          <t>36</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>144</t>
+          <t>32</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>Fibonacci sequence</t>
+          <t>Incrementing differences: +2, +4, +6, +8, next +10=32</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>Find the missing number: 3, 9, 27, ?, 243</t>
+          <t>What comes next in the series? 2, 6, 12, 20, 30, ?</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>54</t>
+          <t>40</t>
         </is>
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>81</t>
+          <t>42</t>
         </is>
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>72</t>
+          <t>44</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>90</t>
+          <t>36</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>81</t>
+          <t>42</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>Each term multiplied by 3; 27×3=81</t>
+          <t>Each term is n(n+1); next: 6×7=42</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>24</v>
+        <v>3</v>
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>Find the missing number: 4, 12, 36, 108, ?</t>
+          <t>What comes next: 4, 9, 19, 39, 79, ?</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>324</t>
+          <t>159</t>
         </is>
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>300</t>
+          <t>149</t>
         </is>
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>350</t>
+          <t>169</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>320</t>
+          <t>179</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>324</t>
+          <t>159</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>Each term ×3</t>
+          <t>Each term nearly doubles minus 1</t>
         </is>
       </c>
     </row>
@@ -3556,1837 +3556,1837 @@
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>Find missing letter: G, K, P, V, ?</t>
+          <t>Find missing number: 6, 11, 21, 36, 56, ?</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>81</t>
         </is>
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>80</t>
         </is>
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>85</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Z</t>
+          <t>75</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>81</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>Increments +4, +5, +6, +7</t>
+          <t>Add increasing numbers +5,+10,+15,...</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="n">
-        <v>21</v>
+        <v>18</v>
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>Find missing letter: F, K, P, U, ?</t>
+          <t>Find the missing number: 2, 6, 12, 20, 30, ?</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>Z</t>
+          <t>40</t>
         </is>
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>Y</t>
+          <t>42</t>
         </is>
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>44</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>W</t>
+          <t>36</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>Z</t>
+          <t>42</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>Increments +5 each time</t>
+          <t>Using formula n(n+1).</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="n">
-        <v>18</v>
+        <v>5</v>
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>Find missing term: 8, 27, 64, 125, 216, ?</t>
+          <t>What comes next? 121, 144, 169, 196, ?</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>343</t>
+          <t>225</t>
         </is>
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>350</t>
+          <t>240</t>
         </is>
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>330</t>
+          <t>256</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>300</t>
+          <t>289</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>343</t>
+          <t>225</t>
         </is>
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>Cubes</t>
+          <t>Squares of 11,12,13,14,15</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="n">
-        <v>6</v>
+        <v>11</v>
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>Find next number: 5, 10, 20, 40, 80, ?</t>
+          <t>What comes next: 3, 6, 12, 24, 48, ?</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>160</t>
+          <t>96</t>
         </is>
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>180</t>
+          <t>100</t>
         </is>
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>150</t>
+          <t>90</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>200</t>
+          <t>98</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>160</t>
+          <t>96</t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>Each term ×2</t>
+          <t>Each term multiplied by 2</t>
         </is>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="n">
-        <v>13</v>
+        <v>8</v>
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>What is the next term? 3, 6, 12, 24, 48, ?</t>
+          <t>Find missing term: FG, IJ, MN, QR, ?</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>96</t>
+          <t>UV</t>
         </is>
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>90</t>
+          <t>ST</t>
         </is>
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>100</t>
+          <t>WX</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>108</t>
+          <t>YZ</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>96</t>
+          <t>UV</t>
         </is>
       </c>
       <c r="H83" t="inlineStr">
         <is>
-          <t>Each term ×2</t>
+          <t>Pairs jump +4 letters each time.</t>
         </is>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="n">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>Find next term: 1, 3, 6, 10, 15, ?</t>
+          <t>Find the missing letter: P, M, J, G, ?</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>21</t>
+          <t>D</t>
         </is>
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>22</t>
+          <t>C</t>
         </is>
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>E</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>23</t>
+          <t>F</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>21</t>
+          <t>D</t>
         </is>
       </c>
       <c r="H84" t="inlineStr">
         <is>
-          <t>Triangular numbers.</t>
+          <t>Decreasing by 3 letters.</t>
         </is>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="n">
-        <v>17</v>
+        <v>23</v>
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>Find missing term: JK, NO, RS, VW, ?</t>
+          <t>What comes next: 5, 11, 23, 47, 95, ?</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>BC</t>
+          <t>191</t>
         </is>
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t>YZ</t>
+          <t>189</t>
         </is>
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>XY</t>
+          <t>193</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>ZA</t>
+          <t>185</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>BC</t>
+          <t>191</t>
         </is>
       </c>
       <c r="H85" t="inlineStr">
         <is>
-          <t>Pairs jump +4 letters.</t>
+          <t>Doubling minus 1.</t>
         </is>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="n">
-        <v>14</v>
+        <v>21</v>
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>Find next letter: D, G, K, P, ?</t>
+          <t>Find missing term: EF, IJ, MN, ST, ?</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>V</t>
+          <t>YZ</t>
         </is>
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t>W</t>
+          <t>WX</t>
         </is>
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>U</t>
+          <t>UV</t>
         </is>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>T</t>
+          <t>QR</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>V</t>
+          <t>YZ</t>
         </is>
       </c>
       <c r="H86" t="inlineStr">
         <is>
-          <t>Increments +3, +4, +5, +6</t>
+          <t>Pairs jump +4 letters.</t>
         </is>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="n">
-        <v>4</v>
+        <v>16</v>
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>Find the missing letter: A, C, F, J, O, ?</t>
+          <t>Find missing term: 7, 14, 28, 56, 112, ?</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>U</t>
+          <t>224</t>
         </is>
       </c>
       <c r="D87" t="inlineStr">
         <is>
-          <t>T</t>
+          <t>226</t>
         </is>
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>S</t>
+          <t>230</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>V</t>
+          <t>220</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>U</t>
+          <t>224</t>
         </is>
       </c>
       <c r="H87" t="inlineStr">
         <is>
-          <t>Alphabet position increments +2,+3,+4,+5,+6.</t>
+          <t>Each term ×2.</t>
         </is>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="n">
-        <v>3</v>
+        <v>10</v>
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>What is the next term? A, D, I, P, ?</t>
+          <t>What letter comes next? C, F, J, O, ?</t>
         </is>
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>Y</t>
+          <t>U</t>
         </is>
       </c>
       <c r="D88" t="inlineStr">
         <is>
-          <t>Z</t>
+          <t>T</t>
         </is>
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>W</t>
+          <t>S</t>
         </is>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>R</t>
         </is>
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>Y</t>
+          <t>U</t>
         </is>
       </c>
       <c r="H88" t="inlineStr">
         <is>
-          <t>Positions are squares: 1,4,9,16,25 → A,E,I,P,Y</t>
+          <t>Difference in positions: +3,+4,+5,+6</t>
         </is>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>Find the next number: 1, 8, 27, 64, ?</t>
+          <t>Find next letter: P, M, J, G, ?</t>
         </is>
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>125</t>
+          <t>D</t>
         </is>
       </c>
       <c r="D89" t="inlineStr">
         <is>
-          <t>130</t>
+          <t>C</t>
         </is>
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>120</t>
+          <t>B</t>
         </is>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>135</t>
+          <t>E</t>
         </is>
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>125</t>
+          <t>D</t>
         </is>
       </c>
       <c r="H89" t="inlineStr">
         <is>
-          <t>Cubes of 1,2,3,4,5.</t>
+          <t>Decreasing by 3 letters</t>
         </is>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>Find the next number: 2, 12, 36, 80, 150, ?</t>
+          <t>Next letter: A, D, H, M, S, ?</t>
         </is>
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>252</t>
+          <t>Z</t>
         </is>
       </c>
       <c r="D90" t="inlineStr">
         <is>
-          <t>200</t>
+          <t>Y</t>
         </is>
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>240</t>
+          <t>X</t>
         </is>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>300</t>
+          <t>W</t>
         </is>
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>252</t>
+          <t>Z</t>
         </is>
       </c>
       <c r="H90" t="inlineStr">
         <is>
-          <t>Pattern: n³ - n, for n=2,3,4,5,6 → 6³-6=216-6=210 (adjusted here as 252)</t>
+          <t>Increments +3, +4, +5, +6, +7</t>
         </is>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="n">
-        <v>21</v>
+        <v>2</v>
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>Next number: 3, 9, 27, 81, ?</t>
+          <t>Find the missing letter: Z, X, U, Q, L, ?</t>
         </is>
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>243</t>
+          <t>F</t>
         </is>
       </c>
       <c r="D91" t="inlineStr">
         <is>
-          <t>256</t>
+          <t>G</t>
         </is>
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>225</t>
+          <t>E</t>
         </is>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>270</t>
+          <t>H</t>
         </is>
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>243</t>
+          <t>F</t>
         </is>
       </c>
       <c r="H91" t="inlineStr">
         <is>
-          <t>Multiplying by 3.</t>
+          <t>Positions decrease by 2,3,4,5,6</t>
         </is>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="n">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>Find next letter: Z, V, Q, K, ?</t>
+          <t>What comes next: 13, 21, 34, 55, 89, ?</t>
         </is>
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>144</t>
         </is>
       </c>
       <c r="D92" t="inlineStr">
         <is>
-          <t>F</t>
+          <t>135</t>
         </is>
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>E</t>
+          <t>140</t>
         </is>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>150</t>
         </is>
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>F</t>
+          <t>144</t>
         </is>
       </c>
       <c r="H92" t="inlineStr">
         <is>
-          <t>Difference in positions: -4, -5, -6, -7</t>
+          <t>Fibonacci sequence</t>
         </is>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="n">
-        <v>7</v>
+        <v>13</v>
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>Find the missing term: 2, 3, 5, 9, 17, ?</t>
+          <t>Next number: 7, 14, 28, 56, 112, ?</t>
         </is>
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>33</t>
+          <t>224</t>
         </is>
       </c>
       <c r="D93" t="inlineStr">
         <is>
-          <t>31</t>
+          <t>225</t>
         </is>
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>34</t>
+          <t>223</t>
         </is>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>30</t>
+          <t>220</t>
         </is>
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>33</t>
+          <t>224</t>
         </is>
       </c>
       <c r="H93" t="inlineStr">
         <is>
-          <t>Each term after 2 is previous term ×2 -1.</t>
+          <t>Each term multiplied by 2</t>
         </is>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="n">
-        <v>22</v>
+        <v>2</v>
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>What comes next: MNO, PQR, STU, VWX, ?</t>
+          <t>Find the missing number: 3, 9, 27, ?, 243</t>
         </is>
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>YZA</t>
+          <t>54</t>
         </is>
       </c>
       <c r="D94" t="inlineStr">
         <is>
-          <t>BCD</t>
+          <t>81</t>
         </is>
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>CDE</t>
+          <t>72</t>
         </is>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>DEF</t>
+          <t>90</t>
         </is>
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>YZA</t>
+          <t>81</t>
         </is>
       </c>
       <c r="H94" t="inlineStr">
         <is>
-          <t>Triplets shift +4 letters cyclically.</t>
+          <t>Each term multiplied by 3; 27×3=81</t>
         </is>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="n">
-        <v>23</v>
+        <v>8</v>
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>Find the next number: 17, 19, 23, 29, 31, ?</t>
+          <t>Find missing number: 1, 3, 7, 15, 31, ?</t>
         </is>
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>37</t>
+          <t>63</t>
         </is>
       </c>
       <c r="D95" t="inlineStr">
         <is>
-          <t>35</t>
+          <t>64</t>
         </is>
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>36</t>
+          <t>65</t>
         </is>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>38</t>
+          <t>62</t>
         </is>
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>37</t>
+          <t>63</t>
         </is>
       </c>
       <c r="H95" t="inlineStr">
         <is>
-          <t>Prime numbers</t>
+          <t>Each term = previous ×2 +1</t>
         </is>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="n">
-        <v>16</v>
+        <v>5</v>
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>What letter comes next? P, M, J, G, ?</t>
+          <t>Find the next number: 1, 8, 27, 64, ?</t>
         </is>
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>125</t>
         </is>
       </c>
       <c r="D96" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>130</t>
         </is>
       </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t>E</t>
+          <t>120</t>
         </is>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>F</t>
+          <t>135</t>
         </is>
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>125</t>
         </is>
       </c>
       <c r="H96" t="inlineStr">
         <is>
-          <t>Decreasing by 3 positions each time</t>
+          <t>Cubes of 1,2,3,4,5.</t>
         </is>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="n">
-        <v>9</v>
+        <v>17</v>
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>Find missing number: 2, 4, 8, 14, 22, ?</t>
+          <t>Next letter: F, K, P, U, ?</t>
         </is>
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>32</t>
+          <t>Z</t>
         </is>
       </c>
       <c r="D97" t="inlineStr">
         <is>
-          <t>30</t>
+          <t>Y</t>
         </is>
       </c>
       <c r="E97" t="inlineStr">
         <is>
-          <t>34</t>
+          <t>X</t>
         </is>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>36</t>
+          <t>W</t>
         </is>
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>32</t>
+          <t>Z</t>
         </is>
       </c>
       <c r="H97" t="inlineStr">
         <is>
-          <t>Incrementing differences: +2, +4, +6, +8, next +10=32</t>
+          <t>Increasing by 5 letters each time.</t>
         </is>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="n">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>Next number: 7, 14, 28, 56, 112, ?</t>
+          <t>What comes next: ABC, BCD, CDE, DEF, ?</t>
         </is>
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>224</t>
+          <t>EFG</t>
         </is>
       </c>
       <c r="D98" t="inlineStr">
         <is>
-          <t>225</t>
+          <t>FGH</t>
         </is>
       </c>
       <c r="E98" t="inlineStr">
         <is>
-          <t>223</t>
+          <t>GHI</t>
         </is>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>220</t>
+          <t>HIJ</t>
         </is>
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>224</t>
+          <t>EFG</t>
         </is>
       </c>
       <c r="H98" t="inlineStr">
         <is>
-          <t>Each term multiplied by 2</t>
+          <t>Each triplet shifts by one letter forward.</t>
         </is>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>Next in series: RST, UVW, XYZ, ABC, ?</t>
+          <t>Next number in series: 2, 6, 18, 54, ?</t>
         </is>
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>DEF</t>
+          <t>162</t>
         </is>
       </c>
       <c r="D99" t="inlineStr">
         <is>
-          <t>GHI</t>
+          <t>150</t>
         </is>
       </c>
       <c r="E99" t="inlineStr">
         <is>
-          <t>JKL</t>
+          <t>180</t>
         </is>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>MNO</t>
+          <t>170</t>
         </is>
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>DEF</t>
+          <t>162</t>
         </is>
       </c>
       <c r="H99" t="inlineStr">
         <is>
-          <t>Triplets shift +3 letters cyclically.</t>
+          <t>Each term ×3</t>
         </is>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="n">
-        <v>12</v>
+        <v>22</v>
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>Find missing letter: G, J, N, S, ?</t>
+          <t>What comes next? E, G, J, N, ?</t>
         </is>
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>Y</t>
+          <t>S</t>
         </is>
       </c>
       <c r="D100" t="inlineStr">
         <is>
-          <t>Z</t>
+          <t>T</t>
         </is>
       </c>
       <c r="E100" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>R</t>
         </is>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>W</t>
+          <t>Q</t>
         </is>
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>Y</t>
+          <t>S</t>
         </is>
       </c>
       <c r="H100" t="inlineStr">
         <is>
-          <t>Difference: +3,+4,+5,+6</t>
+          <t>Increments +2,+3,+4,+5</t>
         </is>
       </c>
     </row>
     <row r="101">
       <c r="A101" t="n">
-        <v>22</v>
+        <v>7</v>
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>Find missing number: 9, 19, 39, 79, 159, ?</t>
+          <t>What comes next: 4, 9, 16, 25, 36, ?</t>
         </is>
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>319</t>
+          <t>49</t>
         </is>
       </c>
       <c r="D101" t="inlineStr">
         <is>
-          <t>310</t>
+          <t>48</t>
         </is>
       </c>
       <c r="E101" t="inlineStr">
         <is>
-          <t>320</t>
+          <t>50</t>
         </is>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>300</t>
+          <t>51</t>
         </is>
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t>319</t>
+          <t>49</t>
         </is>
       </c>
       <c r="H101" t="inlineStr">
         <is>
-          <t>Each term doubles minus 1</t>
+          <t>Perfect squares</t>
         </is>
       </c>
     </row>
     <row r="102">
       <c r="A102" t="n">
-        <v>4</v>
+        <v>19</v>
       </c>
       <c r="B102" t="inlineStr">
         <is>
-          <t>What comes next? KL, NO, ST, WX, ?</t>
+          <t>Find the next letter: D, H, M, S, ?</t>
         </is>
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>BD</t>
+          <t>Z</t>
         </is>
       </c>
       <c r="D102" t="inlineStr">
         <is>
-          <t>YZ</t>
+          <t>Y</t>
         </is>
       </c>
       <c r="E102" t="inlineStr">
         <is>
-          <t>AB</t>
+          <t>X</t>
         </is>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>CD</t>
+          <t>W</t>
         </is>
       </c>
       <c r="G102" t="inlineStr">
         <is>
-          <t>AB</t>
+          <t>Z</t>
         </is>
       </c>
       <c r="H102" t="inlineStr">
         <is>
-          <t>Letters move in pairs skipping one letter; after WX comes AB.</t>
+          <t>Increments +4, +5, +6, +7</t>
         </is>
       </c>
     </row>
     <row r="103">
       <c r="A103" t="n">
-        <v>19</v>
+        <v>10</v>
       </c>
       <c r="B103" t="inlineStr">
         <is>
-          <t>Next number in series: 2, 6, 18, 54, ?</t>
+          <t>Find missing number: 4, 9, 19, 39, 79, ?</t>
         </is>
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>162</t>
+          <t>159</t>
         </is>
       </c>
       <c r="D103" t="inlineStr">
         <is>
-          <t>150</t>
+          <t>169</t>
         </is>
       </c>
       <c r="E103" t="inlineStr">
         <is>
-          <t>180</t>
+          <t>149</t>
         </is>
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>170</t>
+          <t>179</t>
         </is>
       </c>
       <c r="G103" t="inlineStr">
         <is>
-          <t>162</t>
+          <t>159</t>
         </is>
       </c>
       <c r="H103" t="inlineStr">
         <is>
-          <t>Each term ×3</t>
+          <t>Each term approximately doubles minus 1.</t>
         </is>
       </c>
     </row>
     <row r="104">
       <c r="A104" t="n">
-        <v>25</v>
+        <v>7</v>
       </c>
       <c r="B104" t="inlineStr">
         <is>
-          <t>Next letter: A, C, F, J, O, ?</t>
+          <t>Find next letter: B, E, I, N, ?</t>
         </is>
       </c>
       <c r="C104" t="inlineStr">
         <is>
+          <t>T</t>
+        </is>
+      </c>
+      <c r="D104" t="inlineStr">
+        <is>
           <t>U</t>
         </is>
       </c>
-      <c r="D104" t="inlineStr">
+      <c r="E104" t="inlineStr">
+        <is>
+          <t>S</t>
+        </is>
+      </c>
+      <c r="F104" t="inlineStr">
+        <is>
+          <t>R</t>
+        </is>
+      </c>
+      <c r="G104" t="inlineStr">
         <is>
           <t>T</t>
         </is>
       </c>
-      <c r="E104" t="inlineStr">
-        <is>
-          <t>S</t>
-        </is>
-      </c>
-      <c r="F104" t="inlineStr">
-        <is>
-          <t>V</t>
-        </is>
-      </c>
-      <c r="G104" t="inlineStr">
-        <is>
-          <t>U</t>
-        </is>
-      </c>
       <c r="H104" t="inlineStr">
         <is>
-          <t>Incrementing by increasing letters.</t>
+          <t>Increments +3, +4, +5, +6</t>
         </is>
       </c>
     </row>
     <row r="105">
       <c r="A105" t="n">
-        <v>8</v>
+        <v>16</v>
       </c>
       <c r="B105" t="inlineStr">
         <is>
-          <t>What comes next: 5, 15, 45, 135, ?</t>
+          <t>What letter comes next? P, M, J, G, ?</t>
         </is>
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>405</t>
+          <t>D</t>
         </is>
       </c>
       <c r="D105" t="inlineStr">
         <is>
-          <t>400</t>
+          <t>C</t>
         </is>
       </c>
       <c r="E105" t="inlineStr">
         <is>
-          <t>410</t>
+          <t>E</t>
         </is>
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>420</t>
+          <t>F</t>
         </is>
       </c>
       <c r="G105" t="inlineStr">
         <is>
-          <t>405</t>
+          <t>D</t>
         </is>
       </c>
       <c r="H105" t="inlineStr">
         <is>
-          <t>Multiplied by 3</t>
+          <t>Decreasing by 3 positions each time</t>
         </is>
       </c>
     </row>
     <row r="106">
       <c r="A106" t="n">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="B106" t="inlineStr">
         <is>
-          <t>Find the next number: 21, 34, 55, 89, 144, ?</t>
+          <t>Find missing number: 11, 21, 43, 87, 175, ?</t>
         </is>
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>233</t>
+          <t>351</t>
         </is>
       </c>
       <c r="D106" t="inlineStr">
         <is>
-          <t>220</t>
+          <t>350</t>
         </is>
       </c>
       <c r="E106" t="inlineStr">
         <is>
-          <t>240</t>
+          <t>352</t>
         </is>
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>200</t>
+          <t>355</t>
         </is>
       </c>
       <c r="G106" t="inlineStr">
         <is>
-          <t>233</t>
+          <t>351</t>
         </is>
       </c>
       <c r="H106" t="inlineStr">
         <is>
-          <t>Fibonacci sequence</t>
+          <t>Each term doubles minus 1</t>
         </is>
       </c>
     </row>
     <row r="107">
       <c r="A107" t="n">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="B107" t="inlineStr">
         <is>
-          <t>Find next letter: B, E, I, N, ?</t>
+          <t>What comes next in the series? AB, DE, IJ, OP, ?</t>
         </is>
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>T</t>
+          <t>UV</t>
         </is>
       </c>
       <c r="D107" t="inlineStr">
         <is>
-          <t>U</t>
+          <t>ST</t>
         </is>
       </c>
       <c r="E107" t="inlineStr">
         <is>
-          <t>S</t>
+          <t>WX</t>
         </is>
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>R</t>
+          <t>YZ</t>
         </is>
       </c>
       <c r="G107" t="inlineStr">
         <is>
-          <t>T</t>
+          <t>UV</t>
         </is>
       </c>
       <c r="H107" t="inlineStr">
         <is>
-          <t>Increments +3, +4, +5, +6</t>
+          <t>Each pair skips increasing letters: +3,+4,+5,+6 between first letters.</t>
         </is>
       </c>
     </row>
     <row r="108">
       <c r="A108" t="n">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="B108" t="inlineStr">
         <is>
-          <t>Find next term: 1, 4, 9, 16, 25, ?</t>
+          <t>What comes next: MNO, PQR, STU, VWX, ?</t>
         </is>
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>36</t>
+          <t>YZA</t>
         </is>
       </c>
       <c r="D108" t="inlineStr">
         <is>
-          <t>49</t>
+          <t>BCD</t>
         </is>
       </c>
       <c r="E108" t="inlineStr">
         <is>
-          <t>30</t>
+          <t>CDE</t>
         </is>
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t>42</t>
+          <t>DEF</t>
         </is>
       </c>
       <c r="G108" t="inlineStr">
         <is>
-          <t>36</t>
+          <t>YZA</t>
         </is>
       </c>
       <c r="H108" t="inlineStr">
         <is>
-          <t>Squares.</t>
+          <t>Triplets shift +4 letters cyclically.</t>
         </is>
       </c>
     </row>
     <row r="109">
       <c r="A109" t="n">
-        <v>5</v>
+        <v>13</v>
       </c>
       <c r="B109" t="inlineStr">
         <is>
-          <t>What comes next? 121, 144, 169, 196, ?</t>
+          <t>Next number: 1, 4, 9, 16, 25, ?</t>
         </is>
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>225</t>
+          <t>36</t>
         </is>
       </c>
       <c r="D109" t="inlineStr">
         <is>
-          <t>240</t>
+          <t>49</t>
         </is>
       </c>
       <c r="E109" t="inlineStr">
         <is>
-          <t>256</t>
+          <t>30</t>
         </is>
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t>289</t>
+          <t>42</t>
         </is>
       </c>
       <c r="G109" t="inlineStr">
         <is>
-          <t>225</t>
+          <t>36</t>
         </is>
       </c>
       <c r="H109" t="inlineStr">
         <is>
-          <t>Squares of 11,12,13,14,15</t>
+          <t>Squares of natural numbers</t>
         </is>
       </c>
     </row>
     <row r="110">
       <c r="A110" t="n">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="B110" t="inlineStr">
         <is>
-          <t>Find next number: 6, 12, 24, 48, 96, ?</t>
+          <t>Find next number: 4, 9, 19, 39, 79, ?</t>
         </is>
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t>192</t>
+          <t>159</t>
         </is>
       </c>
       <c r="D110" t="inlineStr">
         <is>
-          <t>190</t>
+          <t>149</t>
         </is>
       </c>
       <c r="E110" t="inlineStr">
         <is>
-          <t>195</t>
+          <t>169</t>
         </is>
       </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t>185</t>
+          <t>179</t>
         </is>
       </c>
       <c r="G110" t="inlineStr">
         <is>
-          <t>192</t>
+          <t>159</t>
         </is>
       </c>
       <c r="H110" t="inlineStr">
         <is>
-          <t>Each term multiplied by 2</t>
+          <t>Each term roughly doubles minus 1</t>
         </is>
       </c>
     </row>
     <row r="111">
       <c r="A111" t="n">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="B111" t="inlineStr">
         <is>
-          <t>Find missing term: 7, 14, 28, 56, 112, ?</t>
+          <t>Find the next term: DE, GH, KL, OP, ?</t>
         </is>
       </c>
       <c r="C111" t="inlineStr">
         <is>
-          <t>224</t>
+          <t>ST</t>
         </is>
       </c>
       <c r="D111" t="inlineStr">
         <is>
-          <t>226</t>
+          <t>UV</t>
         </is>
       </c>
       <c r="E111" t="inlineStr">
         <is>
-          <t>230</t>
+          <t>WX</t>
         </is>
       </c>
       <c r="F111" t="inlineStr">
         <is>
-          <t>220</t>
+          <t>YZ</t>
         </is>
       </c>
       <c r="G111" t="inlineStr">
         <is>
-          <t>224</t>
+          <t>ST</t>
         </is>
       </c>
       <c r="H111" t="inlineStr">
         <is>
-          <t>Each term ×2.</t>
+          <t>Pairs jump +4 letters.</t>
         </is>
       </c>
     </row>
     <row r="112">
       <c r="A112" t="n">
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="B112" t="inlineStr">
         <is>
-          <t>Find the missing letter: Z, X, U, Q, L, ?</t>
+          <t>What comes next: 3, 8, 15, 24, 35, ?</t>
         </is>
       </c>
       <c r="C112" t="inlineStr">
         <is>
-          <t>F</t>
+          <t>48</t>
         </is>
       </c>
       <c r="D112" t="inlineStr">
         <is>
-          <t>G</t>
+          <t>49</t>
         </is>
       </c>
       <c r="E112" t="inlineStr">
         <is>
-          <t>H</t>
+          <t>50</t>
         </is>
       </c>
       <c r="F112" t="inlineStr">
         <is>
-          <t>I</t>
+          <t>55</t>
         </is>
       </c>
       <c r="G112" t="inlineStr">
         <is>
-          <t>F</t>
+          <t>48</t>
         </is>
       </c>
       <c r="H112" t="inlineStr">
         <is>
-          <t>Positions decrease by 2,3,4,5,6</t>
+          <t>Each term = n² + n, n=1,2,3,...</t>
         </is>
       </c>
     </row>
     <row r="113">
       <c r="A113" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="B113" t="inlineStr">
         <is>
-          <t>Find the missing letter: Z, X, U, Q, L, ?</t>
+          <t>Find next number: 5, 10, 20, 40, 80, ?</t>
         </is>
       </c>
       <c r="C113" t="inlineStr">
         <is>
-          <t>F</t>
+          <t>160</t>
         </is>
       </c>
       <c r="D113" t="inlineStr">
         <is>
-          <t>G</t>
+          <t>180</t>
         </is>
       </c>
       <c r="E113" t="inlineStr">
         <is>
-          <t>E</t>
+          <t>150</t>
         </is>
       </c>
       <c r="F113" t="inlineStr">
         <is>
-          <t>H</t>
+          <t>200</t>
         </is>
       </c>
       <c r="G113" t="inlineStr">
         <is>
-          <t>F</t>
+          <t>160</t>
         </is>
       </c>
       <c r="H113" t="inlineStr">
         <is>
-          <t>Positions decrease by 2,3,4,5,6</t>
+          <t>Each term ×2</t>
         </is>
       </c>
     </row>
     <row r="114">
       <c r="A114" t="n">
-        <v>6</v>
+        <v>24</v>
       </c>
       <c r="B114" t="inlineStr">
         <is>
-          <t>Find missing number: 11, 21, 43, 87, 175, ?</t>
+          <t>Find next term: 1, 4, 9, 16, 25, ?</t>
         </is>
       </c>
       <c r="C114" t="inlineStr">
         <is>
-          <t>351</t>
+          <t>36</t>
         </is>
       </c>
       <c r="D114" t="inlineStr">
         <is>
-          <t>350</t>
+          <t>49</t>
         </is>
       </c>
       <c r="E114" t="inlineStr">
         <is>
-          <t>352</t>
+          <t>30</t>
         </is>
       </c>
       <c r="F114" t="inlineStr">
         <is>
-          <t>355</t>
+          <t>42</t>
         </is>
       </c>
       <c r="G114" t="inlineStr">
         <is>
-          <t>351</t>
+          <t>36</t>
         </is>
       </c>
       <c r="H114" t="inlineStr">
         <is>
-          <t>Each term doubles minus 1</t>
+          <t>Squares.</t>
         </is>
       </c>
     </row>
     <row r="115">
       <c r="A115" t="n">
-        <v>3</v>
+        <v>17</v>
       </c>
       <c r="B115" t="inlineStr">
         <is>
-          <t>Next in series: AZ, CY, EX, GV, ?</t>
+          <t>Find missing term: JK, NO, RS, VW, ?</t>
         </is>
       </c>
       <c r="C115" t="inlineStr">
         <is>
-          <t>IT</t>
+          <t>BC</t>
         </is>
       </c>
       <c r="D115" t="inlineStr">
         <is>
-          <t>HS</t>
+          <t>YZ</t>
         </is>
       </c>
       <c r="E115" t="inlineStr">
         <is>
-          <t>JU</t>
+          <t>XY</t>
         </is>
       </c>
       <c r="F115" t="inlineStr">
         <is>
-          <t>KT</t>
+          <t>ZA</t>
         </is>
       </c>
       <c r="G115" t="inlineStr">
         <is>
-          <t>IT</t>
+          <t>BC</t>
         </is>
       </c>
       <c r="H115" t="inlineStr">
         <is>
-          <t>First letters move +2, second letters -2; IT follows pattern.</t>
+          <t>Pairs jump +4 letters.</t>
         </is>
       </c>
     </row>
     <row r="116">
       <c r="A116" t="n">
-        <v>1</v>
+        <v>25</v>
       </c>
       <c r="B116" t="inlineStr">
         <is>
-          <t>Find the next number: 7, 14, 28, 56, ?</t>
+          <t>Find missing term: UV, YZ, DE, HI, ?</t>
         </is>
       </c>
       <c r="C116" t="inlineStr">
         <is>
-          <t>110</t>
+          <t>LM</t>
         </is>
       </c>
       <c r="D116" t="inlineStr">
         <is>
-          <t>112</t>
+          <t>OP</t>
         </is>
       </c>
       <c r="E116" t="inlineStr">
         <is>
-          <t>120</t>
+          <t>QR</t>
         </is>
       </c>
       <c r="F116" t="inlineStr">
         <is>
-          <t>114</t>
+          <t>ST</t>
         </is>
       </c>
       <c r="G116" t="inlineStr">
         <is>
-          <t>112</t>
+          <t>LM</t>
         </is>
       </c>
       <c r="H116" t="inlineStr">
         <is>
-          <t>Each term is multiplied by 2.</t>
+          <t>Pairs jump +4 letters cyclically.</t>
         </is>
       </c>
     </row>
     <row r="117">
       <c r="A117" t="n">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="B117" t="inlineStr">
         <is>
-          <t>What comes next: 13, 21, 34, 55, 89, ?</t>
+          <t>Find missing term: CDE, FGH, KLM, PQR, ?</t>
         </is>
       </c>
       <c r="C117" t="inlineStr">
         <is>
-          <t>144</t>
+          <t>VWX</t>
         </is>
       </c>
       <c r="D117" t="inlineStr">
         <is>
-          <t>135</t>
+          <t>STU</t>
         </is>
       </c>
       <c r="E117" t="inlineStr">
         <is>
-          <t>150</t>
+          <t>XYZ</t>
         </is>
       </c>
       <c r="F117" t="inlineStr">
         <is>
-          <t>140</t>
+          <t>UVW</t>
         </is>
       </c>
       <c r="G117" t="inlineStr">
         <is>
-          <t>144</t>
+          <t>VWX</t>
         </is>
       </c>
       <c r="H117" t="inlineStr">
         <is>
-          <t>Fibonacci series.</t>
+          <t>Triplets jump by +3 letters each time.</t>
         </is>
       </c>
     </row>
     <row r="118">
       <c r="A118" t="n">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="B118" t="inlineStr">
         <is>
-          <t>Find next term: BC, DE, GH, KL, ?</t>
+          <t>Find next term: 1, 3, 6, 10, 15, ?</t>
         </is>
       </c>
       <c r="C118" t="inlineStr">
         <is>
-          <t>OP</t>
+          <t>21</t>
         </is>
       </c>
       <c r="D118" t="inlineStr">
         <is>
-          <t>MN</t>
+          <t>22</t>
         </is>
       </c>
       <c r="E118" t="inlineStr">
         <is>
-          <t>QR</t>
+          <t>20</t>
         </is>
       </c>
       <c r="F118" t="inlineStr">
         <is>
-          <t>ST</t>
+          <t>23</t>
         </is>
       </c>
       <c r="G118" t="inlineStr">
         <is>
-          <t>OP</t>
+          <t>21</t>
         </is>
       </c>
       <c r="H118" t="inlineStr">
         <is>
-          <t>Pairs jump increasing letters.</t>
+          <t>Triangular numbers</t>
         </is>
       </c>
     </row>
     <row r="119">
       <c r="A119" t="n">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="B119" t="inlineStr">
         <is>
-          <t>What comes next: 1, 8, 27, 64, 125, ?</t>
+          <t>What comes next: 2, 6, 18, 54, 162, ?</t>
         </is>
       </c>
       <c r="C119" t="inlineStr">
         <is>
-          <t>216</t>
+          <t>486</t>
         </is>
       </c>
       <c r="D119" t="inlineStr">
         <is>
-          <t>225</t>
+          <t>500</t>
         </is>
       </c>
       <c r="E119" t="inlineStr">
         <is>
-          <t>210</t>
+          <t>490</t>
         </is>
       </c>
       <c r="F119" t="inlineStr">
         <is>
-          <t>230</t>
+          <t>480</t>
         </is>
       </c>
       <c r="G119" t="inlineStr">
         <is>
-          <t>216</t>
+          <t>486</t>
         </is>
       </c>
       <c r="H119" t="inlineStr">
         <is>
-          <t>Cubes of natural numbers</t>
+          <t>Each term ×3</t>
         </is>
       </c>
     </row>
     <row r="120">
       <c r="A120" t="n">
-        <v>19</v>
+        <v>10</v>
       </c>
       <c r="B120" t="inlineStr">
         <is>
-          <t>What comes next: 8, 27, 64, 125, ?</t>
+          <t>Find the next number: 21, 34, 55, 89, 144, ?</t>
         </is>
       </c>
       <c r="C120" t="inlineStr">
         <is>
-          <t>216</t>
+          <t>233</t>
         </is>
       </c>
       <c r="D120" t="inlineStr">
         <is>
-          <t>225</t>
+          <t>220</t>
         </is>
       </c>
       <c r="E120" t="inlineStr">
         <is>
+          <t>240</t>
+        </is>
+      </c>
+      <c r="F120" t="inlineStr">
+        <is>
           <t>200</t>
         </is>
       </c>
-      <c r="F120" t="inlineStr">
-        <is>
-          <t>230</t>
-        </is>
-      </c>
       <c r="G120" t="inlineStr">
         <is>
-          <t>216</t>
+          <t>233</t>
         </is>
       </c>
       <c r="H120" t="inlineStr">
         <is>
-          <t>Cubes of 2,3,4,5,6.</t>
+          <t>Fibonacci sequence</t>
         </is>
       </c>
     </row>
     <row r="121">
       <c r="A121" t="n">
-        <v>19</v>
+        <v>2</v>
       </c>
       <c r="B121" t="inlineStr">
         <is>
-          <t>Find the next letter: D, H, M, S, ?</t>
+          <t>Find the missing number: 3, 9, 27, 81, ?</t>
         </is>
       </c>
       <c r="C121" t="inlineStr">
         <is>
-          <t>Z</t>
+          <t>243</t>
         </is>
       </c>
       <c r="D121" t="inlineStr">
         <is>
-          <t>Y</t>
+          <t>256</t>
         </is>
       </c>
       <c r="E121" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>225</t>
         </is>
       </c>
       <c r="F121" t="inlineStr">
         <is>
-          <t>W</t>
+          <t>270</t>
         </is>
       </c>
       <c r="G121" t="inlineStr">
         <is>
-          <t>Z</t>
+          <t>243</t>
         </is>
       </c>
       <c r="H121" t="inlineStr">
         <is>
-          <t>Increments +4, +5, +6, +7</t>
+          <t>Each term multiplied by 3.</t>
         </is>
       </c>
     </row>
     <row r="122">
       <c r="A122" t="n">
-        <v>17</v>
+        <v>4</v>
       </c>
       <c r="B122" t="inlineStr">
         <is>
-          <t>Find missing number: 3, 9, 27, 81, ?</t>
+          <t>Find the missing letter: A, C, F, J, O, ?</t>
         </is>
       </c>
       <c r="C122" t="inlineStr">
         <is>
-          <t>243</t>
+          <t>U</t>
         </is>
       </c>
       <c r="D122" t="inlineStr">
         <is>
-          <t>250</t>
+          <t>T</t>
         </is>
       </c>
       <c r="E122" t="inlineStr">
         <is>
-          <t>240</t>
+          <t>S</t>
         </is>
       </c>
       <c r="F122" t="inlineStr">
         <is>
-          <t>245</t>
+          <t>V</t>
         </is>
       </c>
       <c r="G122" t="inlineStr">
         <is>
-          <t>243</t>
+          <t>U</t>
         </is>
       </c>
       <c r="H122" t="inlineStr">
         <is>
-          <t>Multiplied by 3</t>
+          <t>Alphabet position increments +2,+3,+4,+5,+6.</t>
         </is>
       </c>
     </row>
     <row r="123">
       <c r="A123" t="n">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="B123" t="inlineStr">
         <is>
-          <t>Find the next term: 7, 14, 28, 56, 112, ?</t>
+          <t>What comes next: 13, 21, 34, 55, 89, ?</t>
         </is>
       </c>
       <c r="C123" t="inlineStr">
         <is>
-          <t>224</t>
+          <t>144</t>
         </is>
       </c>
       <c r="D123" t="inlineStr">
         <is>
-          <t>230</t>
+          <t>135</t>
         </is>
       </c>
       <c r="E123" t="inlineStr">
         <is>
-          <t>220</t>
+          <t>150</t>
         </is>
       </c>
       <c r="F123" t="inlineStr">
         <is>
-          <t>210</t>
+          <t>140</t>
         </is>
       </c>
       <c r="G123" t="inlineStr">
         <is>
-          <t>224</t>
+          <t>144</t>
         </is>
       </c>
       <c r="H123" t="inlineStr">
         <is>
-          <t>Each term ×2</t>
+          <t>Fibonacci series.</t>
         </is>
       </c>
     </row>
     <row r="124">
       <c r="A124" t="n">
-        <v>1</v>
+        <v>17</v>
       </c>
       <c r="B124" t="inlineStr">
         <is>
-          <t>Find the next number: 2, 5, 10, 17, 26, ?</t>
+          <t>What comes next: 1, 8, 27, 64, 125, ?</t>
         </is>
       </c>
       <c r="C124" t="inlineStr">
         <is>
-          <t>35</t>
+          <t>216</t>
         </is>
       </c>
       <c r="D124" t="inlineStr">
         <is>
-          <t>37</t>
+          <t>225</t>
         </is>
       </c>
       <c r="E124" t="inlineStr">
         <is>
-          <t>38</t>
+          <t>210</t>
         </is>
       </c>
       <c r="F124" t="inlineStr">
         <is>
-          <t>40</t>
+          <t>230</t>
         </is>
       </c>
       <c r="G124" t="inlineStr">
         <is>
-          <t>37</t>
+          <t>216</t>
         </is>
       </c>
       <c r="H124" t="inlineStr">
         <is>
-          <t>Each term increases by consecutive odd numbers: +3, +5, +7, +9, next +11=37</t>
+          <t>Cubes of natural numbers</t>
         </is>
       </c>
     </row>
